--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/_tutorial.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/_tutorial.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="800">
   <si>
     <t xml:space="preserve">version</t>
   </si>
@@ -302,6 +302,15 @@
     <t xml:space="preserve">위험한 물</t>
   </si>
   <si>
+    <t xml:space="preserve">field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フィールドエフェクト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field Effect</t>
+  </si>
+  <si>
     <t xml:space="preserve">ether</t>
   </si>
   <si>
@@ -492,6 +501,132 @@
   </si>
   <si>
     <t xml:space="preserve">*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ねえ、感じる？
+この異様な空気…何か特別な「理」が息づいている。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you feel it?
+This strange air...there’s a special law at work here.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">있잖아, 느껴져?
+이 이상한 공기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">… 뭔가 특별한 「이치」가 숨쉬고 있어.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">これは…そう、きっと「フィールドエフェクト」が発動しているのね。
+話には聞いていたけど、実際に経験するのは私も初めてよ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes—something like a ‘Field Effect’ is pulsing through this place.
+I’ve heard about it before, but this is my first time experiencing it myself.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">이건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">… 그래, 틀림없이 「필드 이펙트」가 발동하고 있는 거겠지.
+나도 얘기는 들어 봤지만, 실제로 경험하는 건 처음이야.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">フィールドエフェクトは、現在居るマップにだけ適用される特殊なルール。
+時計の右側に、今まで見たことがないアイコンが見えるでしょ？
+このアイコンを調べれば、効果を知ることができるわ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Field Effect is a special rule that applies only to the map you’re currently on.
+See that unfamiliar icon to the right of the clock?
+If you check it, you can learn what effect is active.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">필드 이펙트는 현재 있는 맵에서만 적용되는 특별한 룰이야.
+시계 오른쪽에, 지금까지 본 적 없는 아이콘이 보이지?
+이 아이콘을 살펴보면 무슨 효과인지 알 수 있어.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">世界の理を変えるほどの力が、この場所には働いている…
+もちろん、それには相応の理由があるはずよ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There’s a power here strong enough to bend the very laws of the world.
+And of course, there must be a reason for that.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">세계의 이치를 바꿔버릴 정도의 힘이, 이 장소에 있어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">…
+물론, 그에 상응하는 이유가 있을 거야.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">…気をつけて進んでね。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…Be careful as you go.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…조심하면서 나아가도록 해.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">end</t>
   </si>
   <si>
     <t xml:space="preserve">チリンチリーン！ 
@@ -507,12 +642,6 @@
     <t xml:space="preserve">딸랑딸랑!
 네가 모험을 시작한 날부터…
 무려 2000년의 시간이 흘렀어!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">...</t>
   </si>
   <si>
     <t xml:space="preserve">なかなか、長生きするのね？</t>
@@ -602,9 +731,6 @@
   <si>
     <t xml:space="preserve">그러니까…
 이제부터는, 조금 느긋하게 시간을 보내지 않을래?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">end</t>
   </si>
   <si>
     <t xml:space="preserve">薬草みーつけた！</t>
@@ -1545,47 +1671,8 @@
 What on earth were you doing? </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">이 기간 동안 너는 정확히 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">#1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">번 죽었네</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">…
+    <t xml:space="preserve">이 기간 동안 너는 정확히 #1번 죽었네…
 대체 뭔 짓을 하고 다닌 거야?</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">さすがの私も、キミみたいな冒険者は初めてよ…</t>
@@ -1594,26 +1681,7 @@
     <t xml:space="preserve">Even for me, I’ve never seen an adventurer quite like you...</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">아니 진짜로, 너 같은 모험가는 생전 처음이야</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">…</t>
-    </r>
+    <t xml:space="preserve">아니 진짜로, 너 같은 모험가는 생전 처음이야…</t>
   </si>
   <si>
     <t xml:space="preserve">これからは死んだら
@@ -3246,7 +3314,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3300,13 +3368,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="游ゴシック"/>
@@ -3314,18 +3375,11 @@
       <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
-      <charset val="129"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3432,10 +3486,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3444,7 +3494,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3452,11 +3502,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3658,7 +3712,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="8.83"/>
@@ -4190,9 +4244,9 @@
         <v>92</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="1" t="n">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>8</v>
@@ -4203,19 +4257,16 @@
       <c r="E26" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H26" s="0" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="n">
-        <v>850</v>
+        <v>830</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>8</v>
@@ -4224,53 +4275,45 @@
         <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="G27" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="H27" s="0" t="s">
         <v>99</v>
       </c>
-      <c r="H27" s="0" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="1" t="n">
+        <v>850</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4" t="n">
-        <v>851</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="5" t="s">
+      <c r="F28" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="G28" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="H28" s="0" t="s">
         <v>103</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="n">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>8</v>
@@ -4279,16 +4322,16 @@
         <v>8</v>
       </c>
       <c r="E29" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="G29" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="H29" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -4301,7 +4344,7 @@
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="n">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>8</v>
@@ -4310,22 +4353,29 @@
         <v>8</v>
       </c>
       <c r="E30" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="H30" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H30" s="1" t="s">
-        <v>112</v>
-      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="n">
-        <v>870</v>
+        <v>860</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>8</v>
@@ -4334,29 +4384,22 @@
         <v>8</v>
       </c>
       <c r="E31" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="G31" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="H31" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="n">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>8</v>
@@ -4365,22 +4408,29 @@
         <v>8</v>
       </c>
       <c r="E32" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="G32" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="H32" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="H32" s="1" t="s">
-        <v>120</v>
-      </c>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="n">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>8</v>
@@ -4389,22 +4439,22 @@
         <v>8</v>
       </c>
       <c r="E33" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="G33" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="G33" s="10" t="s">
+      <c r="H33" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="n">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>8</v>
@@ -4413,29 +4463,22 @@
         <v>8</v>
       </c>
       <c r="E34" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="G34" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="H34" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H34" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="n">
-        <v>890</v>
+        <v>880</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>8</v>
@@ -4444,16 +4487,16 @@
         <v>8</v>
       </c>
       <c r="E35" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="G35" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="H35" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -4464,31 +4507,39 @@
       <c r="O35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="1" t="n">
-        <v>899</v>
-      </c>
-      <c r="C36" s="1" t="s">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4" t="n">
+        <v>890</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E36" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F36" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="G36" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H36" s="0" t="s">
+      <c r="H36" s="1" t="s">
         <v>135</v>
       </c>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="1" t="n">
-        <v>950</v>
+        <v>899</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>8</v>
@@ -4496,22 +4547,22 @@
       <c r="D37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="5" t="s">
         <v>136</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>137</v>
       </c>
       <c r="G37" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H37" s="0" t="s">
         <v>138</v>
-      </c>
-      <c r="H37" s="0" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="1" t="n">
-        <v>990</v>
+        <v>950</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>8</v>
@@ -4520,16 +4571,39 @@
         <v>8</v>
       </c>
       <c r="E38" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="G38" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="0" t="s">
         <v>142</v>
       </c>
-      <c r="H38" s="0" t="s">
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="1" t="n">
+        <v>990</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>143</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H39" s="0" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -4548,406 +4622,393 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K363"/>
+  <dimension ref="A1:K373"/>
   <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="12" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="11.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="12" width="15.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="12" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="12" width="6.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="12" width="74.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="12" width="88.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="13" width="55.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="64.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="63.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="12" width="47.06"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="E1" s="12" t="s">
+      <c r="B1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="C1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="D1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="13" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="12" t="n">
+      <c r="H2" s="1" t="n">
         <f aca="false">MAX(H4:H1048576)</f>
-        <v>232</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D5" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>150</v>
+      <c r="D5" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D6" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="F6" s="12" t="s">
+      <c r="D6" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D7" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>153</v>
+      <c r="D7" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D8" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>155</v>
+      <c r="D8" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="12" t="s">
-        <v>156</v>
+      <c r="B9" s="1" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="K12" s="12"/>
-    </row>
-    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H13" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="K12" s="14"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I13" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H14" s="1" t="n">
+        <v>233</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H15" s="1" t="n">
+        <v>234</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H16" s="1" t="n">
+        <v>235</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H17" s="1" t="n">
+        <v>236</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H18" s="1" t="n">
+        <v>327</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I19" s="4"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="14"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I20" s="4"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="14"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="14"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="K22" s="14"/>
+    </row>
+    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H23" s="1" t="n">
         <v>220</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="K13" s="12" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H14" s="12" t="n">
+      <c r="I23" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H24" s="1" t="n">
         <v>221</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I24" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J24" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="K14" s="12" t="s">
+      <c r="K24" s="14" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H15" s="12" t="n">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H25" s="1" t="n">
         <v>222</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="K15" s="12" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H16" s="12" t="n">
+      <c r="I25" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H26" s="1" t="n">
         <v>223</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="K16" s="12" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H17" s="12" t="n">
+      <c r="I26" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H27" s="1" t="n">
         <v>224</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="K17" s="12" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H18" s="12" t="n">
+      <c r="I27" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H28" s="1" t="n">
         <v>225</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="K18" s="12" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H19" s="12" t="n">
+      <c r="I28" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H29" s="1" t="n">
         <v>226</v>
       </c>
-      <c r="I19" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="K19" s="12" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H20" s="12" t="n">
+      <c r="I29" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H30" s="1" t="n">
         <v>227</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I30" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="J20" s="10" t="s">
+      <c r="J30" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="K20" s="12" t="s">
+      <c r="K30" s="14" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H21" s="12" t="n">
+    <row r="31" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H31" s="1" t="n">
         <v>228</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I31" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H32" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="J21" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="K21" s="12" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H22" s="12" t="n">
-        <v>229</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="K22" s="12" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="12"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="14"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="K24" s="12"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H25" s="12" t="n">
+      <c r="K34" s="14"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H35" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="I25" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="K25" s="12" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H26" s="12" t="n">
+      <c r="I35" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="K35" s="14" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H36" s="1" t="n">
         <v>201</v>
       </c>
-      <c r="I26" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="K26" s="12" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H27" s="12" t="n">
+      <c r="I36" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H37" s="1" t="n">
         <v>202</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="K27" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H28" s="12" t="n">
-        <v>203</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="J28" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="K28" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H29" s="12" t="n">
-        <v>204</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="J29" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="K29" s="12" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H30" s="12" t="n">
-        <v>205</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="J30" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="K30" s="12" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H31" s="12" t="n">
-        <v>206</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="J31" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="K31" s="12" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H32" s="12" t="n">
-        <v>207</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="K32" s="12" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H33" s="12" t="n">
-        <v>208</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="K33" s="12" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="12"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="12"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="K36" s="12"/>
-    </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H37" s="12" t="n">
-        <v>210</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>208</v>
@@ -4955,13 +5016,13 @@
       <c r="J37" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="K37" s="12" t="s">
+      <c r="K37" s="14" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H38" s="12" t="n">
-        <v>211</v>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H38" s="1" t="n">
+        <v>203</v>
       </c>
       <c r="I38" s="4" t="s">
         <v>211</v>
@@ -4969,633 +5030,442 @@
       <c r="J38" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="K38" s="12" t="s">
+      <c r="K38" s="14" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I39" s="4"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="12"/>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="12"/>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="12"/>
+    <row r="39" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H39" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="K39" s="14" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H40" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H41" s="1" t="n">
+        <v>206</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="12"/>
-    </row>
-    <row r="43" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="12"/>
-      <c r="J43" s="12"/>
-      <c r="K43" s="12"/>
-    </row>
-    <row r="44" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="12"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12" t="n">
-        <v>193</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="J44" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="K44" s="12" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="12"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12" t="n">
-        <v>194</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="J45" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="K45" s="12" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="46" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="12"/>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12" t="n">
-        <v>195</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="J46" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="K46" s="12" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="47" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="12"/>
-      <c r="B47" s="12"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12" t="n">
-        <v>196</v>
+      <c r="H42" s="1" t="n">
+        <v>207</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H43" s="1" t="n">
+        <v>208</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="K43" s="14" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="14"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="14"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="K46" s="14"/>
+    </row>
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H47" s="1" t="n">
+        <v>210</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="K47" s="12" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="48" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="12"/>
-      <c r="B48" s="12"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12" t="n">
-        <v>197</v>
+        <v>227</v>
+      </c>
+      <c r="K47" s="14" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H48" s="1" t="n">
+        <v>211</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="K48" s="12" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="49" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="12"/>
-      <c r="B49" s="12"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="12" t="n">
-        <v>198</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="J49" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="K49" s="12" t="s">
+      <c r="K48" s="14" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="12"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12"/>
-      <c r="H50" s="12" t="n">
-        <v>199</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="J50" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="K50" s="12" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="51" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="12"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I49" s="4"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="14"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="14"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="4" t="s">
+        <v>177</v>
+      </c>
       <c r="I51" s="4"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="12"/>
-    </row>
-    <row r="52" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="12"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="14"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="4"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
-      <c r="K52" s="12"/>
+      <c r="K52" s="14"/>
     </row>
     <row r="53" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="12"/>
-      <c r="B53" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="12"/>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="12"/>
-    </row>
-    <row r="55" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
+      <c r="A53" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="K53" s="14"/>
+    </row>
+    <row r="54" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H54" s="1" t="n">
+        <v>193</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="J54" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="K54" s="14" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H55" s="1" t="n">
+        <v>194</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="J55" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="K55" s="14" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H56" s="1" t="n">
+        <v>195</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J56" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="K56" s="14" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H57" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="J57" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="K57" s="14" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H58" s="1" t="n">
+        <v>197</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J58" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="K58" s="14" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H59" s="1" t="n">
+        <v>198</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="J59" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="K59" s="14" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H60" s="1" t="n">
+        <v>199</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="J60" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="K60" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I61" s="4"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="14"/>
+    </row>
+    <row r="62" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="14"/>
+    </row>
+    <row r="63" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="14"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="14"/>
+    </row>
+    <row r="65" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B55" s="12"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
-      <c r="K55" s="12"/>
-    </row>
-    <row r="56" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="12"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12" t="n">
+      <c r="K65" s="14"/>
+    </row>
+    <row r="66" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H66" s="1" t="n">
         <v>184</v>
       </c>
-      <c r="I56" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="J56" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="K56" s="12" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="12"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12" t="n">
+      <c r="I66" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="J66" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="K66" s="14" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="67" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H67" s="1" t="n">
         <v>185</v>
       </c>
-      <c r="I57" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="J57" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="K57" s="12" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="58" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="12"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12" t="n">
+      <c r="I67" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="J67" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="K67" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="68" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H68" s="1" t="n">
         <v>186</v>
       </c>
-      <c r="I58" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="J58" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="K58" s="12" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="59" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="12"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="12" t="n">
+      <c r="I68" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="J68" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="K68" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="69" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H69" s="1" t="n">
         <v>187</v>
       </c>
-      <c r="I59" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="J59" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="K59" s="12" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="60" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="12"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="12" t="n">
+      <c r="I69" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J69" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="K69" s="14" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="70" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H70" s="1" t="n">
         <v>188</v>
       </c>
-      <c r="I60" s="4" t="s">
+      <c r="I70" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="J60" s="4" t="s">
+      <c r="J70" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="K60" s="12" t="s">
+      <c r="K70" s="14" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="61" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="12"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="12" t="n">
+    <row r="71" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H71" s="1" t="n">
         <v>189</v>
       </c>
-      <c r="I61" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="J61" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="K61" s="12" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="62" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="12"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
-      <c r="F62" s="12"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="12" t="n">
+      <c r="I71" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="J71" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="K71" s="14" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="72" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H72" s="1" t="n">
         <v>190</v>
       </c>
-      <c r="I62" s="4" t="s">
+      <c r="I72" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="J62" s="4" t="s">
+      <c r="J72" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="K62" s="12" t="s">
+      <c r="K72" s="14" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="63" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="12"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="12"/>
-      <c r="E63" s="12"/>
-      <c r="F63" s="12"/>
-      <c r="G63" s="12"/>
-      <c r="H63" s="12" t="n">
+    <row r="73" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H73" s="1" t="n">
         <v>191</v>
       </c>
-      <c r="I63" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="J63" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="K63" s="12" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="64" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="12"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="12"/>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12"/>
-      <c r="H64" s="12" t="n">
+      <c r="I73" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="J73" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="K73" s="14" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="74" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H74" s="1" t="n">
         <v>192</v>
       </c>
-      <c r="I64" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="J64" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="K64" s="12" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="65" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="12"/>
-      <c r="B65" s="12"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="12"/>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="12"/>
-      <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="12"/>
-    </row>
-    <row r="66" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="12"/>
-      <c r="B66" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12"/>
-      <c r="H66" s="12"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="12"/>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
-      <c r="K67" s="12"/>
-    </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="K68" s="12"/>
-    </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K69" s="12"/>
-    </row>
-    <row r="70" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="12"/>
-      <c r="B70" s="12"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12"/>
-      <c r="E70" s="12"/>
-      <c r="F70" s="12"/>
-      <c r="G70" s="12"/>
-      <c r="H70" s="12" t="n">
+      <c r="I74" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="J74" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="K74" s="14" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="75" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="14"/>
+    </row>
+    <row r="76" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="14"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="14"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K78" s="14"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K79" s="14"/>
+    </row>
+    <row r="80" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H80" s="1" t="n">
         <v>174</v>
-      </c>
-      <c r="I70" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="J70" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="K70" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="71" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="12"/>
-      <c r="B71" s="12"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12"/>
-      <c r="E71" s="12"/>
-      <c r="F71" s="12"/>
-      <c r="G71" s="12"/>
-      <c r="H71" s="12" t="n">
-        <v>175</v>
-      </c>
-      <c r="I71" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="J71" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="K71" s="12" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="72" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="12"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="12"/>
-      <c r="D72" s="12"/>
-      <c r="E72" s="12"/>
-      <c r="F72" s="12"/>
-      <c r="G72" s="12"/>
-      <c r="H72" s="12" t="n">
-        <v>176</v>
-      </c>
-      <c r="I72" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="J72" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="K72" s="12" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="73" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="12"/>
-      <c r="B73" s="12"/>
-      <c r="C73" s="12"/>
-      <c r="D73" s="12"/>
-      <c r="E73" s="12"/>
-      <c r="F73" s="12"/>
-      <c r="G73" s="12"/>
-      <c r="H73" s="12" t="n">
-        <v>177</v>
-      </c>
-      <c r="I73" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="J73" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="K73" s="12" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="74" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="12"/>
-      <c r="B74" s="12"/>
-      <c r="C74" s="12"/>
-      <c r="D74" s="12"/>
-      <c r="E74" s="12"/>
-      <c r="F74" s="12"/>
-      <c r="G74" s="12"/>
-      <c r="H74" s="12" t="n">
-        <v>178</v>
-      </c>
-      <c r="I74" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="J74" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="K74" s="12" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="75" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="12"/>
-      <c r="B75" s="12"/>
-      <c r="C75" s="12"/>
-      <c r="D75" s="12"/>
-      <c r="E75" s="12"/>
-      <c r="F75" s="12"/>
-      <c r="G75" s="12"/>
-      <c r="H75" s="12" t="n">
-        <v>179</v>
-      </c>
-      <c r="I75" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="J75" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="K75" s="12" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="K76" s="12"/>
-    </row>
-    <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="K78" s="12"/>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K79" s="12"/>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H80" s="12" t="n">
-        <v>180</v>
       </c>
       <c r="I80" s="4" t="s">
         <v>274</v>
@@ -5603,391 +5473,246 @@
       <c r="J80" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="K80" s="12" t="s">
+      <c r="K80" s="14" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H81" s="12" t="n">
-        <v>181</v>
+    <row r="81" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H81" s="1" t="n">
+        <v>175</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="J81" s="10" t="s">
+      <c r="J81" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="K81" s="12" t="s">
+      <c r="K81" s="14" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H82" s="12" t="n">
-        <v>182</v>
+    <row r="82" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H82" s="1" t="n">
+        <v>176</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="J82" s="10" t="s">
+      <c r="J82" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="K82" s="12" t="s">
+      <c r="K82" s="14" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H83" s="12" t="n">
-        <v>183</v>
+    <row r="83" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H83" s="1" t="n">
+        <v>177</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="J83" s="10" t="s">
+      <c r="J83" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="K83" s="12" t="s">
+      <c r="K83" s="14" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="4" t="s">
+    <row r="84" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H84" s="1" t="n">
+        <v>178</v>
+      </c>
+      <c r="I84" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="K84" s="14" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="85" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H85" s="1" t="n">
+        <v>179</v>
+      </c>
+      <c r="I85" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K85" s="14" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K86" s="14"/>
+    </row>
+    <row r="88" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="K88" s="14"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K89" s="14"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H90" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="I90" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="J90" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="K90" s="14" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H91" s="1" t="n">
+        <v>181</v>
+      </c>
+      <c r="I91" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="J91" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="K91" s="14" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H92" s="1" t="n">
+        <v>182</v>
+      </c>
+      <c r="I92" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="J92" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="K92" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H93" s="1" t="n">
         <v>183</v>
       </c>
-      <c r="K84" s="12"/>
-    </row>
-    <row r="87" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4" t="s">
+      <c r="I93" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="J93" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="K93" s="14" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B94" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K94" s="14"/>
+    </row>
+    <row r="97" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B87" s="12"/>
-      <c r="C87" s="12"/>
-      <c r="D87" s="12"/>
-      <c r="E87" s="12"/>
-      <c r="F87" s="12"/>
-      <c r="G87" s="12"/>
-      <c r="H87" s="12"/>
-      <c r="I87" s="12"/>
-      <c r="J87" s="12"/>
-      <c r="K87" s="12"/>
-    </row>
-    <row r="88" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="12"/>
-      <c r="B88" s="12"/>
-      <c r="C88" s="12"/>
-      <c r="D88" s="12"/>
-      <c r="E88" s="12"/>
-      <c r="F88" s="12"/>
-      <c r="G88" s="12"/>
-      <c r="H88" s="12"/>
-      <c r="I88" s="12"/>
-      <c r="J88" s="12"/>
-      <c r="K88" s="12"/>
-    </row>
-    <row r="89" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="12"/>
-      <c r="B89" s="12"/>
-      <c r="C89" s="12"/>
-      <c r="D89" s="12"/>
-      <c r="E89" s="12"/>
-      <c r="F89" s="12"/>
-      <c r="G89" s="12"/>
-      <c r="H89" s="12" t="n">
+      <c r="K97" s="14"/>
+    </row>
+    <row r="98" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K98" s="14"/>
+    </row>
+    <row r="99" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H99" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="I89" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="J89" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="K89" s="12" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="90" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="12"/>
-      <c r="B90" s="12"/>
-      <c r="C90" s="12"/>
-      <c r="D90" s="12"/>
-      <c r="E90" s="12"/>
-      <c r="F90" s="12"/>
-      <c r="G90" s="12"/>
-      <c r="H90" s="12" t="n">
+      <c r="I99" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="J99" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="K99" s="14" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="100" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H100" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="I90" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="J90" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K90" s="12" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="91" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="12"/>
-      <c r="B91" s="12"/>
-      <c r="C91" s="12"/>
-      <c r="D91" s="12"/>
-      <c r="E91" s="12"/>
-      <c r="F91" s="12"/>
-      <c r="G91" s="12"/>
-      <c r="H91" s="12" t="n">
+      <c r="I100" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J100" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="K100" s="14" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="101" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H101" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="I91" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="J91" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="K91" s="12" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="92" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="12"/>
-      <c r="B92" s="12"/>
-      <c r="C92" s="12"/>
-      <c r="D92" s="12"/>
-      <c r="E92" s="12"/>
-      <c r="F92" s="12"/>
-      <c r="G92" s="12"/>
-      <c r="H92" s="12" t="n">
+      <c r="I101" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="J101" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="K101" s="14" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="102" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H102" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="I92" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="J92" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="K92" s="12" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="93" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="12"/>
-      <c r="B93" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C93" s="12"/>
-      <c r="D93" s="12"/>
-      <c r="E93" s="12"/>
-      <c r="F93" s="12"/>
-      <c r="G93" s="12"/>
-      <c r="H93" s="12"/>
-      <c r="I93" s="12"/>
-      <c r="J93" s="12"/>
-      <c r="K93" s="12"/>
-    </row>
-    <row r="94" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J94" s="4"/>
-    </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="4" t="s">
+      <c r="I102" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="J102" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="K102" s="14" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="103" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B103" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K103" s="14"/>
+    </row>
+    <row r="104" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J104" s="4"/>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="I95" s="4"/>
-      <c r="J95" s="4"/>
-      <c r="K95" s="4"/>
-    </row>
-    <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4"/>
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="4"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="4"/>
-      <c r="H96" s="12" t="n">
-        <v>169</v>
-      </c>
-      <c r="I96" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="J96" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="K96" s="4" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="4"/>
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="4"/>
-      <c r="H97" s="12" t="n">
-        <v>170</v>
-      </c>
-      <c r="I97" s="15" t="s">
-        <v>301</v>
-      </c>
-      <c r="J97" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="K97" s="4" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="4"/>
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-      <c r="E98" s="4"/>
-      <c r="F98" s="4"/>
-      <c r="G98" s="4"/>
-      <c r="H98" s="12" t="n">
-        <v>171</v>
-      </c>
-      <c r="I98" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="J98" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="K98" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="4"/>
-      <c r="B99" s="4"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4"/>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="12" t="n">
-        <v>172</v>
-      </c>
-      <c r="I99" s="15" t="s">
-        <v>307</v>
-      </c>
-      <c r="J99" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K99" s="4" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="4"/>
-      <c r="B100" s="4"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
-      <c r="E100" s="4"/>
-      <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
-      <c r="H100" s="12" t="n">
-        <v>173</v>
-      </c>
-      <c r="I100" s="15" t="s">
-        <v>310</v>
-      </c>
-      <c r="J100" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="K100" s="4" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="4"/>
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
-      <c r="E101" s="4"/>
-      <c r="F101" s="4"/>
-      <c r="G101" s="4"/>
-      <c r="I101" s="15"/>
-      <c r="J101" s="10"/>
-      <c r="K101" s="4"/>
-    </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="4"/>
-      <c r="B102" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
-      <c r="E102" s="4"/>
-      <c r="F102" s="4"/>
-      <c r="G102" s="4"/>
-      <c r="I102" s="4"/>
-      <c r="J102" s="4"/>
-      <c r="K102" s="4"/>
-    </row>
-    <row r="103" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B103" s="4"/>
-      <c r="C103" s="4"/>
-      <c r="D103" s="4"/>
-      <c r="E103" s="4"/>
-      <c r="F103" s="4"/>
-      <c r="G103" s="4"/>
-      <c r="H103" s="12"/>
-      <c r="I103" s="4"/>
-      <c r="J103" s="4"/>
-      <c r="K103" s="4"/>
-    </row>
-    <row r="104" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="4"/>
-      <c r="B104" s="4"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="4"/>
-      <c r="E104" s="4"/>
-      <c r="F104" s="4"/>
-      <c r="G104" s="4"/>
-      <c r="H104" s="12" t="n">
-        <v>155</v>
-      </c>
-      <c r="I104" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="J104" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="K104" s="4" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="105" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
       <c r="G105" s="4"/>
-      <c r="H105" s="12" t="n">
-        <v>156</v>
-      </c>
-      <c r="I105" s="15" t="s">
-        <v>316</v>
-      </c>
-      <c r="J105" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="K105" s="4" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="106" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I105" s="4"/>
+      <c r="J105" s="4"/>
+      <c r="K105" s="4"/>
+    </row>
+    <row r="106" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -5995,20 +5720,20 @@
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
       <c r="G106" s="4"/>
-      <c r="H106" s="12" t="n">
-        <v>157</v>
-      </c>
-      <c r="I106" s="15" t="s">
-        <v>319</v>
+      <c r="H106" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="I106" s="16" t="s">
+        <v>316</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="107" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -6016,20 +5741,20 @@
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
       <c r="G107" s="4"/>
-      <c r="H107" s="12" t="n">
-        <v>158</v>
-      </c>
-      <c r="I107" s="15" t="s">
-        <v>322</v>
+      <c r="H107" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="I107" s="16" t="s">
+        <v>319</v>
       </c>
       <c r="J107" s="10" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="108" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -6037,20 +5762,20 @@
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
       <c r="G108" s="4"/>
-      <c r="H108" s="12" t="n">
-        <v>159</v>
-      </c>
-      <c r="I108" s="15" t="s">
-        <v>325</v>
+      <c r="H108" s="1" t="n">
+        <v>171</v>
+      </c>
+      <c r="I108" s="16" t="s">
+        <v>322</v>
       </c>
       <c r="J108" s="10" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="109" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -6058,92 +5783,81 @@
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
       <c r="G109" s="4"/>
-      <c r="H109" s="12" t="n">
-        <v>160</v>
-      </c>
-      <c r="I109" s="15" t="s">
-        <v>328</v>
+      <c r="H109" s="1" t="n">
+        <v>172</v>
+      </c>
+      <c r="I109" s="16" t="s">
+        <v>325</v>
       </c>
       <c r="J109" s="10" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="110" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="4"/>
-      <c r="B110" s="4" t="s">
-        <v>183</v>
-      </c>
+      <c r="B110" s="4"/>
       <c r="C110" s="4"/>
       <c r="D110" s="4"/>
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
       <c r="G110" s="4"/>
-      <c r="H110" s="12"/>
-      <c r="I110" s="4"/>
-      <c r="J110" s="4"/>
-      <c r="K110" s="4"/>
-    </row>
-    <row r="111" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="4" t="s">
-        <v>121</v>
-      </c>
+      <c r="H110" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="I110" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="J110" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="K110" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
       <c r="E111" s="4"/>
       <c r="F111" s="4"/>
       <c r="G111" s="4"/>
-      <c r="H111" s="12"/>
-      <c r="I111" s="4"/>
-      <c r="J111" s="4"/>
+      <c r="I111" s="7"/>
+      <c r="J111" s="10"/>
       <c r="K111" s="4"/>
     </row>
-    <row r="112" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="4"/>
-      <c r="B112" s="4"/>
+      <c r="B112" s="4" t="s">
+        <v>177</v>
+      </c>
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
       <c r="G112" s="4"/>
-      <c r="H112" s="12" t="n">
-        <v>161</v>
-      </c>
-      <c r="I112" s="16" t="s">
-        <v>331</v>
-      </c>
-      <c r="J112" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="K112" s="4" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="113" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="4"/>
+      <c r="I112" s="4"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="4"/>
+    </row>
+    <row r="113" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="4" t="s">
+        <v>120</v>
+      </c>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
       <c r="G113" s="4"/>
-      <c r="H113" s="12" t="n">
-        <v>162</v>
-      </c>
-      <c r="I113" s="15" t="s">
-        <v>334</v>
-      </c>
-      <c r="J113" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="K113" s="4" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="114" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I113" s="4"/>
+      <c r="J113" s="4"/>
+      <c r="K113" s="4"/>
+    </row>
+    <row r="114" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -6151,20 +5865,20 @@
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
-      <c r="H114" s="12" t="n">
-        <v>163</v>
-      </c>
-      <c r="I114" s="15" t="s">
-        <v>337</v>
+      <c r="H114" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="I114" s="17" t="s">
+        <v>331</v>
       </c>
       <c r="J114" s="10" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="115" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="115" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -6172,50 +5886,62 @@
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
       <c r="G115" s="4"/>
-      <c r="H115" s="12" t="n">
-        <v>164</v>
-      </c>
-      <c r="I115" s="15" t="s">
-        <v>340</v>
+      <c r="H115" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="I115" s="16" t="s">
+        <v>334</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="116" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="116" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="4"/>
-      <c r="B116" s="4" t="s">
-        <v>183</v>
-      </c>
+      <c r="B116" s="4"/>
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
       <c r="G116" s="4"/>
-      <c r="H116" s="12"/>
-      <c r="I116" s="4"/>
-      <c r="J116" s="4"/>
-      <c r="K116" s="4"/>
-    </row>
-    <row r="117" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="4" t="s">
-        <v>89</v>
-      </c>
+      <c r="H116" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="I116" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="J116" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="K116" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="117" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
       <c r="G117" s="4"/>
-      <c r="H117" s="12"/>
-      <c r="I117" s="4"/>
-      <c r="J117" s="4"/>
-      <c r="K117" s="4"/>
-    </row>
-    <row r="118" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H117" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="I117" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="J117" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="K117" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="118" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -6223,8 +5949,8 @@
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
       <c r="G118" s="4"/>
-      <c r="H118" s="12" t="n">
-        <v>165</v>
+      <c r="H118" s="1" t="n">
+        <v>159</v>
       </c>
       <c r="I118" s="16" t="s">
         <v>343</v>
@@ -6236,7 +5962,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="119" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -6244,92 +5970,90 @@
       <c r="E119" s="4"/>
       <c r="F119" s="4"/>
       <c r="G119" s="4"/>
-      <c r="H119" s="12" t="n">
-        <v>166</v>
+      <c r="H119" s="1" t="n">
+        <v>160</v>
       </c>
       <c r="I119" s="16" t="s">
-        <v>160</v>
+        <v>346</v>
       </c>
       <c r="J119" s="10" t="s">
-        <v>161</v>
+        <v>347</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="120" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="120" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="4"/>
-      <c r="B120" s="4"/>
+      <c r="B120" s="4" t="s">
+        <v>177</v>
+      </c>
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
       <c r="F120" s="4"/>
       <c r="G120" s="4"/>
-      <c r="H120" s="12" t="n">
-        <v>167</v>
-      </c>
-      <c r="I120" s="16" t="s">
-        <v>346</v>
-      </c>
-      <c r="J120" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="K120" s="4" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="121" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="4"/>
+      <c r="I120" s="4"/>
+      <c r="J120" s="4"/>
+      <c r="K120" s="4"/>
+    </row>
+    <row r="121" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="4" t="s">
+        <v>124</v>
+      </c>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
       <c r="F121" s="4"/>
       <c r="G121" s="4"/>
-      <c r="H121" s="12" t="n">
-        <v>168</v>
-      </c>
-      <c r="I121" s="15" t="s">
-        <v>349</v>
-      </c>
-      <c r="J121" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="K121" s="4" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="122" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I121" s="4"/>
+      <c r="J121" s="4"/>
+      <c r="K121" s="4"/>
+    </row>
+    <row r="122" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="4"/>
-      <c r="B122" s="4" t="s">
-        <v>183</v>
-      </c>
+      <c r="B122" s="4"/>
       <c r="C122" s="4"/>
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
       <c r="F122" s="4"/>
       <c r="G122" s="4"/>
-      <c r="H122" s="12"/>
-      <c r="I122" s="4"/>
-      <c r="J122" s="4"/>
-      <c r="K122" s="4"/>
-    </row>
-    <row r="123" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="4" t="s">
-        <v>77</v>
-      </c>
+      <c r="H122" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="I122" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="J122" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="K122" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="123" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
       <c r="F123" s="4"/>
       <c r="G123" s="4"/>
-      <c r="H123" s="12"/>
-      <c r="I123" s="4"/>
-      <c r="J123" s="4"/>
-      <c r="K123" s="4"/>
-    </row>
-    <row r="124" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H123" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="I123" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="J123" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="K123" s="4" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="124" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -6337,20 +6061,20 @@
       <c r="E124" s="4"/>
       <c r="F124" s="4"/>
       <c r="G124" s="4"/>
-      <c r="H124" s="12" t="n">
-        <v>116</v>
-      </c>
-      <c r="I124" s="15" t="s">
-        <v>352</v>
+      <c r="H124" s="1" t="n">
+        <v>163</v>
+      </c>
+      <c r="I124" s="16" t="s">
+        <v>355</v>
       </c>
       <c r="J124" s="10" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K124" s="4" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="125" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="125" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -6358,62 +6082,48 @@
       <c r="E125" s="4"/>
       <c r="F125" s="4"/>
       <c r="G125" s="4"/>
-      <c r="H125" s="12" t="n">
-        <v>117</v>
-      </c>
-      <c r="I125" s="15" t="s">
-        <v>355</v>
+      <c r="H125" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="I125" s="16" t="s">
+        <v>358</v>
       </c>
       <c r="J125" s="10" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="126" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="126" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="4"/>
-      <c r="B126" s="4"/>
+      <c r="B126" s="4" t="s">
+        <v>177</v>
+      </c>
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
       <c r="F126" s="4"/>
       <c r="G126" s="4"/>
-      <c r="H126" s="12" t="n">
-        <v>118</v>
-      </c>
-      <c r="I126" s="15" t="s">
-        <v>358</v>
-      </c>
-      <c r="J126" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="K126" s="4" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="127" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="4"/>
+      <c r="I126" s="4"/>
+      <c r="J126" s="4"/>
+      <c r="K126" s="4"/>
+    </row>
+    <row r="127" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="4" t="s">
+        <v>89</v>
+      </c>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
       <c r="F127" s="4"/>
       <c r="G127" s="4"/>
-      <c r="H127" s="12" t="n">
-        <v>119</v>
-      </c>
-      <c r="I127" s="15" t="s">
-        <v>361</v>
-      </c>
-      <c r="J127" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="K127" s="4" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="128" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I127" s="4"/>
+      <c r="J127" s="4"/>
+      <c r="K127" s="4"/>
+    </row>
+    <row r="128" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -6421,35 +6131,41 @@
       <c r="E128" s="4"/>
       <c r="F128" s="4"/>
       <c r="G128" s="4"/>
-      <c r="H128" s="12" t="n">
-        <v>120</v>
-      </c>
-      <c r="I128" s="15" t="s">
-        <v>364</v>
+      <c r="H128" s="1" t="n">
+        <v>165</v>
+      </c>
+      <c r="I128" s="17" t="s">
+        <v>361</v>
       </c>
       <c r="J128" s="10" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="K128" s="4" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="129" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="129" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="4"/>
-      <c r="B129" s="4" t="s">
-        <v>183</v>
-      </c>
+      <c r="B129" s="4"/>
       <c r="C129" s="4"/>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
       <c r="F129" s="4"/>
       <c r="G129" s="4"/>
-      <c r="H129" s="12"/>
-      <c r="I129" s="4"/>
-      <c r="J129" s="4"/>
-      <c r="K129" s="4"/>
-    </row>
-    <row r="130" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H129" s="1" t="n">
+        <v>166</v>
+      </c>
+      <c r="I129" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="J129" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="K129" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="130" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -6457,69 +6173,69 @@
       <c r="E130" s="4"/>
       <c r="F130" s="4"/>
       <c r="G130" s="4"/>
-      <c r="H130" s="12"/>
-      <c r="I130" s="4"/>
-      <c r="J130" s="4"/>
-      <c r="K130" s="4"/>
-    </row>
-    <row r="131" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="4" t="s">
-        <v>81</v>
-      </c>
+      <c r="H130" s="1" t="n">
+        <v>167</v>
+      </c>
+      <c r="I130" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="J130" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="K130" s="4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="131" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
       <c r="D131" s="4"/>
       <c r="E131" s="4"/>
       <c r="F131" s="4"/>
       <c r="G131" s="4"/>
-      <c r="H131" s="12"/>
-      <c r="I131" s="4"/>
-      <c r="J131" s="4"/>
-      <c r="K131" s="4"/>
-    </row>
-    <row r="132" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H131" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="I131" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="J131" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="K131" s="4" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="132" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="4"/>
-      <c r="B132" s="4"/>
+      <c r="B132" s="4" t="s">
+        <v>177</v>
+      </c>
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
       <c r="E132" s="4"/>
       <c r="F132" s="4"/>
       <c r="G132" s="4"/>
-      <c r="H132" s="12" t="n">
-        <v>121</v>
-      </c>
-      <c r="I132" s="15" t="s">
-        <v>367</v>
-      </c>
-      <c r="J132" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="K132" s="4" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="133" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="4"/>
+      <c r="I132" s="4"/>
+      <c r="J132" s="4"/>
+      <c r="K132" s="4"/>
+    </row>
+    <row r="133" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
       <c r="F133" s="4"/>
       <c r="G133" s="4"/>
-      <c r="H133" s="12" t="n">
-        <v>122</v>
-      </c>
-      <c r="I133" s="15" t="s">
-        <v>370</v>
-      </c>
-      <c r="J133" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="K133" s="4" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="134" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I133" s="4"/>
+      <c r="J133" s="4"/>
+      <c r="K133" s="4"/>
+    </row>
+    <row r="134" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -6527,20 +6243,20 @@
       <c r="E134" s="4"/>
       <c r="F134" s="4"/>
       <c r="G134" s="4"/>
-      <c r="H134" s="12" t="n">
-        <v>123</v>
-      </c>
-      <c r="I134" s="15" t="s">
-        <v>373</v>
-      </c>
-      <c r="J134" s="4" t="s">
-        <v>374</v>
+      <c r="H134" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="I134" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="J134" s="10" t="s">
+        <v>371</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="135" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="135" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -6548,20 +6264,20 @@
       <c r="E135" s="4"/>
       <c r="F135" s="4"/>
       <c r="G135" s="4"/>
-      <c r="H135" s="12" t="n">
-        <v>124</v>
-      </c>
-      <c r="I135" s="15" t="s">
-        <v>376</v>
-      </c>
-      <c r="J135" s="4" t="s">
-        <v>377</v>
+      <c r="H135" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="I135" s="16" t="s">
+        <v>373</v>
+      </c>
+      <c r="J135" s="10" t="s">
+        <v>374</v>
       </c>
       <c r="K135" s="4" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="136" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="136" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -6569,20 +6285,20 @@
       <c r="E136" s="4"/>
       <c r="F136" s="4"/>
       <c r="G136" s="4"/>
-      <c r="H136" s="12" t="n">
-        <v>125</v>
-      </c>
-      <c r="I136" s="15" t="s">
-        <v>379</v>
-      </c>
-      <c r="J136" s="4" t="s">
-        <v>380</v>
+      <c r="H136" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="I136" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="J136" s="10" t="s">
+        <v>377</v>
       </c>
       <c r="K136" s="4" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="137" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="137" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -6590,20 +6306,20 @@
       <c r="E137" s="4"/>
       <c r="F137" s="4"/>
       <c r="G137" s="4"/>
-      <c r="H137" s="12" t="n">
-        <v>126</v>
-      </c>
-      <c r="I137" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="J137" s="4" t="s">
-        <v>383</v>
+      <c r="H137" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="I137" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="J137" s="10" t="s">
+        <v>380</v>
       </c>
       <c r="K137" s="4" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="138" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="138" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -6611,22 +6327,29 @@
       <c r="E138" s="4"/>
       <c r="F138" s="4"/>
       <c r="G138" s="4"/>
-      <c r="H138" s="12"/>
-      <c r="I138" s="4"/>
-      <c r="J138" s="4"/>
-      <c r="K138" s="4"/>
+      <c r="H138" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="I138" s="16" t="s">
+        <v>382</v>
+      </c>
+      <c r="J138" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="K138" s="4" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="139" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="4"/>
       <c r="B139" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C139" s="4"/>
       <c r="D139" s="4"/>
       <c r="E139" s="4"/>
       <c r="F139" s="4"/>
       <c r="G139" s="4"/>
-      <c r="H139" s="12"/>
       <c r="I139" s="4"/>
       <c r="J139" s="4"/>
       <c r="K139" s="4"/>
@@ -6639,14 +6362,13 @@
       <c r="E140" s="4"/>
       <c r="F140" s="4"/>
       <c r="G140" s="4"/>
-      <c r="H140" s="12"/>
       <c r="I140" s="4"/>
       <c r="J140" s="4"/>
       <c r="K140" s="4"/>
     </row>
-    <row r="141" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -6654,12 +6376,11 @@
       <c r="E141" s="4"/>
       <c r="F141" s="4"/>
       <c r="G141" s="4"/>
-      <c r="H141" s="12"/>
       <c r="I141" s="4"/>
       <c r="J141" s="4"/>
       <c r="K141" s="4"/>
     </row>
-    <row r="142" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -6667,10 +6388,10 @@
       <c r="E142" s="4"/>
       <c r="F142" s="4"/>
       <c r="G142" s="4"/>
-      <c r="H142" s="12" t="n">
-        <v>127</v>
-      </c>
-      <c r="I142" s="15" t="s">
+      <c r="H142" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="I142" s="16" t="s">
         <v>385</v>
       </c>
       <c r="J142" s="10" t="s">
@@ -6680,76 +6401,70 @@
         <v>387</v>
       </c>
     </row>
-    <row r="143" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
-      <c r="C143" s="4" t="s">
-        <v>388</v>
-      </c>
+      <c r="C143" s="4"/>
       <c r="D143" s="4"/>
       <c r="E143" s="4"/>
       <c r="F143" s="4"/>
       <c r="G143" s="4"/>
-      <c r="H143" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="I143" s="15" t="s">
+      <c r="H143" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="I143" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="J143" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="J143" s="10" t="s">
+      <c r="K143" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="K143" s="17" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="144" s="1" customFormat="true" ht="24.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="144" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
-      <c r="C144" s="4" t="s">
-        <v>392</v>
-      </c>
+      <c r="C144" s="4"/>
       <c r="D144" s="4"/>
       <c r="E144" s="4"/>
       <c r="F144" s="4"/>
       <c r="G144" s="4"/>
-      <c r="H144" s="12" t="n">
-        <v>231</v>
-      </c>
-      <c r="I144" s="15" t="s">
+      <c r="H144" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="I144" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="J144" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="K144" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="J144" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="K144" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="145" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="145" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
-      <c r="C145" s="4" t="s">
-        <v>392</v>
-      </c>
+      <c r="C145" s="4"/>
       <c r="D145" s="4"/>
       <c r="E145" s="4"/>
       <c r="F145" s="4"/>
       <c r="G145" s="4"/>
-      <c r="H145" s="12" t="n">
-        <v>232</v>
-      </c>
-      <c r="I145" s="15" t="s">
+      <c r="H145" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="I145" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="J145" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="K145" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="J145" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="K145" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="146" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="146" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -6757,20 +6472,20 @@
       <c r="E146" s="4"/>
       <c r="F146" s="4"/>
       <c r="G146" s="4"/>
-      <c r="H146" s="12" t="n">
-        <v>128</v>
-      </c>
-      <c r="I146" s="18" t="s">
+      <c r="H146" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="I146" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="J146" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="K146" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="J146" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="K146" s="4" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="147" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="147" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -6778,76 +6493,72 @@
       <c r="E147" s="4"/>
       <c r="F147" s="4"/>
       <c r="G147" s="4"/>
-      <c r="H147" s="12"/>
-      <c r="I147" s="4"/>
-      <c r="J147" s="4"/>
-      <c r="K147" s="4"/>
+      <c r="H147" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="I147" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="J147" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="K147" s="4" t="s">
+        <v>402</v>
+      </c>
     </row>
     <row r="148" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="4"/>
-      <c r="B148" s="4" t="s">
-        <v>183</v>
-      </c>
+      <c r="B148" s="4"/>
       <c r="C148" s="4"/>
       <c r="D148" s="4"/>
       <c r="E148" s="4"/>
       <c r="F148" s="4"/>
       <c r="G148" s="4"/>
-      <c r="H148" s="12"/>
       <c r="I148" s="4"/>
       <c r="J148" s="4"/>
       <c r="K148" s="4"/>
     </row>
     <row r="149" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="4"/>
-      <c r="B149" s="4"/>
+      <c r="B149" s="4" t="s">
+        <v>177</v>
+      </c>
       <c r="C149" s="4"/>
       <c r="D149" s="4"/>
       <c r="E149" s="4"/>
       <c r="F149" s="4"/>
       <c r="G149" s="4"/>
-      <c r="H149" s="12"/>
       <c r="I149" s="4"/>
       <c r="J149" s="4"/>
       <c r="K149" s="4"/>
     </row>
     <row r="150" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="4" t="s">
-        <v>125</v>
-      </c>
+      <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
       <c r="D150" s="4"/>
       <c r="E150" s="4"/>
       <c r="F150" s="4"/>
       <c r="G150" s="4"/>
-      <c r="H150" s="12"/>
       <c r="I150" s="4"/>
       <c r="J150" s="4"/>
       <c r="K150" s="4"/>
     </row>
-    <row r="151" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="4"/>
+    <row r="151" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="4" t="s">
+        <v>85</v>
+      </c>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
       <c r="D151" s="4"/>
       <c r="E151" s="4"/>
       <c r="F151" s="4"/>
       <c r="G151" s="4"/>
-      <c r="H151" s="12" t="n">
-        <v>129</v>
-      </c>
-      <c r="I151" s="15" t="s">
-        <v>402</v>
-      </c>
-      <c r="J151" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="K151" s="4" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="152" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I151" s="4"/>
+      <c r="J151" s="4"/>
+      <c r="K151" s="4"/>
+    </row>
+    <row r="152" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -6855,83 +6566,89 @@
       <c r="E152" s="4"/>
       <c r="F152" s="4"/>
       <c r="G152" s="4"/>
-      <c r="H152" s="12" t="n">
-        <v>130</v>
-      </c>
-      <c r="I152" s="15" t="s">
+      <c r="H152" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="I152" s="16" t="s">
+        <v>403</v>
+      </c>
+      <c r="J152" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="K152" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="J152" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="K152" s="4" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="153" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="153" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
-      <c r="C153" s="4"/>
+      <c r="C153" s="4" t="s">
+        <v>406</v>
+      </c>
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
       <c r="F153" s="4"/>
       <c r="G153" s="4"/>
-      <c r="H153" s="12" t="n">
-        <v>131</v>
-      </c>
-      <c r="I153" s="15" t="s">
+      <c r="H153" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="I153" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="J153" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="J153" s="4" t="s">
+      <c r="K153" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="K153" s="4" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="154" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="154" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
-      <c r="C154" s="4"/>
+      <c r="C154" s="4" t="s">
+        <v>410</v>
+      </c>
       <c r="D154" s="4"/>
       <c r="E154" s="4"/>
       <c r="F154" s="4"/>
       <c r="G154" s="4"/>
-      <c r="H154" s="12" t="n">
-        <v>132</v>
-      </c>
-      <c r="I154" s="15" t="s">
+      <c r="H154" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="I154" s="16" t="s">
         <v>411</v>
       </c>
-      <c r="J154" s="4" t="s">
+      <c r="J154" s="10" t="s">
         <v>412</v>
       </c>
       <c r="K154" s="4" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="155" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
-      <c r="C155" s="4"/>
+      <c r="C155" s="4" t="s">
+        <v>410</v>
+      </c>
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
       <c r="F155" s="4"/>
       <c r="G155" s="4"/>
-      <c r="H155" s="12" t="n">
-        <v>133</v>
-      </c>
-      <c r="I155" s="15" t="s">
+      <c r="H155" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="I155" s="16" t="s">
         <v>414</v>
       </c>
-      <c r="J155" s="4" t="s">
+      <c r="J155" s="10" t="s">
         <v>415</v>
       </c>
       <c r="K155" s="4" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="156" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -6939,10 +6656,10 @@
       <c r="E156" s="4"/>
       <c r="F156" s="4"/>
       <c r="G156" s="4"/>
-      <c r="H156" s="12" t="n">
-        <v>134</v>
-      </c>
-      <c r="I156" s="15" t="s">
+      <c r="H156" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="I156" s="18" t="s">
         <v>417</v>
       </c>
       <c r="J156" s="4" t="s">
@@ -6952,7 +6669,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="157" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -6960,84 +6677,72 @@
       <c r="E157" s="4"/>
       <c r="F157" s="4"/>
       <c r="G157" s="4"/>
-      <c r="H157" s="12" t="n">
-        <v>135</v>
-      </c>
-      <c r="I157" s="18" t="s">
-        <v>420</v>
-      </c>
-      <c r="J157" s="4" t="s">
-        <v>421</v>
-      </c>
-      <c r="K157" s="4" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="158" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I157" s="4"/>
+      <c r="J157" s="4"/>
+      <c r="K157" s="4"/>
+    </row>
+    <row r="158" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="4"/>
-      <c r="B158" s="4"/>
+      <c r="B158" s="4" t="s">
+        <v>177</v>
+      </c>
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
       <c r="F158" s="4"/>
       <c r="G158" s="4"/>
-      <c r="H158" s="12" t="n">
-        <v>136</v>
-      </c>
-      <c r="I158" s="18" t="s">
-        <v>423</v>
-      </c>
-      <c r="J158" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="K158" s="4" t="s">
-        <v>425</v>
-      </c>
+      <c r="I158" s="4"/>
+      <c r="J158" s="4"/>
+      <c r="K158" s="4"/>
     </row>
     <row r="159" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="4"/>
-      <c r="B159" s="4" t="s">
-        <v>183</v>
-      </c>
+      <c r="B159" s="4"/>
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
       <c r="F159" s="4"/>
       <c r="G159" s="4"/>
-      <c r="H159" s="12"/>
       <c r="I159" s="4"/>
       <c r="J159" s="4"/>
       <c r="K159" s="4"/>
     </row>
     <row r="160" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="4"/>
+      <c r="A160" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
       <c r="F160" s="4"/>
       <c r="G160" s="4"/>
-      <c r="H160" s="12"/>
       <c r="I160" s="4"/>
       <c r="J160" s="4"/>
       <c r="K160" s="4"/>
     </row>
-    <row r="161" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="4" t="s">
-        <v>21</v>
-      </c>
+    <row r="161" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
       <c r="F161" s="4"/>
       <c r="G161" s="4"/>
-      <c r="H161" s="12"/>
-      <c r="I161" s="4"/>
-      <c r="J161" s="4"/>
-      <c r="K161" s="4"/>
-    </row>
-    <row r="162" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H161" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="I161" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="J161" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="K161" s="4" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="162" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -7045,20 +6750,20 @@
       <c r="E162" s="4"/>
       <c r="F162" s="4"/>
       <c r="G162" s="4"/>
-      <c r="H162" s="12" t="n">
-        <v>137</v>
-      </c>
-      <c r="I162" s="15" t="s">
-        <v>426</v>
-      </c>
-      <c r="J162" s="10" t="s">
-        <v>427</v>
+      <c r="H162" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="I162" s="16" t="s">
+        <v>423</v>
+      </c>
+      <c r="J162" s="4" t="s">
+        <v>424</v>
       </c>
       <c r="K162" s="4" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="163" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="163" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -7066,20 +6771,20 @@
       <c r="E163" s="4"/>
       <c r="F163" s="4"/>
       <c r="G163" s="4"/>
-      <c r="H163" s="12" t="n">
-        <v>138</v>
-      </c>
-      <c r="I163" s="15" t="s">
-        <v>429</v>
-      </c>
-      <c r="J163" s="10" t="s">
-        <v>430</v>
+      <c r="H163" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="I163" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="J163" s="4" t="s">
+        <v>427</v>
       </c>
       <c r="K163" s="4" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="164" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="164" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -7087,20 +6792,20 @@
       <c r="E164" s="4"/>
       <c r="F164" s="4"/>
       <c r="G164" s="4"/>
-      <c r="H164" s="12" t="n">
-        <v>139</v>
-      </c>
-      <c r="I164" s="15" t="s">
-        <v>432</v>
-      </c>
-      <c r="J164" s="10" t="s">
-        <v>433</v>
+      <c r="H164" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="I164" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="J164" s="4" t="s">
+        <v>430</v>
       </c>
       <c r="K164" s="4" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="165" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="165" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -7108,20 +6813,20 @@
       <c r="E165" s="4"/>
       <c r="F165" s="4"/>
       <c r="G165" s="4"/>
-      <c r="H165" s="12" t="n">
-        <v>140</v>
-      </c>
-      <c r="I165" s="15" t="s">
-        <v>435</v>
-      </c>
-      <c r="J165" s="10" t="s">
-        <v>436</v>
+      <c r="H165" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="I165" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="J165" s="4" t="s">
+        <v>433</v>
       </c>
       <c r="K165" s="4" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="166" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="166" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -7129,20 +6834,20 @@
       <c r="E166" s="4"/>
       <c r="F166" s="4"/>
       <c r="G166" s="4"/>
-      <c r="H166" s="12" t="n">
-        <v>141</v>
-      </c>
-      <c r="I166" s="15" t="s">
-        <v>438</v>
-      </c>
-      <c r="J166" s="10" t="s">
-        <v>439</v>
+      <c r="H166" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="I166" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="J166" s="4" t="s">
+        <v>436</v>
       </c>
       <c r="K166" s="4" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="167" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="167" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -7150,50 +6855,55 @@
       <c r="E167" s="4"/>
       <c r="F167" s="4"/>
       <c r="G167" s="4"/>
-      <c r="H167" s="12" t="n">
-        <v>142</v>
-      </c>
-      <c r="I167" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="J167" s="10" t="s">
-        <v>442</v>
+      <c r="H167" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="I167" s="18" t="s">
+        <v>438</v>
+      </c>
+      <c r="J167" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="K167" s="4" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="168" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="168" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="4"/>
-      <c r="B168" s="4" t="s">
-        <v>183</v>
-      </c>
+      <c r="B168" s="4"/>
       <c r="C168" s="4"/>
       <c r="D168" s="4"/>
       <c r="E168" s="4"/>
       <c r="F168" s="4"/>
       <c r="G168" s="4"/>
-      <c r="H168" s="12"/>
-      <c r="I168" s="4"/>
-      <c r="J168" s="4"/>
-      <c r="K168" s="4"/>
+      <c r="H168" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="I168" s="18" t="s">
+        <v>441</v>
+      </c>
+      <c r="J168" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="K168" s="4" t="s">
+        <v>443</v>
+      </c>
     </row>
     <row r="169" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B169" s="4"/>
+      <c r="A169" s="4"/>
+      <c r="B169" s="4" t="s">
+        <v>177</v>
+      </c>
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
       <c r="F169" s="4"/>
       <c r="G169" s="4"/>
-      <c r="H169" s="12"/>
       <c r="I169" s="4"/>
       <c r="J169" s="4"/>
       <c r="K169" s="4"/>
     </row>
-    <row r="170" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
@@ -7201,41 +6911,25 @@
       <c r="E170" s="4"/>
       <c r="F170" s="4"/>
       <c r="G170" s="4"/>
-      <c r="H170" s="12" t="n">
-        <v>143</v>
-      </c>
-      <c r="I170" s="15" t="s">
-        <v>444</v>
-      </c>
-      <c r="J170" s="10" t="s">
-        <v>445</v>
-      </c>
-      <c r="K170" s="4" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="171" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="4"/>
+      <c r="I170" s="4"/>
+      <c r="J170" s="4"/>
+      <c r="K170" s="4"/>
+    </row>
+    <row r="171" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
       <c r="D171" s="4"/>
       <c r="E171" s="4"/>
       <c r="F171" s="4"/>
       <c r="G171" s="4"/>
-      <c r="H171" s="12" t="n">
-        <v>144</v>
-      </c>
-      <c r="I171" s="15" t="s">
-        <v>447</v>
-      </c>
-      <c r="J171" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="K171" s="4" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="172" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I171" s="4"/>
+      <c r="J171" s="4"/>
+      <c r="K171" s="4"/>
+    </row>
+    <row r="172" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -7243,20 +6937,20 @@
       <c r="E172" s="4"/>
       <c r="F172" s="4"/>
       <c r="G172" s="4"/>
-      <c r="H172" s="12" t="n">
-        <v>145</v>
-      </c>
-      <c r="I172" s="15" t="s">
-        <v>450</v>
-      </c>
-      <c r="J172" s="4" t="s">
-        <v>451</v>
+      <c r="H172" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="I172" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="J172" s="10" t="s">
+        <v>445</v>
       </c>
       <c r="K172" s="4" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="173" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="173" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -7264,20 +6958,20 @@
       <c r="E173" s="4"/>
       <c r="F173" s="4"/>
       <c r="G173" s="4"/>
-      <c r="H173" s="12" t="n">
-        <v>146</v>
-      </c>
-      <c r="I173" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="J173" s="4" t="s">
-        <v>454</v>
+      <c r="H173" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="I173" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="J173" s="10" t="s">
+        <v>448</v>
       </c>
       <c r="K173" s="4" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="174" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="174" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -7285,20 +6979,20 @@
       <c r="E174" s="4"/>
       <c r="F174" s="4"/>
       <c r="G174" s="4"/>
-      <c r="H174" s="12" t="n">
-        <v>147</v>
-      </c>
-      <c r="I174" s="15" t="s">
-        <v>456</v>
-      </c>
-      <c r="J174" s="4" t="s">
-        <v>457</v>
+      <c r="H174" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="I174" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="J174" s="10" t="s">
+        <v>451</v>
       </c>
       <c r="K174" s="4" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="175" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="175" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -7306,12 +7000,20 @@
       <c r="E175" s="4"/>
       <c r="F175" s="4"/>
       <c r="G175" s="4"/>
-      <c r="H175" s="12"/>
-      <c r="I175" s="4"/>
-      <c r="J175" s="4"/>
-      <c r="K175" s="4"/>
-    </row>
-    <row r="176" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H175" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="I175" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="J175" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="K175" s="4" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="176" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -7319,63 +7021,69 @@
       <c r="E176" s="4"/>
       <c r="F176" s="4"/>
       <c r="G176" s="4"/>
-      <c r="H176" s="12"/>
-      <c r="I176" s="4"/>
-      <c r="J176" s="4"/>
-      <c r="K176" s="4"/>
-    </row>
-    <row r="177" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H176" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="I176" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="J176" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="K176" s="4" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="177" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="4"/>
-      <c r="B177" s="4" t="s">
-        <v>183</v>
-      </c>
+      <c r="B177" s="4"/>
       <c r="C177" s="4"/>
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
       <c r="F177" s="4"/>
       <c r="G177" s="4"/>
-      <c r="H177" s="12"/>
-      <c r="I177" s="4"/>
-      <c r="J177" s="4"/>
-      <c r="K177" s="4"/>
+      <c r="H177" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="I177" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="J177" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="K177" s="4" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="178" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B178" s="4"/>
+      <c r="A178" s="4"/>
+      <c r="B178" s="4" t="s">
+        <v>177</v>
+      </c>
       <c r="C178" s="4"/>
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
       <c r="F178" s="4"/>
       <c r="G178" s="4"/>
-      <c r="H178" s="12"/>
       <c r="I178" s="4"/>
       <c r="J178" s="4"/>
       <c r="K178" s="4"/>
     </row>
     <row r="179" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="4"/>
+      <c r="A179" s="4" t="s">
+        <v>116</v>
+      </c>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
       <c r="D179" s="4"/>
       <c r="E179" s="4"/>
       <c r="F179" s="4"/>
       <c r="G179" s="4"/>
-      <c r="H179" s="12" t="n">
-        <v>148</v>
-      </c>
-      <c r="I179" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="J179" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="K179" s="4" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="180" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I179" s="4"/>
+      <c r="J179" s="4"/>
+      <c r="K179" s="4"/>
+    </row>
+    <row r="180" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -7383,20 +7091,20 @@
       <c r="E180" s="4"/>
       <c r="F180" s="4"/>
       <c r="G180" s="4"/>
-      <c r="H180" s="12" t="n">
-        <v>149</v>
-      </c>
-      <c r="I180" s="4" t="s">
+      <c r="H180" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="I180" s="16" t="s">
         <v>462</v>
       </c>
-      <c r="J180" s="4" t="s">
+      <c r="J180" s="10" t="s">
         <v>463</v>
       </c>
       <c r="K180" s="4" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="181" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -7404,10 +7112,10 @@
       <c r="E181" s="4"/>
       <c r="F181" s="4"/>
       <c r="G181" s="4"/>
-      <c r="H181" s="12" t="n">
-        <v>150</v>
-      </c>
-      <c r="I181" s="4" t="s">
+      <c r="H181" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="I181" s="16" t="s">
         <v>465</v>
       </c>
       <c r="J181" s="4" t="s">
@@ -7417,7 +7125,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="182" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -7425,10 +7133,10 @@
       <c r="E182" s="4"/>
       <c r="F182" s="4"/>
       <c r="G182" s="4"/>
-      <c r="H182" s="12" t="n">
-        <v>151</v>
-      </c>
-      <c r="I182" s="4" t="s">
+      <c r="H182" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="I182" s="16" t="s">
         <v>468</v>
       </c>
       <c r="J182" s="4" t="s">
@@ -7438,7 +7146,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="183" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -7446,10 +7154,10 @@
       <c r="E183" s="4"/>
       <c r="F183" s="4"/>
       <c r="G183" s="4"/>
-      <c r="H183" s="12" t="n">
-        <v>152</v>
-      </c>
-      <c r="I183" s="4" t="s">
+      <c r="H183" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="I183" s="16" t="s">
         <v>471</v>
       </c>
       <c r="J183" s="4" t="s">
@@ -7459,7 +7167,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="184" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" s="1" customFormat="true" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -7467,10 +7175,10 @@
       <c r="E184" s="4"/>
       <c r="F184" s="4"/>
       <c r="G184" s="4"/>
-      <c r="H184" s="12" t="n">
-        <v>153</v>
-      </c>
-      <c r="I184" s="4" t="s">
+      <c r="H184" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="I184" s="16" t="s">
         <v>474</v>
       </c>
       <c r="J184" s="4" t="s">
@@ -7480,7 +7188,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -7488,106 +7196,102 @@
       <c r="E185" s="4"/>
       <c r="F185" s="4"/>
       <c r="G185" s="4"/>
-      <c r="H185" s="12" t="n">
-        <v>154</v>
-      </c>
-      <c r="I185" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="J185" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="K185" s="4" t="s">
-        <v>479</v>
-      </c>
+      <c r="I185" s="4"/>
+      <c r="J185" s="4"/>
+      <c r="K185" s="4"/>
     </row>
     <row r="186" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="4"/>
-      <c r="B186" s="4" t="s">
-        <v>183</v>
-      </c>
+      <c r="B186" s="4"/>
       <c r="C186" s="4"/>
       <c r="D186" s="4"/>
       <c r="E186" s="4"/>
       <c r="F186" s="4"/>
       <c r="G186" s="4"/>
-      <c r="H186" s="12"/>
       <c r="I186" s="4"/>
       <c r="J186" s="4"/>
       <c r="K186" s="4"/>
     </row>
     <row r="187" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="12"/>
-      <c r="B187" s="4"/>
-      <c r="C187" s="12"/>
-      <c r="D187" s="12"/>
-      <c r="E187" s="12"/>
-      <c r="F187" s="12"/>
-      <c r="G187" s="12"/>
-      <c r="H187" s="12"/>
-      <c r="I187" s="12"/>
-      <c r="J187" s="12"/>
-      <c r="K187" s="12"/>
+      <c r="A187" s="4"/>
+      <c r="B187" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C187" s="4"/>
+      <c r="D187" s="4"/>
+      <c r="E187" s="4"/>
+      <c r="F187" s="4"/>
+      <c r="G187" s="4"/>
+      <c r="I187" s="4"/>
+      <c r="J187" s="4"/>
+      <c r="K187" s="4"/>
     </row>
     <row r="188" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B188" s="12"/>
-      <c r="C188" s="12"/>
-      <c r="D188" s="12"/>
-      <c r="E188" s="12"/>
-      <c r="F188" s="12"/>
-      <c r="G188" s="12"/>
-      <c r="H188" s="12"/>
-      <c r="I188" s="12"/>
-      <c r="J188" s="12"/>
-      <c r="K188" s="12"/>
+        <v>49</v>
+      </c>
+      <c r="B188" s="4"/>
+      <c r="C188" s="4"/>
+      <c r="D188" s="4"/>
+      <c r="E188" s="4"/>
+      <c r="F188" s="4"/>
+      <c r="G188" s="4"/>
+      <c r="I188" s="4"/>
+      <c r="J188" s="4"/>
+      <c r="K188" s="4"/>
     </row>
     <row r="189" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="12"/>
-      <c r="B189" s="12"/>
-      <c r="C189" s="12"/>
-      <c r="D189" s="12"/>
-      <c r="E189" s="12"/>
-      <c r="F189" s="12"/>
-      <c r="G189" s="12"/>
-      <c r="H189" s="12"/>
-      <c r="I189" s="12"/>
-      <c r="J189" s="12"/>
-      <c r="K189" s="12"/>
+      <c r="A189" s="4"/>
+      <c r="B189" s="4"/>
+      <c r="C189" s="4"/>
+      <c r="D189" s="4"/>
+      <c r="E189" s="4"/>
+      <c r="F189" s="4"/>
+      <c r="G189" s="4"/>
+      <c r="H189" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="I189" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="J189" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="K189" s="4" t="s">
+        <v>479</v>
+      </c>
     </row>
     <row r="190" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="12"/>
-      <c r="B190" s="12"/>
-      <c r="C190" s="12"/>
-      <c r="D190" s="12"/>
-      <c r="E190" s="12"/>
-      <c r="F190" s="12"/>
-      <c r="G190" s="12"/>
-      <c r="H190" s="12" t="n">
-        <v>105</v>
+      <c r="A190" s="4"/>
+      <c r="B190" s="4"/>
+      <c r="C190" s="4"/>
+      <c r="D190" s="4"/>
+      <c r="E190" s="4"/>
+      <c r="F190" s="4"/>
+      <c r="G190" s="4"/>
+      <c r="H190" s="1" t="n">
+        <v>149</v>
       </c>
       <c r="I190" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="J190" s="10" t="s">
+      <c r="J190" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="K190" s="12" t="s">
+      <c r="K190" s="4" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="191" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="12"/>
-      <c r="B191" s="12"/>
-      <c r="C191" s="12"/>
-      <c r="D191" s="12"/>
-      <c r="E191" s="12"/>
-      <c r="F191" s="12"/>
-      <c r="G191" s="12"/>
-      <c r="H191" s="12" t="n">
-        <v>106</v>
+    <row r="191" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="4"/>
+      <c r="B191" s="4"/>
+      <c r="C191" s="4"/>
+      <c r="D191" s="4"/>
+      <c r="E191" s="4"/>
+      <c r="F191" s="4"/>
+      <c r="G191" s="4"/>
+      <c r="H191" s="1" t="n">
+        <v>150</v>
       </c>
       <c r="I191" s="4" t="s">
         <v>483</v>
@@ -7595,20 +7299,20 @@
       <c r="J191" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="K191" s="12" t="s">
+      <c r="K191" s="4" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="192" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="12"/>
-      <c r="B192" s="12"/>
-      <c r="C192" s="12"/>
-      <c r="D192" s="12"/>
-      <c r="E192" s="12"/>
-      <c r="F192" s="12"/>
-      <c r="G192" s="12"/>
-      <c r="H192" s="12" t="n">
-        <v>107</v>
+    <row r="192" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="4"/>
+      <c r="B192" s="4"/>
+      <c r="C192" s="4"/>
+      <c r="D192" s="4"/>
+      <c r="E192" s="4"/>
+      <c r="F192" s="4"/>
+      <c r="G192" s="4"/>
+      <c r="H192" s="1" t="n">
+        <v>151</v>
       </c>
       <c r="I192" s="4" t="s">
         <v>486</v>
@@ -7616,20 +7320,20 @@
       <c r="J192" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="K192" s="12" t="s">
+      <c r="K192" s="4" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="193" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="12"/>
-      <c r="B193" s="12"/>
-      <c r="C193" s="12"/>
-      <c r="D193" s="12"/>
-      <c r="E193" s="12"/>
-      <c r="F193" s="12"/>
-      <c r="G193" s="12"/>
-      <c r="H193" s="12" t="n">
-        <v>108</v>
+    <row r="193" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="4"/>
+      <c r="B193" s="4"/>
+      <c r="C193" s="4"/>
+      <c r="D193" s="4"/>
+      <c r="E193" s="4"/>
+      <c r="F193" s="4"/>
+      <c r="G193" s="4"/>
+      <c r="H193" s="1" t="n">
+        <v>152</v>
       </c>
       <c r="I193" s="4" t="s">
         <v>489</v>
@@ -7637,20 +7341,20 @@
       <c r="J193" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="K193" s="12" t="s">
+      <c r="K193" s="4" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="194" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="12"/>
-      <c r="B194" s="12"/>
-      <c r="C194" s="12"/>
-      <c r="D194" s="12"/>
-      <c r="E194" s="12"/>
-      <c r="F194" s="12"/>
-      <c r="G194" s="12"/>
-      <c r="H194" s="12" t="n">
-        <v>109</v>
+    <row r="194" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="4"/>
+      <c r="B194" s="4"/>
+      <c r="C194" s="4"/>
+      <c r="D194" s="4"/>
+      <c r="E194" s="4"/>
+      <c r="F194" s="4"/>
+      <c r="G194" s="4"/>
+      <c r="H194" s="1" t="n">
+        <v>153</v>
       </c>
       <c r="I194" s="4" t="s">
         <v>492</v>
@@ -7658,238 +7362,146 @@
       <c r="J194" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="K194" s="12" t="s">
+      <c r="K194" s="4" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="195" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="12"/>
-      <c r="B195" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C195" s="12"/>
-      <c r="D195" s="12"/>
-      <c r="E195" s="12"/>
-      <c r="F195" s="12"/>
-      <c r="G195" s="12"/>
-      <c r="H195" s="12"/>
-      <c r="I195" s="12"/>
-      <c r="J195" s="12"/>
-      <c r="K195" s="12"/>
+    <row r="195" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="4"/>
+      <c r="B195" s="4"/>
+      <c r="C195" s="4"/>
+      <c r="D195" s="4"/>
+      <c r="E195" s="4"/>
+      <c r="F195" s="4"/>
+      <c r="G195" s="4"/>
+      <c r="H195" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="I195" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="J195" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="K195" s="4" t="s">
+        <v>497</v>
+      </c>
     </row>
     <row r="196" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="4" t="s">
+      <c r="A196" s="4"/>
+      <c r="B196" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C196" s="4"/>
+      <c r="D196" s="4"/>
+      <c r="E196" s="4"/>
+      <c r="F196" s="4"/>
+      <c r="G196" s="4"/>
+      <c r="I196" s="4"/>
+      <c r="J196" s="4"/>
+      <c r="K196" s="4"/>
+    </row>
+    <row r="197" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B197" s="4"/>
+      <c r="K197" s="14"/>
+    </row>
+    <row r="198" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K198" s="14"/>
+    </row>
+    <row r="199" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K199" s="14"/>
+    </row>
+    <row r="200" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H200" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="I200" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="J200" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="K200" s="14" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="201" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H201" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="I201" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="J201" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="K201" s="14" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="202" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H202" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="I202" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="J202" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="K202" s="14" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="203" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H203" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="I203" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="J203" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="K203" s="14" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="204" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H204" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="I204" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="J204" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="K204" s="14" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="205" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B205" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K205" s="14"/>
+    </row>
+    <row r="206" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B196" s="12"/>
-      <c r="C196" s="12"/>
-      <c r="D196" s="12"/>
-      <c r="E196" s="12"/>
-      <c r="F196" s="12"/>
-      <c r="G196" s="12"/>
-      <c r="H196" s="12"/>
-      <c r="I196" s="12"/>
-      <c r="J196" s="12"/>
-      <c r="K196" s="12"/>
-    </row>
-    <row r="197" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="12"/>
-      <c r="B197" s="12"/>
-      <c r="C197" s="12"/>
-      <c r="D197" s="12"/>
-      <c r="E197" s="12"/>
-      <c r="F197" s="12"/>
-      <c r="G197" s="12"/>
-      <c r="H197" s="12"/>
-      <c r="I197" s="12"/>
-      <c r="J197" s="12"/>
-      <c r="K197" s="12"/>
-    </row>
-    <row r="198" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="12"/>
-      <c r="B198" s="12"/>
-      <c r="C198" s="12"/>
-      <c r="D198" s="12"/>
-      <c r="E198" s="12"/>
-      <c r="F198" s="12"/>
-      <c r="G198" s="12"/>
-      <c r="H198" s="12" t="n">
+      <c r="K206" s="14"/>
+    </row>
+    <row r="207" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K207" s="14"/>
+    </row>
+    <row r="208" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H208" s="1" t="n">
         <v>110</v>
-      </c>
-      <c r="I198" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="J198" s="10" t="s">
-        <v>496</v>
-      </c>
-      <c r="K198" s="12" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="199" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="12"/>
-      <c r="B199" s="12"/>
-      <c r="C199" s="12"/>
-      <c r="D199" s="12"/>
-      <c r="E199" s="12"/>
-      <c r="F199" s="12"/>
-      <c r="G199" s="12"/>
-      <c r="H199" s="12" t="n">
-        <v>111</v>
-      </c>
-      <c r="I199" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="J199" s="10" t="s">
-        <v>499</v>
-      </c>
-      <c r="K199" s="12" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="200" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="12"/>
-      <c r="B200" s="12"/>
-      <c r="C200" s="12"/>
-      <c r="D200" s="12"/>
-      <c r="E200" s="12"/>
-      <c r="F200" s="12"/>
-      <c r="G200" s="12"/>
-      <c r="H200" s="12" t="n">
-        <v>112</v>
-      </c>
-      <c r="I200" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="J200" s="10" t="s">
-        <v>502</v>
-      </c>
-      <c r="K200" s="12" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="201" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="12"/>
-      <c r="B201" s="12"/>
-      <c r="C201" s="12"/>
-      <c r="D201" s="12"/>
-      <c r="E201" s="12"/>
-      <c r="F201" s="12"/>
-      <c r="G201" s="12"/>
-      <c r="H201" s="12" t="n">
-        <v>113</v>
-      </c>
-      <c r="I201" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="J201" s="10" t="s">
-        <v>505</v>
-      </c>
-      <c r="K201" s="12" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="202" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="12"/>
-      <c r="B202" s="12"/>
-      <c r="C202" s="12"/>
-      <c r="D202" s="12"/>
-      <c r="E202" s="12"/>
-      <c r="F202" s="12"/>
-      <c r="G202" s="12"/>
-      <c r="H202" s="12" t="n">
-        <v>114</v>
-      </c>
-      <c r="I202" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="J202" s="10" t="s">
-        <v>508</v>
-      </c>
-      <c r="K202" s="12" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="203" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H203" s="12" t="n">
-        <v>115</v>
-      </c>
-      <c r="I203" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="J203" s="10" t="s">
-        <v>511</v>
-      </c>
-      <c r="K203" s="12" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="204" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="12"/>
-      <c r="B204" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C204" s="12"/>
-      <c r="D204" s="12"/>
-      <c r="E204" s="12"/>
-      <c r="F204" s="12"/>
-      <c r="G204" s="12"/>
-      <c r="H204" s="12"/>
-      <c r="I204" s="12"/>
-      <c r="J204" s="12"/>
-      <c r="K204" s="12"/>
-    </row>
-    <row r="205" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="12"/>
-      <c r="B205" s="4"/>
-      <c r="C205" s="12"/>
-      <c r="D205" s="12"/>
-      <c r="E205" s="12"/>
-      <c r="F205" s="12"/>
-      <c r="G205" s="12"/>
-      <c r="H205" s="12"/>
-      <c r="I205" s="12"/>
-      <c r="J205" s="12"/>
-      <c r="K205" s="12"/>
-    </row>
-    <row r="206" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B206" s="12"/>
-      <c r="C206" s="12"/>
-      <c r="D206" s="12"/>
-      <c r="E206" s="12"/>
-      <c r="F206" s="12"/>
-      <c r="G206" s="12"/>
-      <c r="H206" s="12"/>
-      <c r="I206" s="12"/>
-      <c r="J206" s="12"/>
-      <c r="K206" s="12"/>
-    </row>
-    <row r="207" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="12"/>
-      <c r="B207" s="12"/>
-      <c r="C207" s="12"/>
-      <c r="D207" s="12"/>
-      <c r="E207" s="12"/>
-      <c r="F207" s="12"/>
-      <c r="G207" s="12"/>
-      <c r="H207" s="12"/>
-      <c r="I207" s="12"/>
-      <c r="J207" s="12"/>
-      <c r="K207" s="12"/>
-    </row>
-    <row r="208" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="12"/>
-      <c r="B208" s="12"/>
-      <c r="C208" s="12"/>
-      <c r="D208" s="12"/>
-      <c r="E208" s="12"/>
-      <c r="F208" s="12"/>
-      <c r="G208" s="12"/>
-      <c r="H208" s="12" t="n">
-        <v>26</v>
       </c>
       <c r="I208" s="4" t="s">
         <v>513</v>
@@ -7897,551 +7509,408 @@
       <c r="J208" s="10" t="s">
         <v>514</v>
       </c>
-      <c r="K208" s="12" t="s">
+      <c r="K208" s="14" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="209" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="12"/>
-      <c r="B209" s="12"/>
-      <c r="C209" s="12"/>
-      <c r="D209" s="12"/>
-      <c r="E209" s="12"/>
-      <c r="F209" s="12"/>
-      <c r="G209" s="12"/>
-      <c r="H209" s="12" t="n">
-        <v>27</v>
+    <row r="209" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H209" s="1" t="n">
+        <v>111</v>
       </c>
       <c r="I209" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="J209" s="4" t="s">
+      <c r="J209" s="10" t="s">
         <v>517</v>
       </c>
-      <c r="K209" s="12" t="s">
+      <c r="K209" s="14" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="210" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="12"/>
-      <c r="B210" s="12"/>
-      <c r="C210" s="12"/>
-      <c r="D210" s="12"/>
-      <c r="E210" s="12"/>
-      <c r="F210" s="12"/>
-      <c r="G210" s="12"/>
-      <c r="H210" s="12" t="n">
-        <v>28</v>
+    <row r="210" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H210" s="1" t="n">
+        <v>112</v>
       </c>
       <c r="I210" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="J210" s="4" t="s">
+      <c r="J210" s="10" t="s">
         <v>520</v>
       </c>
-      <c r="K210" s="12" t="s">
+      <c r="K210" s="14" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="211" s="1" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="12"/>
-      <c r="B211" s="12"/>
-      <c r="C211" s="12"/>
-      <c r="D211" s="12"/>
-      <c r="E211" s="12"/>
-      <c r="F211" s="12"/>
-      <c r="G211" s="12"/>
-      <c r="H211" s="12" t="n">
-        <v>29</v>
+    <row r="211" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H211" s="1" t="n">
+        <v>113</v>
       </c>
       <c r="I211" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="J211" s="4" t="s">
+      <c r="J211" s="10" t="s">
         <v>523</v>
       </c>
-      <c r="K211" s="12" t="s">
+      <c r="K211" s="14" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="212" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="12"/>
-      <c r="B212" s="12"/>
-      <c r="C212" s="12"/>
-      <c r="D212" s="12"/>
-      <c r="E212" s="12"/>
-      <c r="F212" s="12"/>
-      <c r="G212" s="12"/>
-      <c r="H212" s="12" t="n">
-        <v>30</v>
+    <row r="212" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H212" s="1" t="n">
+        <v>114</v>
       </c>
       <c r="I212" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="J212" s="4" t="s">
+      <c r="J212" s="10" t="s">
         <v>526</v>
       </c>
-      <c r="K212" s="12" t="s">
+      <c r="K212" s="14" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="213" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="12"/>
-      <c r="B213" s="12"/>
-      <c r="C213" s="12"/>
-      <c r="D213" s="12"/>
-      <c r="E213" s="12"/>
-      <c r="F213" s="12"/>
-      <c r="G213" s="12"/>
-      <c r="H213" s="12" t="n">
-        <v>31</v>
+    <row r="213" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H213" s="1" t="n">
+        <v>115</v>
       </c>
       <c r="I213" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="J213" s="4" t="s">
+      <c r="J213" s="10" t="s">
         <v>529</v>
       </c>
-      <c r="K213" s="12" t="s">
+      <c r="K213" s="14" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="214" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="12"/>
-      <c r="B214" s="12"/>
-      <c r="C214" s="12"/>
-      <c r="D214" s="12"/>
-      <c r="E214" s="12"/>
-      <c r="F214" s="12"/>
-      <c r="G214" s="12"/>
-      <c r="H214" s="12" t="n">
+      <c r="B214" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K214" s="14"/>
+    </row>
+    <row r="215" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B215" s="4"/>
+      <c r="K215" s="14"/>
+    </row>
+    <row r="216" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K216" s="14"/>
+    </row>
+    <row r="217" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K217" s="14"/>
+    </row>
+    <row r="218" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H218" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="I218" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="J218" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="K218" s="14" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="219" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H219" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="I219" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="J219" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="K219" s="14" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="220" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H220" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="I220" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="J220" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="K220" s="14" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="221" s="1" customFormat="true" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H221" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="I221" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="J221" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="K221" s="14" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="222" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H222" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="I222" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="J222" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="K222" s="14" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="223" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H223" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I223" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="J223" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="K223" s="14" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="224" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H224" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="I214" s="4" t="s">
+      <c r="I224" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="J214" s="4" t="s">
+      <c r="J224" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="K214" s="12" t="s">
+      <c r="K224" s="14" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="215" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="12"/>
-      <c r="B215" s="12"/>
-      <c r="C215" s="12"/>
-      <c r="D215" s="12"/>
-      <c r="E215" s="12"/>
-      <c r="F215" s="12"/>
-      <c r="G215" s="12"/>
-      <c r="H215" s="12" t="n">
+    <row r="225" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H225" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="I215" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="J215" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="K215" s="12" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H216" s="12" t="n">
+      <c r="I225" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="J225" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="K225" s="14" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H226" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="I216" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="J216" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="K216" s="12" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B217" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="K217" s="12"/>
-    </row>
-    <row r="218" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="219" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="220" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="12" t="s">
+      <c r="I226" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="J226" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="K226" s="14" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B227" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K227" s="14"/>
+    </row>
+    <row r="228" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="229" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="230" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H223" s="12" t="n">
+    <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H233" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="I223" s="4" t="s">
-        <v>537</v>
-      </c>
-      <c r="J223" s="10" t="s">
-        <v>538</v>
-      </c>
-      <c r="K223" s="13" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B224" s="12" t="s">
-        <v>540</v>
-      </c>
-      <c r="D224" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="H224" s="12" t="n">
+      <c r="I233" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="J233" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="K233" s="12" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B234" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="H234" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="I224" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="J224" s="10" t="s">
-        <v>543</v>
-      </c>
-      <c r="K224" s="13" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B225" s="12" t="s">
-        <v>545</v>
-      </c>
-      <c r="D225" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="H225" s="12" t="n">
+      <c r="I234" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="J234" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="K234" s="12" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B235" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="H235" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="I225" s="4" t="s">
-        <v>546</v>
-      </c>
-      <c r="J225" s="10" t="s">
-        <v>547</v>
-      </c>
-      <c r="K225" s="13" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I226" s="4"/>
-      <c r="J226" s="10"/>
-    </row>
-    <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="12" t="s">
-        <v>540</v>
-      </c>
-      <c r="I227" s="4"/>
-      <c r="J227" s="10"/>
-    </row>
-    <row r="228" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H228" s="12" t="n">
+      <c r="I235" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="J235" s="10" t="s">
+        <v>565</v>
+      </c>
+      <c r="K235" s="12" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I236" s="4"/>
+      <c r="J236" s="10"/>
+    </row>
+    <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="I237" s="4"/>
+      <c r="J237" s="10"/>
+    </row>
+    <row r="238" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H238" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="I228" s="4" t="s">
-        <v>549</v>
-      </c>
-      <c r="J228" s="4" t="s">
-        <v>550</v>
-      </c>
-      <c r="K228" s="13" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="229" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="12"/>
-      <c r="B229" s="12"/>
-      <c r="C229" s="12"/>
-      <c r="D229" s="12"/>
-      <c r="E229" s="12"/>
-      <c r="F229" s="12"/>
-      <c r="G229" s="12"/>
-      <c r="H229" s="12" t="n">
+      <c r="I238" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="J238" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="K238" s="12" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="239" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H239" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="I229" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="J229" s="4" t="s">
-        <v>553</v>
-      </c>
-      <c r="K229" s="12" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="230" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H230" s="12" t="n">
+      <c r="I239" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="J239" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="K239" s="14" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H240" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="I230" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="J230" s="4" t="s">
-        <v>556</v>
-      </c>
-      <c r="K230" s="13" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="231" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H231" s="12" t="n">
+      <c r="I240" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="J240" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="K240" s="12" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H241" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="I231" s="4" t="s">
-        <v>558</v>
-      </c>
-      <c r="J231" s="4" t="s">
-        <v>559</v>
-      </c>
-      <c r="K231" s="12" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="232" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H232" s="12" t="n">
+      <c r="I241" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="J241" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="K241" s="14" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H242" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="I232" s="4" t="s">
-        <v>561</v>
-      </c>
-      <c r="J232" s="4" t="s">
-        <v>562</v>
-      </c>
-      <c r="K232" s="13" t="s">
+      <c r="I242" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="J242" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="K242" s="12" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H243" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="I243" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="J243" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="K243" s="12" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B244" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J244" s="4"/>
+    </row>
+    <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="1" t="s">
         <v>563</v>
       </c>
-    </row>
-    <row r="233" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H233" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="I233" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="J233" s="4" t="s">
-        <v>565</v>
-      </c>
-      <c r="K233" s="13" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B234" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="J234" s="4"/>
-    </row>
-    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="12" t="s">
-        <v>545</v>
-      </c>
-      <c r="J235" s="4"/>
-    </row>
-    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H236" s="12" t="n">
+      <c r="J245" s="4"/>
+    </row>
+    <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H246" s="1" t="n">
         <v>44</v>
-      </c>
-      <c r="I236" s="4" t="s">
-        <v>567</v>
-      </c>
-      <c r="J236" s="10" t="s">
-        <v>568</v>
-      </c>
-      <c r="K236" s="13" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="237" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="12"/>
-      <c r="B237" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="C237" s="12"/>
-      <c r="D237" s="12"/>
-      <c r="E237" s="12"/>
-      <c r="F237" s="12"/>
-      <c r="G237" s="12"/>
-      <c r="H237" s="12"/>
-      <c r="I237" s="12"/>
-      <c r="J237" s="12"/>
-      <c r="K237" s="12"/>
-    </row>
-    <row r="238" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="12"/>
-      <c r="B238" s="12"/>
-      <c r="C238" s="12"/>
-      <c r="D238" s="12"/>
-      <c r="E238" s="12"/>
-      <c r="F238" s="12"/>
-      <c r="G238" s="12"/>
-      <c r="H238" s="12"/>
-      <c r="I238" s="12"/>
-      <c r="J238" s="12"/>
-      <c r="K238" s="12"/>
-    </row>
-    <row r="239" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B239" s="12"/>
-      <c r="C239" s="12"/>
-      <c r="D239" s="12"/>
-      <c r="E239" s="12"/>
-      <c r="F239" s="12"/>
-      <c r="G239" s="12"/>
-      <c r="H239" s="12"/>
-      <c r="I239" s="12"/>
-      <c r="J239" s="12"/>
-      <c r="K239" s="12"/>
-    </row>
-    <row r="240" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="12"/>
-      <c r="B240" s="12"/>
-      <c r="C240" s="12"/>
-      <c r="D240" s="12"/>
-      <c r="E240" s="12"/>
-      <c r="F240" s="12"/>
-      <c r="G240" s="12"/>
-      <c r="H240" s="12" t="n">
-        <v>93</v>
-      </c>
-      <c r="I240" s="4" t="s">
-        <v>570</v>
-      </c>
-      <c r="J240" s="10" t="s">
-        <v>571</v>
-      </c>
-      <c r="K240" s="12" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="241" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="12"/>
-      <c r="B241" s="12"/>
-      <c r="C241" s="12"/>
-      <c r="D241" s="12"/>
-      <c r="E241" s="12"/>
-      <c r="F241" s="12"/>
-      <c r="G241" s="12"/>
-      <c r="H241" s="12" t="n">
-        <v>94</v>
-      </c>
-      <c r="I241" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="J241" s="4" t="s">
-        <v>574</v>
-      </c>
-      <c r="K241" s="12" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="242" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="12"/>
-      <c r="B242" s="12"/>
-      <c r="C242" s="12"/>
-      <c r="D242" s="12"/>
-      <c r="E242" s="12"/>
-      <c r="F242" s="12"/>
-      <c r="G242" s="12"/>
-      <c r="H242" s="12" t="n">
-        <v>95</v>
-      </c>
-      <c r="I242" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="J242" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="K242" s="12" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="243" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="12"/>
-      <c r="B243" s="12"/>
-      <c r="C243" s="12"/>
-      <c r="D243" s="12"/>
-      <c r="E243" s="12"/>
-      <c r="F243" s="12"/>
-      <c r="G243" s="12"/>
-      <c r="H243" s="12" t="n">
-        <v>96</v>
-      </c>
-      <c r="I243" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="J243" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="K243" s="12" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="244" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="12"/>
-      <c r="B244" s="12"/>
-      <c r="C244" s="12"/>
-      <c r="D244" s="12"/>
-      <c r="E244" s="12"/>
-      <c r="F244" s="12"/>
-      <c r="G244" s="12"/>
-      <c r="H244" s="12" t="n">
-        <v>97</v>
-      </c>
-      <c r="I244" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="J244" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="K244" s="12" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="245" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="12"/>
-      <c r="B245" s="12"/>
-      <c r="C245" s="12"/>
-      <c r="D245" s="12"/>
-      <c r="E245" s="12"/>
-      <c r="F245" s="12"/>
-      <c r="G245" s="12"/>
-      <c r="H245" s="12" t="n">
-        <v>98</v>
-      </c>
-      <c r="I245" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="J245" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="K245" s="12" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="246" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="12"/>
-      <c r="B246" s="12"/>
-      <c r="C246" s="12"/>
-      <c r="D246" s="12"/>
-      <c r="E246" s="12"/>
-      <c r="F246" s="12"/>
-      <c r="G246" s="12"/>
-      <c r="H246" s="12" t="n">
-        <v>99</v>
       </c>
       <c r="I246" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J246" s="4" t="s">
+      <c r="J246" s="10" t="s">
         <v>586</v>
       </c>
       <c r="K246" s="12" t="s">
@@ -8449,58 +7918,23 @@
       </c>
     </row>
     <row r="247" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="12"/>
-      <c r="B247" s="12"/>
-      <c r="C247" s="12"/>
-      <c r="D247" s="12"/>
-      <c r="E247" s="12"/>
-      <c r="F247" s="12"/>
-      <c r="G247" s="12"/>
-      <c r="H247" s="12"/>
-      <c r="I247" s="4"/>
-      <c r="J247" s="4"/>
-      <c r="K247" s="12"/>
+      <c r="B247" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K247" s="14"/>
     </row>
     <row r="248" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="12"/>
-      <c r="B248" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C248" s="12"/>
-      <c r="D248" s="12"/>
-      <c r="E248" s="12"/>
-      <c r="F248" s="12"/>
-      <c r="G248" s="12"/>
-      <c r="H248" s="12"/>
-      <c r="I248" s="12"/>
-      <c r="J248" s="12"/>
-      <c r="K248" s="12"/>
+      <c r="K248" s="14"/>
     </row>
     <row r="249" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B249" s="12"/>
-      <c r="C249" s="12"/>
-      <c r="D249" s="12"/>
-      <c r="E249" s="12"/>
-      <c r="F249" s="12"/>
-      <c r="G249" s="12"/>
-      <c r="H249" s="12"/>
-      <c r="I249" s="12"/>
-      <c r="J249" s="12"/>
-      <c r="K249" s="12"/>
-    </row>
-    <row r="250" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="12"/>
-      <c r="B250" s="12"/>
-      <c r="C250" s="12"/>
-      <c r="D250" s="12"/>
-      <c r="E250" s="12"/>
-      <c r="F250" s="12"/>
-      <c r="G250" s="12"/>
-      <c r="H250" s="12" t="n">
         <v>100</v>
+      </c>
+      <c r="K249" s="14"/>
+    </row>
+    <row r="250" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H250" s="1" t="n">
+        <v>93</v>
       </c>
       <c r="I250" s="4" t="s">
         <v>588</v>
@@ -8508,20 +7942,13 @@
       <c r="J250" s="10" t="s">
         <v>589</v>
       </c>
-      <c r="K250" s="12" t="s">
+      <c r="K250" s="14" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="251" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="12"/>
-      <c r="B251" s="12"/>
-      <c r="C251" s="12"/>
-      <c r="D251" s="12"/>
-      <c r="E251" s="12"/>
-      <c r="F251" s="12"/>
-      <c r="G251" s="12"/>
-      <c r="H251" s="12" t="n">
-        <v>101</v>
+    <row r="251" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H251" s="1" t="n">
+        <v>94</v>
       </c>
       <c r="I251" s="4" t="s">
         <v>591</v>
@@ -8529,20 +7956,13 @@
       <c r="J251" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="K251" s="12" t="s">
+      <c r="K251" s="14" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="252" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="12"/>
-      <c r="B252" s="12"/>
-      <c r="C252" s="12"/>
-      <c r="D252" s="12"/>
-      <c r="E252" s="12"/>
-      <c r="F252" s="12"/>
-      <c r="G252" s="12"/>
-      <c r="H252" s="12" t="n">
-        <v>102</v>
+    <row r="252" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H252" s="1" t="n">
+        <v>95</v>
       </c>
       <c r="I252" s="4" t="s">
         <v>594</v>
@@ -8550,20 +7970,13 @@
       <c r="J252" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="K252" s="12" t="s">
+      <c r="K252" s="14" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="253" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="12"/>
-      <c r="B253" s="12"/>
-      <c r="C253" s="12"/>
-      <c r="D253" s="12"/>
-      <c r="E253" s="12"/>
-      <c r="F253" s="12"/>
-      <c r="G253" s="12"/>
-      <c r="H253" s="12" t="n">
-        <v>103</v>
+    <row r="253" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H253" s="1" t="n">
+        <v>96</v>
       </c>
       <c r="I253" s="4" t="s">
         <v>597</v>
@@ -8571,237 +7984,163 @@
       <c r="J253" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="K253" s="12" t="s">
+      <c r="K253" s="14" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="254" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="12"/>
-      <c r="B254" s="12"/>
-      <c r="C254" s="12"/>
-      <c r="D254" s="12"/>
-      <c r="E254" s="12"/>
-      <c r="F254" s="12"/>
-      <c r="G254" s="12"/>
-      <c r="H254" s="12" t="n">
+      <c r="H254" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="I254" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="J254" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="K254" s="14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="255" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H255" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="I255" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="J255" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="K255" s="14" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="256" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H256" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="I256" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="J256" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="K256" s="14" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="257" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I257" s="4"/>
+      <c r="J257" s="4"/>
+      <c r="K257" s="14"/>
+    </row>
+    <row r="258" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B258" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K258" s="14"/>
+    </row>
+    <row r="259" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="I254" s="4" t="s">
-        <v>600</v>
-      </c>
-      <c r="J254" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="K254" s="12" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="255" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="12"/>
-      <c r="B255" s="12"/>
-      <c r="C255" s="12"/>
-      <c r="D255" s="12"/>
-      <c r="E255" s="12"/>
-      <c r="F255" s="12"/>
-      <c r="G255" s="12"/>
-      <c r="H255" s="12"/>
-      <c r="I255" s="4"/>
-      <c r="J255" s="4"/>
-      <c r="K255" s="12"/>
-    </row>
-    <row r="256" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="12"/>
-      <c r="B256" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C256" s="12"/>
-      <c r="D256" s="12"/>
-      <c r="E256" s="12"/>
-      <c r="F256" s="12"/>
-      <c r="G256" s="12"/>
-      <c r="H256" s="12"/>
-      <c r="I256" s="12"/>
-      <c r="J256" s="12"/>
-      <c r="K256" s="12"/>
-    </row>
-    <row r="257" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="12"/>
-      <c r="B257" s="4"/>
-      <c r="C257" s="12"/>
-      <c r="D257" s="12"/>
-      <c r="E257" s="12"/>
-      <c r="F257" s="12"/>
-      <c r="G257" s="12"/>
-      <c r="H257" s="12"/>
-      <c r="I257" s="12"/>
-      <c r="J257" s="12"/>
-      <c r="K257" s="12"/>
-    </row>
-    <row r="258" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B258" s="12"/>
-      <c r="C258" s="12"/>
-      <c r="D258" s="12"/>
-      <c r="E258" s="12"/>
-      <c r="F258" s="12"/>
-      <c r="G258" s="12"/>
-      <c r="H258" s="12"/>
-      <c r="I258" s="12"/>
-      <c r="J258" s="12"/>
-      <c r="K258" s="12"/>
-    </row>
-    <row r="259" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="12"/>
-      <c r="B259" s="12"/>
-      <c r="C259" s="12"/>
-      <c r="D259" s="12"/>
-      <c r="E259" s="12"/>
-      <c r="F259" s="12"/>
-      <c r="G259" s="12"/>
-      <c r="H259" s="12" t="n">
-        <v>79</v>
-      </c>
-      <c r="I259" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="J259" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="K259" s="12" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="260" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="12"/>
-      <c r="B260" s="12"/>
-      <c r="C260" s="12"/>
-      <c r="D260" s="12"/>
-      <c r="E260" s="12"/>
-      <c r="F260" s="12"/>
-      <c r="G260" s="12"/>
-      <c r="H260" s="12" t="n">
-        <v>80</v>
+      <c r="K259" s="14"/>
+    </row>
+    <row r="260" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H260" s="1" t="n">
+        <v>100</v>
       </c>
       <c r="I260" s="4" t="s">
-        <v>603</v>
-      </c>
-      <c r="J260" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="K260" s="12" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="261" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="12"/>
-      <c r="B261" s="12"/>
-      <c r="C261" s="12"/>
-      <c r="D261" s="12"/>
-      <c r="E261" s="12"/>
-      <c r="F261" s="12"/>
-      <c r="G261" s="12"/>
-      <c r="H261" s="12" t="n">
-        <v>81</v>
+        <v>606</v>
+      </c>
+      <c r="J260" s="10" t="s">
+        <v>607</v>
+      </c>
+      <c r="K260" s="14" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="261" s="1" customFormat="true" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H261" s="1" t="n">
+        <v>101</v>
       </c>
       <c r="I261" s="4" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="J261" s="4" t="s">
-        <v>607</v>
-      </c>
-      <c r="K261" s="12" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="262" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="12"/>
-      <c r="B262" s="12"/>
-      <c r="C262" s="12"/>
-      <c r="D262" s="12"/>
-      <c r="E262" s="12"/>
-      <c r="F262" s="12"/>
-      <c r="G262" s="12"/>
-      <c r="H262" s="12" t="n">
-        <v>82</v>
+        <v>610</v>
+      </c>
+      <c r="K261" s="14" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="262" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H262" s="1" t="n">
+        <v>102</v>
       </c>
       <c r="I262" s="4" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="J262" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="K262" s="12" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="263" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="12"/>
-      <c r="B263" s="12"/>
-      <c r="C263" s="12"/>
-      <c r="D263" s="12"/>
-      <c r="E263" s="12"/>
-      <c r="F263" s="12"/>
-      <c r="G263" s="12"/>
-      <c r="H263" s="12" t="n">
-        <v>83</v>
+        <v>613</v>
+      </c>
+      <c r="K262" s="14" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="263" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H263" s="1" t="n">
+        <v>103</v>
       </c>
       <c r="I263" s="4" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="J263" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="K263" s="12" t="s">
-        <v>614</v>
+        <v>616</v>
+      </c>
+      <c r="K263" s="14" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="264" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="12"/>
-      <c r="B264" s="12"/>
-      <c r="C264" s="12"/>
-      <c r="D264" s="12"/>
-      <c r="E264" s="12"/>
-      <c r="F264" s="12"/>
-      <c r="G264" s="12"/>
-      <c r="H264" s="12" t="n">
-        <v>84</v>
+      <c r="H264" s="1" t="n">
+        <v>104</v>
       </c>
       <c r="I264" s="4" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="J264" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="K264" s="12" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>619</v>
+      </c>
+      <c r="K264" s="14" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="265" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I265" s="4"/>
       <c r="J265" s="4"/>
-      <c r="K265" s="12"/>
-    </row>
-    <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K265" s="14"/>
+    </row>
+    <row r="266" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B266" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="K266" s="12"/>
-    </row>
-    <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>177</v>
+      </c>
+      <c r="K266" s="14"/>
+    </row>
+    <row r="267" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B267" s="4"/>
-      <c r="K267" s="12"/>
-    </row>
-    <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K267" s="14"/>
+    </row>
+    <row r="268" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="K268" s="12"/>
-    </row>
-    <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H269" s="12" t="n">
-        <v>85</v>
+        <v>57</v>
+      </c>
+      <c r="K268" s="14"/>
+    </row>
+    <row r="269" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H269" s="1" t="n">
+        <v>79</v>
       </c>
       <c r="I269" s="4" t="s">
         <v>160</v>
@@ -8809,617 +8148,447 @@
       <c r="J269" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="K269" s="12" t="s">
+      <c r="K269" s="14" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="270" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H270" s="12" t="n">
+    <row r="270" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H270" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="I270" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="J270" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="K270" s="14" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="271" s="1" customFormat="true" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H271" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="I271" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="J271" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="K271" s="14" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="272" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H272" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="I272" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="J272" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="K272" s="14" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="273" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H273" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="I273" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="J273" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="K273" s="14" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="274" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H274" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="I274" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="J274" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="K274" s="14" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I275" s="4"/>
+      <c r="J275" s="4"/>
+      <c r="K275" s="14"/>
+    </row>
+    <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B276" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K276" s="14"/>
+    </row>
+    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B277" s="4"/>
+      <c r="K277" s="14"/>
+    </row>
+    <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A278" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K278" s="14"/>
+    </row>
+    <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H279" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="I279" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="J279" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="K279" s="14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="280" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H280" s="1" t="n">
         <v>86</v>
       </c>
-      <c r="I270" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="J270" s="4" t="s">
-        <v>619</v>
-      </c>
-      <c r="K270" s="12" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="271" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H271" s="12" t="n">
+      <c r="I280" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="J280" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="K280" s="14" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="281" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H281" s="1" t="n">
         <v>87</v>
       </c>
-      <c r="I271" s="4" t="s">
-        <v>621</v>
-      </c>
-      <c r="J271" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="K271" s="12" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="272" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H272" s="12" t="n">
+      <c r="I281" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="J281" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="K281" s="14" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="282" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H282" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="I272" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="J272" s="4" t="s">
-        <v>625</v>
-      </c>
-      <c r="K272" s="12" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="273" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H273" s="12" t="n">
+      <c r="I282" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="J282" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="K282" s="14" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="283" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H283" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="I273" s="4" t="s">
-        <v>627</v>
-      </c>
-      <c r="J273" s="4" t="s">
-        <v>628</v>
-      </c>
-      <c r="K273" s="12" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="274" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H274" s="12" t="n">
+      <c r="I283" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="J283" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="K283" s="14" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="284" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H284" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="I274" s="4" t="s">
-        <v>630</v>
-      </c>
-      <c r="J274" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="K274" s="12" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="275" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H275" s="12" t="n">
+      <c r="I284" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="J284" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="K284" s="14" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="285" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H285" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="I275" s="4" t="s">
-        <v>633</v>
-      </c>
-      <c r="J275" s="4" t="s">
-        <v>634</v>
-      </c>
-      <c r="K275" s="12" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H276" s="12" t="n">
+      <c r="I285" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="J285" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="K285" s="14" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H286" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="I276" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="J276" s="4" t="s">
-        <v>636</v>
-      </c>
-      <c r="K276" s="12" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B277" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="K277" s="12"/>
-    </row>
-    <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A279" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="K279" s="12"/>
-    </row>
-    <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H280" s="12" t="n">
+      <c r="I286" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="J286" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="K286" s="14" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B287" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K287" s="14"/>
+    </row>
+    <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A289" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="K289" s="14"/>
+    </row>
+    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H290" s="1" t="n">
         <v>74</v>
       </c>
-      <c r="I280" s="4" t="s">
-        <v>638</v>
-      </c>
-      <c r="J280" s="10" t="s">
-        <v>639</v>
-      </c>
-      <c r="K280" s="12" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="281" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H281" s="12" t="n">
+      <c r="I290" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="J290" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="K290" s="14" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="291" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H291" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="I281" s="4" t="s">
-        <v>641</v>
-      </c>
-      <c r="J281" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="K281" s="12" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="282" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H282" s="12" t="n">
+      <c r="I291" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="J291" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K291" s="14" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="292" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H292" s="1" t="n">
         <v>76</v>
       </c>
-      <c r="I282" s="4" t="s">
-        <v>644</v>
-      </c>
-      <c r="J282" s="4" t="s">
-        <v>645</v>
-      </c>
-      <c r="K282" s="12" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="283" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H283" s="12" t="n">
+      <c r="I292" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="J292" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="K292" s="14" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="293" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H293" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="I283" s="4" t="s">
-        <v>647</v>
-      </c>
-      <c r="J283" s="4" t="s">
-        <v>648</v>
-      </c>
-      <c r="K283" s="12" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="284" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H284" s="12" t="n">
+      <c r="I293" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="J293" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="K293" s="14" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="294" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H294" s="1" t="n">
         <v>78</v>
       </c>
-      <c r="I284" s="4" t="s">
-        <v>650</v>
-      </c>
-      <c r="J284" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="K284" s="12" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I285" s="4"/>
-      <c r="J285" s="4"/>
-      <c r="K285" s="12"/>
-    </row>
-    <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I286" s="4"/>
-      <c r="J286" s="4"/>
-      <c r="K286" s="12"/>
-    </row>
-    <row r="287" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="12"/>
-      <c r="B287" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C287" s="12"/>
-      <c r="D287" s="12"/>
-      <c r="E287" s="12"/>
-      <c r="F287" s="12"/>
-      <c r="G287" s="12"/>
-      <c r="H287" s="12"/>
-      <c r="I287" s="12"/>
-      <c r="J287" s="12"/>
-      <c r="K287" s="12"/>
-    </row>
-    <row r="288" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="12"/>
-      <c r="B288" s="12"/>
-      <c r="C288" s="12"/>
-      <c r="D288" s="12"/>
-      <c r="E288" s="12"/>
-      <c r="F288" s="12"/>
-      <c r="G288" s="12"/>
-      <c r="H288" s="12"/>
-      <c r="I288" s="12"/>
-      <c r="J288" s="12"/>
-      <c r="K288" s="12"/>
-    </row>
-    <row r="289" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B289" s="12"/>
-      <c r="C289" s="12"/>
-      <c r="D289" s="12"/>
-      <c r="E289" s="12"/>
-      <c r="F289" s="12"/>
-      <c r="G289" s="12"/>
-      <c r="H289" s="12"/>
-      <c r="I289" s="12"/>
-      <c r="J289" s="12"/>
-      <c r="K289" s="12"/>
-    </row>
-    <row r="290" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="12"/>
-      <c r="B290" s="12"/>
-      <c r="C290" s="12"/>
-      <c r="D290" s="12"/>
-      <c r="E290" s="12"/>
-      <c r="F290" s="12"/>
-      <c r="G290" s="12"/>
-      <c r="H290" s="12" t="n">
-        <v>66</v>
-      </c>
-      <c r="I290" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="J290" s="10" t="s">
-        <v>654</v>
-      </c>
-      <c r="K290" s="12" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="291" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="12"/>
-      <c r="B291" s="12"/>
-      <c r="C291" s="12"/>
-      <c r="D291" s="12"/>
-      <c r="E291" s="12"/>
-      <c r="F291" s="12"/>
-      <c r="G291" s="12"/>
-      <c r="H291" s="12" t="n">
-        <v>67</v>
-      </c>
-      <c r="I291" s="4" t="s">
-        <v>656</v>
-      </c>
-      <c r="J291" s="4" t="s">
-        <v>657</v>
-      </c>
-      <c r="K291" s="12" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="292" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="12"/>
-      <c r="B292" s="12"/>
-      <c r="C292" s="12"/>
-      <c r="D292" s="12"/>
-      <c r="E292" s="12"/>
-      <c r="F292" s="12"/>
-      <c r="G292" s="12"/>
-      <c r="H292" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="I292" s="4" t="s">
-        <v>659</v>
-      </c>
-      <c r="J292" s="4" t="s">
-        <v>660</v>
-      </c>
-      <c r="K292" s="12" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="293" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="12"/>
-      <c r="B293" s="12"/>
-      <c r="C293" s="12"/>
-      <c r="D293" s="12"/>
-      <c r="E293" s="12"/>
-      <c r="F293" s="12"/>
-      <c r="G293" s="12"/>
-      <c r="H293" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="I293" s="4" t="s">
-        <v>662</v>
-      </c>
-      <c r="J293" s="4" t="s">
-        <v>663</v>
-      </c>
-      <c r="K293" s="12" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="294" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="12"/>
-      <c r="B294" s="12"/>
-      <c r="C294" s="12"/>
-      <c r="D294" s="12"/>
-      <c r="E294" s="12"/>
-      <c r="F294" s="12"/>
-      <c r="G294" s="12"/>
-      <c r="H294" s="12" t="n">
-        <v>70</v>
-      </c>
       <c r="I294" s="4" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="J294" s="4" t="s">
-        <v>666</v>
-      </c>
-      <c r="K294" s="12" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="295" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="12"/>
-      <c r="B295" s="12"/>
-      <c r="C295" s="12"/>
-      <c r="D295" s="12"/>
-      <c r="E295" s="12"/>
-      <c r="F295" s="12"/>
-      <c r="G295" s="12"/>
-      <c r="H295" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="I295" s="4" t="s">
-        <v>668</v>
-      </c>
-      <c r="J295" s="4" t="s">
         <v>669</v>
       </c>
-      <c r="K295" s="12" t="s">
+      <c r="K294" s="14" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="296" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A296" s="12"/>
-      <c r="B296" s="12"/>
-      <c r="C296" s="12"/>
-      <c r="D296" s="12"/>
-      <c r="E296" s="12"/>
-      <c r="F296" s="12"/>
-      <c r="G296" s="12"/>
-      <c r="H296" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="I296" s="4" t="s">
-        <v>671</v>
-      </c>
-      <c r="J296" s="4" t="s">
-        <v>672</v>
-      </c>
-      <c r="K296" s="12" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="297" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="12"/>
-      <c r="B297" s="12"/>
-      <c r="C297" s="12"/>
-      <c r="D297" s="12"/>
-      <c r="E297" s="12"/>
-      <c r="F297" s="12"/>
-      <c r="G297" s="12"/>
-      <c r="H297" s="12" t="n">
-        <v>73</v>
-      </c>
-      <c r="I297" s="4" t="s">
-        <v>674</v>
-      </c>
-      <c r="J297" s="4" t="s">
-        <v>675</v>
-      </c>
-      <c r="K297" s="12" t="s">
-        <v>676</v>
-      </c>
+    <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I295" s="4"/>
+      <c r="J295" s="4"/>
+      <c r="K295" s="14"/>
+    </row>
+    <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I296" s="4"/>
+      <c r="J296" s="4"/>
+      <c r="K296" s="14"/>
+    </row>
+    <row r="297" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B297" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K297" s="14"/>
     </row>
     <row r="298" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="12"/>
-      <c r="B298" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C298" s="12"/>
-      <c r="D298" s="12"/>
-      <c r="E298" s="12"/>
-      <c r="F298" s="12"/>
-      <c r="G298" s="12"/>
-      <c r="H298" s="12"/>
-      <c r="I298" s="12"/>
-      <c r="J298" s="12"/>
-      <c r="K298" s="12"/>
+      <c r="K298" s="14"/>
     </row>
     <row r="299" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B299" s="12"/>
-      <c r="C299" s="12"/>
-      <c r="D299" s="12"/>
-      <c r="E299" s="12"/>
-      <c r="F299" s="12"/>
-      <c r="G299" s="12"/>
-      <c r="H299" s="12"/>
-      <c r="I299" s="12"/>
-      <c r="J299" s="12"/>
-      <c r="K299" s="12"/>
-    </row>
-    <row r="300" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="12"/>
-      <c r="B300" s="12"/>
-      <c r="C300" s="12"/>
-      <c r="D300" s="12"/>
-      <c r="E300" s="12"/>
-      <c r="F300" s="12"/>
-      <c r="G300" s="12"/>
-      <c r="H300" s="12" t="n">
-        <v>60</v>
+        <v>73</v>
+      </c>
+      <c r="K299" s="14"/>
+    </row>
+    <row r="300" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H300" s="1" t="n">
+        <v>66</v>
       </c>
       <c r="I300" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="J300" s="10" t="s">
+        <v>672</v>
+      </c>
+      <c r="K300" s="14" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="301" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H301" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="I301" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="J301" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="K301" s="14" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="302" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H302" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="I302" s="4" t="s">
         <v>677</v>
       </c>
-      <c r="J300" s="10" t="s">
+      <c r="J302" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="K300" s="12" t="s">
+      <c r="K302" s="14" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="301" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A301" s="12"/>
-      <c r="B301" s="12"/>
-      <c r="C301" s="12"/>
-      <c r="D301" s="12"/>
-      <c r="E301" s="12"/>
-      <c r="F301" s="12"/>
-      <c r="G301" s="12"/>
-      <c r="H301" s="12" t="n">
-        <v>61</v>
-      </c>
-      <c r="I301" s="4" t="s">
+    <row r="303" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H303" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="I303" s="4" t="s">
         <v>680</v>
       </c>
-      <c r="J301" s="4" t="s">
+      <c r="J303" s="4" t="s">
         <v>681</v>
       </c>
-      <c r="K301" s="12" t="s">
+      <c r="K303" s="14" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="302" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="12"/>
-      <c r="B302" s="12"/>
-      <c r="C302" s="12"/>
-      <c r="D302" s="12"/>
-      <c r="E302" s="12"/>
-      <c r="F302" s="12"/>
-      <c r="G302" s="12"/>
-      <c r="H302" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="I302" s="4" t="s">
+    <row r="304" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H304" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="I304" s="4" t="s">
         <v>683</v>
       </c>
-      <c r="J302" s="4" t="s">
+      <c r="J304" s="4" t="s">
         <v>684</v>
       </c>
-      <c r="K302" s="12" t="s">
+      <c r="K304" s="14" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="303" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A303" s="12"/>
-      <c r="B303" s="12"/>
-      <c r="C303" s="12"/>
-      <c r="D303" s="12"/>
-      <c r="E303" s="12"/>
-      <c r="F303" s="12"/>
-      <c r="G303" s="12"/>
-      <c r="H303" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="I303" s="4" t="s">
+    <row r="305" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H305" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="I305" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="J303" s="4" t="s">
+      <c r="J305" s="4" t="s">
         <v>687</v>
       </c>
-      <c r="K303" s="12" t="s">
+      <c r="K305" s="14" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="304" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A304" s="12"/>
-      <c r="B304" s="12"/>
-      <c r="C304" s="12"/>
-      <c r="D304" s="12"/>
-      <c r="E304" s="12"/>
-      <c r="F304" s="12"/>
-      <c r="G304" s="12"/>
-      <c r="H304" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="I304" s="4" t="s">
+    <row r="306" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H306" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="I306" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="J304" s="4" t="s">
+      <c r="J306" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="K304" s="12" t="s">
+      <c r="K306" s="14" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="305" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H305" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="I305" s="4" t="s">
+    <row r="307" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H307" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="I307" s="4" t="s">
         <v>692</v>
       </c>
-      <c r="J305" s="4" t="s">
+      <c r="J307" s="4" t="s">
         <v>693</v>
       </c>
-      <c r="K305" s="12" t="s">
+      <c r="K307" s="14" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B306" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="K306" s="12"/>
-    </row>
-    <row r="307" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A307" s="12"/>
-      <c r="B307" s="12"/>
-      <c r="C307" s="12"/>
-      <c r="D307" s="12"/>
-      <c r="E307" s="12"/>
-      <c r="F307" s="12"/>
-      <c r="G307" s="12"/>
-      <c r="H307" s="12"/>
-      <c r="I307" s="12"/>
-      <c r="J307" s="12"/>
-      <c r="K307" s="12"/>
-    </row>
     <row r="308" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="12"/>
-      <c r="B308" s="12"/>
-      <c r="C308" s="12"/>
-      <c r="D308" s="12"/>
-      <c r="E308" s="12"/>
-      <c r="F308" s="12"/>
-      <c r="G308" s="12"/>
-      <c r="H308" s="12"/>
-      <c r="I308" s="12"/>
-      <c r="J308" s="12"/>
-      <c r="K308" s="12"/>
+      <c r="B308" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K308" s="14"/>
     </row>
     <row r="309" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B309" s="12"/>
-      <c r="C309" s="12"/>
-      <c r="D309" s="12"/>
-      <c r="E309" s="12"/>
-      <c r="F309" s="12"/>
-      <c r="G309" s="12"/>
-      <c r="H309" s="12"/>
-      <c r="I309" s="12"/>
-      <c r="J309" s="12"/>
-      <c r="K309" s="12"/>
-    </row>
-    <row r="310" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A310" s="12"/>
-      <c r="B310" s="12"/>
-      <c r="C310" s="12"/>
-      <c r="D310" s="12"/>
-      <c r="E310" s="12"/>
-      <c r="F310" s="12"/>
-      <c r="G310" s="12"/>
-      <c r="H310" s="12" t="n">
-        <v>53</v>
+        <v>65</v>
+      </c>
+      <c r="K309" s="14"/>
+    </row>
+    <row r="310" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H310" s="1" t="n">
+        <v>60</v>
       </c>
       <c r="I310" s="4" t="s">
         <v>695</v>
@@ -9427,373 +8596,231 @@
       <c r="J310" s="10" t="s">
         <v>696</v>
       </c>
-      <c r="K310" s="12" t="s">
+      <c r="K310" s="14" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="311" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A311" s="12"/>
-      <c r="B311" s="12"/>
-      <c r="C311" s="12"/>
-      <c r="D311" s="12"/>
-      <c r="E311" s="12"/>
-      <c r="F311" s="12"/>
-      <c r="G311" s="12"/>
-      <c r="H311" s="12" t="n">
-        <v>54</v>
+    <row r="311" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H311" s="1" t="n">
+        <v>61</v>
       </c>
       <c r="I311" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="J311" s="10" t="s">
+      <c r="J311" s="4" t="s">
         <v>699</v>
       </c>
-      <c r="K311" s="12" t="s">
+      <c r="K311" s="14" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="312" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="12"/>
-      <c r="B312" s="12"/>
-      <c r="C312" s="12"/>
-      <c r="D312" s="12"/>
-      <c r="E312" s="12"/>
-      <c r="F312" s="12"/>
-      <c r="G312" s="12"/>
-      <c r="H312" s="12" t="n">
-        <v>55</v>
+    <row r="312" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H312" s="1" t="n">
+        <v>62</v>
       </c>
       <c r="I312" s="4" t="s">
         <v>701</v>
       </c>
-      <c r="J312" s="10" t="s">
+      <c r="J312" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="K312" s="12" t="s">
+      <c r="K312" s="14" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="313" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A313" s="12"/>
-      <c r="B313" s="12"/>
-      <c r="C313" s="12"/>
-      <c r="D313" s="12"/>
-      <c r="E313" s="12"/>
-      <c r="F313" s="12"/>
-      <c r="G313" s="12"/>
-      <c r="H313" s="12" t="n">
-        <v>56</v>
+    <row r="313" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H313" s="1" t="n">
+        <v>63</v>
       </c>
       <c r="I313" s="4" t="s">
         <v>704</v>
       </c>
-      <c r="J313" s="10" t="s">
+      <c r="J313" s="4" t="s">
         <v>705</v>
       </c>
-      <c r="K313" s="12" t="s">
+      <c r="K313" s="14" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="314" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="12"/>
-      <c r="B314" s="12"/>
-      <c r="C314" s="12"/>
-      <c r="D314" s="12"/>
-      <c r="E314" s="12"/>
-      <c r="F314" s="12"/>
-      <c r="G314" s="12"/>
-      <c r="H314" s="12" t="n">
+    <row r="314" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H314" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="I314" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="J314" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="K314" s="14" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="315" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H315" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="I315" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="J315" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="K315" s="14" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B316" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K316" s="14"/>
+    </row>
+    <row r="317" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K317" s="14"/>
+    </row>
+    <row r="318" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K318" s="14"/>
+    </row>
+    <row r="319" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A319" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K319" s="14"/>
+    </row>
+    <row r="320" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H320" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="I320" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="J320" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="K320" s="14" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="321" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H321" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="I321" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="J321" s="10" t="s">
+        <v>717</v>
+      </c>
+      <c r="K321" s="14" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="322" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H322" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="I322" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="J322" s="10" t="s">
+        <v>720</v>
+      </c>
+      <c r="K322" s="14" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="323" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H323" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="I323" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="J323" s="10" t="s">
+        <v>723</v>
+      </c>
+      <c r="K323" s="14" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="324" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H324" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="I314" s="4" t="s">
+      <c r="I324" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="J314" s="4" t="s">
+      <c r="J324" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="K314" s="12" t="s">
+      <c r="K324" s="14" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="315" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="12"/>
-      <c r="B315" s="12"/>
-      <c r="C315" s="12"/>
-      <c r="D315" s="12"/>
-      <c r="E315" s="12"/>
-      <c r="F315" s="12"/>
-      <c r="G315" s="12"/>
-      <c r="H315" s="12" t="n">
+    <row r="325" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H325" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="I315" s="4" t="s">
-        <v>707</v>
-      </c>
-      <c r="J315" s="10" t="s">
-        <v>708</v>
-      </c>
-      <c r="K315" s="12" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H316" s="12" t="n">
+      <c r="I325" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="J325" s="10" t="s">
+        <v>726</v>
+      </c>
+      <c r="K325" s="14" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H326" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="I316" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="J316" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="K316" s="12" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B317" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="K317" s="12"/>
-    </row>
-    <row r="319" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="12"/>
-      <c r="B319" s="12"/>
-      <c r="C319" s="12"/>
-      <c r="D319" s="12"/>
-      <c r="E319" s="12"/>
-      <c r="F319" s="12"/>
-      <c r="G319" s="12"/>
-      <c r="H319" s="12"/>
-      <c r="I319" s="12"/>
-      <c r="J319" s="12"/>
-      <c r="K319" s="12"/>
-    </row>
-    <row r="320" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="12"/>
-      <c r="B320" s="12"/>
-      <c r="C320" s="12"/>
-      <c r="D320" s="12"/>
-      <c r="E320" s="12"/>
-      <c r="F320" s="12"/>
-      <c r="G320" s="12"/>
-      <c r="H320" s="12"/>
-      <c r="I320" s="12"/>
-      <c r="J320" s="12"/>
-      <c r="K320" s="12"/>
-    </row>
-    <row r="321" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B321" s="12"/>
-      <c r="C321" s="12"/>
-      <c r="D321" s="12"/>
-      <c r="E321" s="12"/>
-      <c r="F321" s="12"/>
-      <c r="G321" s="12"/>
-      <c r="H321" s="12"/>
-      <c r="I321" s="12"/>
-      <c r="J321" s="12"/>
-      <c r="K321" s="12"/>
-    </row>
-    <row r="322" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="12"/>
-      <c r="B322" s="12"/>
-      <c r="C322" s="12"/>
-      <c r="D322" s="12"/>
-      <c r="E322" s="12"/>
-      <c r="F322" s="12"/>
-      <c r="G322" s="12"/>
-      <c r="H322" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="I322" s="4" t="s">
-        <v>710</v>
-      </c>
-      <c r="J322" s="10" t="s">
-        <v>711</v>
-      </c>
-      <c r="K322" s="12" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="323" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="12"/>
-      <c r="B323" s="12"/>
-      <c r="C323" s="12"/>
-      <c r="D323" s="12"/>
-      <c r="E323" s="12"/>
-      <c r="F323" s="12"/>
-      <c r="G323" s="12"/>
-      <c r="H323" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="I323" s="4" t="s">
-        <v>713</v>
-      </c>
-      <c r="J323" s="4" t="s">
-        <v>714</v>
-      </c>
-      <c r="K323" s="12" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="324" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="12"/>
-      <c r="B324" s="12"/>
-      <c r="C324" s="12"/>
-      <c r="D324" s="12"/>
-      <c r="E324" s="12"/>
-      <c r="F324" s="12"/>
-      <c r="G324" s="12"/>
-      <c r="H324" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="I324" s="4" t="s">
-        <v>716</v>
-      </c>
-      <c r="J324" s="4" t="s">
-        <v>717</v>
-      </c>
-      <c r="K324" s="12" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="325" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="12"/>
-      <c r="B325" s="12"/>
-      <c r="C325" s="12"/>
-      <c r="D325" s="12"/>
-      <c r="E325" s="12"/>
-      <c r="F325" s="12"/>
-      <c r="G325" s="12"/>
-      <c r="H325" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="I325" s="4" t="s">
-        <v>719</v>
-      </c>
-      <c r="J325" s="10" t="s">
-        <v>720</v>
-      </c>
-      <c r="K325" s="12" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="326" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="12"/>
-      <c r="B326" s="12"/>
-      <c r="C326" s="12"/>
-      <c r="D326" s="12"/>
-      <c r="E326" s="12"/>
-      <c r="F326" s="12"/>
-      <c r="G326" s="12"/>
-      <c r="H326" s="12" t="n">
-        <v>48</v>
-      </c>
       <c r="I326" s="4" t="s">
-        <v>722</v>
-      </c>
-      <c r="J326" s="4" t="s">
-        <v>723</v>
-      </c>
-      <c r="K326" s="12" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="327" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H327" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="I327" s="4" t="s">
-        <v>725</v>
-      </c>
-      <c r="J327" s="4" t="s">
-        <v>726</v>
-      </c>
-      <c r="K327" s="12" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B328" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="K328" s="12"/>
+        <v>271</v>
+      </c>
+      <c r="J326" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="K326" s="14" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B327" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K327" s="14"/>
     </row>
     <row r="329" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A329" s="12"/>
-      <c r="B329" s="12"/>
-      <c r="C329" s="12"/>
-      <c r="D329" s="12"/>
-      <c r="E329" s="12"/>
-      <c r="F329" s="12"/>
-      <c r="G329" s="12"/>
-      <c r="H329" s="12"/>
-      <c r="I329" s="12"/>
-      <c r="J329" s="12"/>
-      <c r="K329" s="12"/>
+      <c r="K329" s="14"/>
     </row>
     <row r="330" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="12"/>
-      <c r="B330" s="12"/>
-      <c r="C330" s="12"/>
-      <c r="D330" s="12"/>
-      <c r="E330" s="12"/>
-      <c r="F330" s="12"/>
-      <c r="G330" s="12"/>
-      <c r="H330" s="12"/>
-      <c r="I330" s="12"/>
-      <c r="J330" s="12"/>
-      <c r="K330" s="12"/>
+      <c r="K330" s="14"/>
     </row>
     <row r="331" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K331" s="14"/>
+    </row>
+    <row r="332" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H332" s="1" t="n">
         <v>45</v>
-      </c>
-      <c r="B331" s="12"/>
-      <c r="C331" s="12"/>
-      <c r="D331" s="12"/>
-      <c r="E331" s="12"/>
-      <c r="F331" s="12"/>
-      <c r="G331" s="12"/>
-      <c r="H331" s="12"/>
-      <c r="I331" s="12"/>
-      <c r="J331" s="12"/>
-      <c r="K331" s="12"/>
-    </row>
-    <row r="332" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A332" s="12"/>
-      <c r="B332" s="12"/>
-      <c r="C332" s="12"/>
-      <c r="D332" s="12"/>
-      <c r="E332" s="12"/>
-      <c r="F332" s="12"/>
-      <c r="G332" s="12"/>
-      <c r="H332" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="I332" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="J332" s="4" t="s">
+      <c r="J332" s="10" t="s">
         <v>729</v>
       </c>
-      <c r="K332" s="12" t="s">
+      <c r="K332" s="14" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="333" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A333" s="12"/>
-      <c r="B333" s="12"/>
-      <c r="C333" s="12"/>
-      <c r="D333" s="12"/>
-      <c r="E333" s="12"/>
-      <c r="F333" s="12"/>
-      <c r="G333" s="12"/>
-      <c r="H333" s="12" t="n">
-        <v>2</v>
+    <row r="333" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H333" s="1" t="n">
+        <v>46</v>
       </c>
       <c r="I333" s="4" t="s">
         <v>731</v>
@@ -9801,20 +8828,13 @@
       <c r="J333" s="4" t="s">
         <v>732</v>
       </c>
-      <c r="K333" s="12" t="s">
+      <c r="K333" s="14" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="334" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A334" s="12"/>
-      <c r="B334" s="12"/>
-      <c r="C334" s="12"/>
-      <c r="D334" s="12"/>
-      <c r="E334" s="12"/>
-      <c r="F334" s="12"/>
-      <c r="G334" s="12"/>
-      <c r="H334" s="12" t="n">
-        <v>5</v>
+    <row r="334" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H334" s="1" t="n">
+        <v>50</v>
       </c>
       <c r="I334" s="4" t="s">
         <v>734</v>
@@ -9822,41 +8842,27 @@
       <c r="J334" s="4" t="s">
         <v>735</v>
       </c>
-      <c r="K334" s="12" t="s">
+      <c r="K334" s="14" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="335" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A335" s="12"/>
-      <c r="B335" s="12"/>
-      <c r="C335" s="12"/>
-      <c r="D335" s="12"/>
-      <c r="E335" s="12"/>
-      <c r="F335" s="12"/>
-      <c r="G335" s="12"/>
-      <c r="H335" s="12" t="n">
-        <v>6</v>
+    <row r="335" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H335" s="1" t="n">
+        <v>47</v>
       </c>
       <c r="I335" s="4" t="s">
         <v>737</v>
       </c>
-      <c r="J335" s="4" t="s">
+      <c r="J335" s="10" t="s">
         <v>738</v>
       </c>
-      <c r="K335" s="12" t="s">
+      <c r="K335" s="14" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="336" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="12"/>
-      <c r="B336" s="12"/>
-      <c r="C336" s="12"/>
-      <c r="D336" s="12"/>
-      <c r="E336" s="12"/>
-      <c r="F336" s="12"/>
-      <c r="G336" s="12"/>
-      <c r="H336" s="12" t="n">
-        <v>212</v>
+    <row r="336" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H336" s="1" t="n">
+        <v>48</v>
       </c>
       <c r="I336" s="4" t="s">
         <v>740</v>
@@ -9864,20 +8870,13 @@
       <c r="J336" s="4" t="s">
         <v>741</v>
       </c>
-      <c r="K336" s="12" t="s">
+      <c r="K336" s="14" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="337" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="12"/>
-      <c r="B337" s="12"/>
-      <c r="C337" s="12"/>
-      <c r="D337" s="12"/>
-      <c r="E337" s="12"/>
-      <c r="F337" s="12"/>
-      <c r="G337" s="12"/>
-      <c r="H337" s="12" t="n">
-        <v>52</v>
+    <row r="337" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H337" s="1" t="n">
+        <v>49</v>
       </c>
       <c r="I337" s="4" t="s">
         <v>743</v>
@@ -9885,238 +8884,333 @@
       <c r="J337" s="4" t="s">
         <v>744</v>
       </c>
-      <c r="K337" s="12" t="s">
+      <c r="K337" s="14" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="338" s="1" customFormat="true" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="12"/>
-      <c r="B338" s="12"/>
-      <c r="C338" s="12"/>
-      <c r="D338" s="12"/>
-      <c r="E338" s="12"/>
-      <c r="F338" s="12"/>
-      <c r="G338" s="12"/>
-      <c r="H338" s="12" t="n">
+    <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B338" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K338" s="14"/>
+    </row>
+    <row r="339" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K339" s="14"/>
+    </row>
+    <row r="340" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K340" s="14"/>
+    </row>
+    <row r="341" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A341" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K341" s="14"/>
+    </row>
+    <row r="342" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H342" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I342" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="J342" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="K342" s="14" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="343" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H343" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I343" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="J343" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="K343" s="14" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="344" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H344" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I344" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="J344" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="K344" s="14" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="345" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H345" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I345" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="J345" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="K345" s="14" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="346" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H346" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="I346" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="J346" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="K346" s="14" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="347" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H347" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="I347" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="J347" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="K347" s="14" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="348" s="1" customFormat="true" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H348" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="I338" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="J338" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="K338" s="12" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H339" s="12" t="n">
+      <c r="I348" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="J348" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="K348" s="14" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H349" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I339" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="J339" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="K339" s="12" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B340" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="K340" s="12"/>
-    </row>
-    <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="12" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D343" s="12" t="s">
-        <v>749</v>
-      </c>
-      <c r="E343" s="12" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="344" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H344" s="12" t="n">
+      <c r="I349" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="J349" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="K349" s="14" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B350" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K350" s="14"/>
+    </row>
+    <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A352" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D353" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="E353" s="1" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="354" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H354" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I344" s="4" t="s">
-        <v>751</v>
-      </c>
-      <c r="J344" s="4" t="s">
-        <v>752</v>
-      </c>
-      <c r="K344" s="13" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="345" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H345" s="12" t="n">
+      <c r="I354" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="J354" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="K354" s="12" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="355" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H355" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="I345" s="4" t="s">
-        <v>754</v>
-      </c>
-      <c r="J345" s="4" t="s">
-        <v>755</v>
-      </c>
-      <c r="K345" s="13" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="346" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B346" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="H346" s="12" t="n">
+      <c r="I355" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="J355" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="K355" s="12" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="356" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B356" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="H356" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I346" s="4" t="s">
-        <v>757</v>
-      </c>
-      <c r="J346" s="4" t="s">
-        <v>758</v>
-      </c>
-      <c r="K346" s="13" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="12" t="s">
-        <v>760</v>
-      </c>
-      <c r="H349" s="12" t="n">
+      <c r="I356" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="J356" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="K356" s="12" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A359" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="H359" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="I349" s="12" t="s">
-        <v>761</v>
-      </c>
-      <c r="J349" s="12" t="s">
-        <v>762</v>
-      </c>
-      <c r="K349" s="13" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B350" s="12" t="s">
-        <v>764</v>
-      </c>
-      <c r="D350" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="H350" s="12" t="n">
+      <c r="I359" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="J359" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="K359" s="12" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B360" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="D360" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="H360" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="I350" s="12" t="s">
-        <v>765</v>
-      </c>
-      <c r="J350" s="12" t="s">
-        <v>766</v>
-      </c>
-      <c r="K350" s="13" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B351" s="12" t="s">
-        <v>764</v>
-      </c>
-      <c r="D351" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="H351" s="12" t="n">
+      <c r="I360" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="J360" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="K360" s="12" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B361" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="D361" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="H361" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="I351" s="12" t="s">
-        <v>768</v>
-      </c>
-      <c r="J351" s="12" t="s">
-        <v>769</v>
-      </c>
-      <c r="K351" s="13" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B352" s="12" t="s">
-        <v>771</v>
-      </c>
-      <c r="D352" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="H352" s="12" t="n">
+      <c r="I361" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="J361" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="K361" s="12" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B362" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="D362" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="H362" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="I352" s="12" t="s">
-        <v>772</v>
-      </c>
-      <c r="J352" s="12" t="s">
-        <v>773</v>
-      </c>
-      <c r="K352" s="13" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B353" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="D353" s="12" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A357" s="12" t="s">
-        <v>764</v>
-      </c>
-      <c r="H357" s="12" t="n">
+      <c r="I362" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="J362" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="K362" s="12" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B363" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A367" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="H367" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="I357" s="12" t="s">
-        <v>776</v>
-      </c>
-      <c r="J357" s="12" t="s">
-        <v>777</v>
-      </c>
-      <c r="K357" s="13" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B358" s="12" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A361" s="12" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H362" s="12" t="n">
+      <c r="I367" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="J367" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="K367" s="12" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B368" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A371" s="1" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H372" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="I362" s="12" t="s">
-        <v>779</v>
-      </c>
-      <c r="J362" s="12" t="s">
-        <v>780</v>
-      </c>
-      <c r="K362" s="13" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B363" s="12" t="s">
-        <v>183</v>
+      <c r="I372" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="J372" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="K372" s="12" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B373" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/_tutorial.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/_tutorial.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="801">
   <si>
     <t xml:space="preserve">version</t>
   </si>
@@ -309,6 +309,9 @@
   </si>
   <si>
     <t xml:space="preserve">Field Effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">필드 이펙트</t>
   </si>
   <si>
     <t xml:space="preserve">ether</t>
@@ -517,27 +520,8 @@
 This strange air...there’s a special law at work here.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">있잖아, 느껴져?
-이 이상한 공기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">… 뭔가 특별한 「이치」가 숨쉬고 있어.</t>
-    </r>
+    <t xml:space="preserve">있잖아, 느껴져?
+이 이상한 공기… 뭔가 특별한 「이치」가 숨쉬고 있어.</t>
   </si>
   <si>
     <t xml:space="preserve">これは…そう、きっと「フィールドエフェクト」が発動しているのね。
@@ -548,27 +532,8 @@
 I’ve heard about it before, but this is my first time experiencing it myself.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">이건</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">… 그래, 틀림없이 「필드 이펙트」가 발동하고 있는 거겠지.
+    <t xml:space="preserve">이건… 그래, 틀림없이 「필드 이펙트」가 발동하고 있는 거겠지.
 나도 얘기는 들어 봤지만, 실제로 경험하는 건 처음이야.</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">フィールドエフェクトは、現在居るマップにだけ適用される特殊なルール。
@@ -594,27 +559,8 @@
 And of course, there must be a reason for that.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">세계의 이치를 바꿔버릴 정도의 힘이, 이 장소에 있어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">…
+    <t xml:space="preserve">세계의 이치를 바꿔버릴 정도의 힘이, 이 장소에 있어…
 물론, 그에 상응하는 이유가 있을 거야.</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">…気をつけて進んでね。</t>
@@ -3314,7 +3260,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3366,13 +3312,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3437,7 +3376,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3486,15 +3425,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3502,15 +3433,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4263,6 +4190,9 @@
       <c r="G26" s="6" t="s">
         <v>95</v>
       </c>
+      <c r="H26" s="0" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="n">
@@ -4275,16 +4205,16 @@
         <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4298,16 +4228,16 @@
         <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4322,16 +4252,16 @@
         <v>8</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -4353,16 +4283,16 @@
         <v>8</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -4384,16 +4314,16 @@
         <v>8</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4408,16 +4338,16 @@
         <v>8</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -4439,16 +4369,16 @@
         <v>8</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4463,16 +4393,16 @@
         <v>8</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4487,16 +4417,16 @@
         <v>8</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -4518,16 +4448,16 @@
         <v>8</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -4548,16 +4478,16 @@
         <v>8</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4571,16 +4501,16 @@
         <v>8</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4594,16 +4524,16 @@
         <v>8</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -4630,9 +4560,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="64.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="63.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="12" width="47.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="74.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="88.2"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4640,19 +4569,19 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>0</v>
@@ -4666,7 +4595,7 @@
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4678,15 +4607,15 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D5" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D6" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>8</v>
@@ -4694,40 +4623,40 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D7" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D8" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="K12" s="14"/>
+      <c r="K12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I13" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J13" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="K13" s="4" t="s">
         <v>161</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4735,41 +4664,41 @@
         <v>233</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="K14" s="14" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K14" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H15" s="1" t="n">
         <v>234</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="K15" s="14" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K15" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H16" s="1" t="n">
         <v>235</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="K16" s="14" t="s">
         <v>170</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4777,13 +4706,13 @@
         <v>236</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="K17" s="14" t="s">
         <v>173</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4791,51 +4720,51 @@
         <v>327</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="K18" s="15" t="s">
         <v>176</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I19" s="4"/>
       <c r="J19" s="10"/>
-      <c r="K19" s="14"/>
+      <c r="K19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I20" s="4"/>
       <c r="J20" s="10"/>
-      <c r="K20" s="14"/>
+      <c r="K20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
-      <c r="K21" s="14"/>
+      <c r="K21" s="1"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="K22" s="14"/>
+        <v>144</v>
+      </c>
+      <c r="K22" s="1"/>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H23" s="1" t="n">
         <v>220</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="K23" s="14" t="s">
         <v>180</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4843,13 +4772,13 @@
         <v>221</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J24" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="K24" s="14" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4857,13 +4786,13 @@
         <v>222</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="K25" s="14" t="s">
         <v>183</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4871,13 +4800,13 @@
         <v>223</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="K26" s="14" t="s">
         <v>186</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4885,13 +4814,13 @@
         <v>224</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="K27" s="14" t="s">
         <v>189</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4899,13 +4828,13 @@
         <v>225</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="K28" s="14" t="s">
         <v>192</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4913,13 +4842,13 @@
         <v>226</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="K29" s="14" t="s">
         <v>195</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4927,69 +4856,69 @@
         <v>227</v>
       </c>
       <c r="I30" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="K30" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="J30" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="K30" s="14" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H31" s="1" t="n">
         <v>228</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="K31" s="14" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K31" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H32" s="1" t="n">
         <v>229</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="K32" s="14" t="s">
         <v>201</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
-      <c r="K33" s="14"/>
+      <c r="K33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="K34" s="14"/>
+      <c r="K34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H35" s="1" t="n">
         <v>200</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="K35" s="14" t="s">
         <v>204</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4997,13 +4926,13 @@
         <v>201</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="K36" s="14" t="s">
         <v>207</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5011,13 +4940,13 @@
         <v>202</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="K37" s="14" t="s">
         <v>210</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5025,41 +4954,41 @@
         <v>203</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="K38" s="14" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K38" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H39" s="1" t="n">
         <v>204</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="K39" s="14" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K39" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H40" s="1" t="n">
         <v>205</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="K40" s="14" t="s">
         <v>219</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5067,13 +4996,13 @@
         <v>206</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="K41" s="14" t="s">
         <v>222</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5081,13 +5010,13 @@
         <v>207</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="K42" s="14" t="s">
         <v>225</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5095,47 +5024,47 @@
         <v>208</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="K43" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
-      <c r="K44" s="14"/>
+      <c r="K44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
-      <c r="K45" s="14"/>
+      <c r="K45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K46" s="14"/>
+        <v>140</v>
+      </c>
+      <c r="K46" s="1"/>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H47" s="1" t="n">
         <v>210</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="K47" s="14" t="s">
         <v>228</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5143,85 +5072,84 @@
         <v>211</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="K48" s="14" t="s">
         <v>231</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I49" s="4"/>
       <c r="J49" s="10"/>
-      <c r="K49" s="14"/>
+      <c r="K49" s="1"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
-      <c r="K50" s="14"/>
+      <c r="K50" s="1"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
-      <c r="K51" s="14"/>
+      <c r="K51" s="1"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="4"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
-      <c r="K52" s="14"/>
+      <c r="K52" s="1"/>
     </row>
     <row r="53" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="K53" s="14"/>
+        <v>133</v>
+      </c>
     </row>
     <row r="54" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H54" s="1" t="n">
         <v>193</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="K54" s="14" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="55" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K54" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H55" s="1" t="n">
         <v>194</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="K55" s="14" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="56" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K55" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H56" s="1" t="n">
         <v>195</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="K56" s="14" t="s">
         <v>240</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5229,113 +5157,109 @@
         <v>196</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="K57" s="14" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="58" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K57" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H58" s="1" t="n">
         <v>197</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J58" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="K58" s="14" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="59" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K58" s="4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H59" s="1" t="n">
         <v>198</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="K59" s="14" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="60" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K59" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H60" s="1" t="n">
         <v>199</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="K60" s="14" t="s">
         <v>252</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I61" s="4"/>
       <c r="J61" s="10"/>
-      <c r="K61" s="14"/>
     </row>
     <row r="62" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
-      <c r="K62" s="14"/>
     </row>
     <row r="63" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I63" s="4"/>
       <c r="J63" s="4"/>
-      <c r="K63" s="14"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4"/>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
-      <c r="K64" s="14"/>
+      <c r="K64" s="1"/>
     </row>
     <row r="65" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K65" s="14"/>
     </row>
     <row r="66" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H66" s="1" t="n">
         <v>184</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J66" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="K66" s="14" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="67" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K66" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="67" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H67" s="1" t="n">
         <v>185</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J67" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="K67" s="14" t="s">
         <v>258</v>
+      </c>
+      <c r="K67" s="4" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5343,27 +5267,27 @@
         <v>186</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J68" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="K68" s="14" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="69" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K68" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="69" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H69" s="1" t="n">
         <v>187</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J69" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="K69" s="14" t="s">
         <v>264</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5371,27 +5295,27 @@
         <v>188</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J70" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="K70" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="K70" s="14" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="71" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="71" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H71" s="1" t="n">
         <v>189</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J71" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="K71" s="14" t="s">
         <v>267</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5399,27 +5323,27 @@
         <v>190</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J72" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="K72" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="K72" s="14" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="73" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="73" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H73" s="1" t="n">
         <v>191</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J73" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="K73" s="14" t="s">
         <v>270</v>
+      </c>
+      <c r="K73" s="4" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5427,82 +5351,80 @@
         <v>192</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J74" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="K74" s="14" t="s">
         <v>273</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I75" s="4"/>
       <c r="J75" s="4"/>
-      <c r="K75" s="14"/>
     </row>
     <row r="76" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I76" s="4"/>
       <c r="J76" s="4"/>
-      <c r="K76" s="14"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
-      <c r="K77" s="14"/>
+      <c r="K77" s="1"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K78" s="14"/>
+        <v>109</v>
+      </c>
+      <c r="K78" s="1"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K79" s="14"/>
+      <c r="K79" s="1"/>
     </row>
     <row r="80" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H80" s="1" t="n">
         <v>174</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J80" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="K80" s="14" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="81" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K80" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="81" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H81" s="1" t="n">
         <v>175</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="K81" s="14" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="82" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K81" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="82" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H82" s="1" t="n">
         <v>176</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="K82" s="14" t="s">
         <v>282</v>
+      </c>
+      <c r="K82" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="83" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5510,141 +5432,138 @@
         <v>177</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="K83" s="14" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="84" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K83" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="84" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H84" s="1" t="n">
         <v>178</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="K84" s="14" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="85" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K84" s="4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="85" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H85" s="1" t="n">
         <v>179</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K85" s="14" t="s">
         <v>291</v>
+      </c>
+      <c r="K85" s="4" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K86" s="14"/>
+        <v>178</v>
+      </c>
+      <c r="K86" s="1"/>
     </row>
     <row r="88" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="K88" s="14"/>
+        <v>113</v>
+      </c>
+      <c r="K88" s="1"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K89" s="14"/>
+      <c r="K89" s="1"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H90" s="1" t="n">
         <v>180</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J90" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="K90" s="14" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="91" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K90" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H91" s="1" t="n">
         <v>181</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J91" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="K91" s="14" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="92" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K91" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H92" s="1" t="n">
         <v>182</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J92" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="K92" s="14" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="93" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K92" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H93" s="1" t="n">
         <v>183</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J93" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="K93" s="14" t="s">
         <v>303</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K94" s="14"/>
+        <v>178</v>
+      </c>
+      <c r="K94" s="1"/>
     </row>
     <row r="97" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K97" s="14"/>
-    </row>
-    <row r="98" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K98" s="14"/>
-    </row>
+    </row>
+    <row r="98" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="99" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H99" s="1" t="n">
         <v>22</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J99" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="K99" s="14" t="s">
         <v>306</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5652,27 +5571,27 @@
         <v>23</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="K100" s="14" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="101" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K100" s="4" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="101" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H101" s="1" t="n">
         <v>24</v>
       </c>
       <c r="I101" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="K101" s="14" t="s">
         <v>312</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5680,20 +5599,19 @@
         <v>25</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J102" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="K102" s="14" t="s">
         <v>315</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K103" s="14"/>
+        <v>178</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J104" s="4"/>
@@ -5712,7 +5630,7 @@
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
     </row>
-    <row r="106" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -5723,17 +5641,17 @@
       <c r="H106" s="1" t="n">
         <v>169</v>
       </c>
-      <c r="I106" s="16" t="s">
-        <v>316</v>
+      <c r="I106" s="12" t="s">
+        <v>317</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -5744,17 +5662,17 @@
       <c r="H107" s="1" t="n">
         <v>170</v>
       </c>
-      <c r="I107" s="16" t="s">
-        <v>319</v>
+      <c r="I107" s="12" t="s">
+        <v>320</v>
       </c>
       <c r="J107" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -5765,17 +5683,17 @@
       <c r="H108" s="1" t="n">
         <v>171</v>
       </c>
-      <c r="I108" s="16" t="s">
-        <v>322</v>
+      <c r="I108" s="12" t="s">
+        <v>323</v>
       </c>
       <c r="J108" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="287.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -5786,17 +5704,17 @@
       <c r="H109" s="1" t="n">
         <v>172</v>
       </c>
-      <c r="I109" s="16" t="s">
-        <v>325</v>
+      <c r="I109" s="12" t="s">
+        <v>326</v>
       </c>
       <c r="J109" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="162" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -5807,14 +5725,14 @@
       <c r="H110" s="1" t="n">
         <v>173</v>
       </c>
-      <c r="I110" s="16" t="s">
-        <v>328</v>
+      <c r="I110" s="12" t="s">
+        <v>329</v>
       </c>
       <c r="J110" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5832,7 +5750,7 @@
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="4"/>
       <c r="B112" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
@@ -5845,7 +5763,7 @@
     </row>
     <row r="113" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -5857,7 +5775,7 @@
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
     </row>
-    <row r="114" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -5868,17 +5786,17 @@
       <c r="H114" s="1" t="n">
         <v>155</v>
       </c>
-      <c r="I114" s="17" t="s">
-        <v>331</v>
+      <c r="I114" s="13" t="s">
+        <v>332</v>
       </c>
       <c r="J114" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="115" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="115" s="1" customFormat="true" ht="138.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -5889,17 +5807,17 @@
       <c r="H115" s="1" t="n">
         <v>156</v>
       </c>
-      <c r="I115" s="16" t="s">
-        <v>334</v>
+      <c r="I115" s="12" t="s">
+        <v>335</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="116" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="116" s="1" customFormat="true" ht="196.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -5910,17 +5828,17 @@
       <c r="H116" s="1" t="n">
         <v>157</v>
       </c>
-      <c r="I116" s="16" t="s">
-        <v>337</v>
+      <c r="I116" s="12" t="s">
+        <v>338</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="117" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="117" s="1" customFormat="true" ht="196.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -5931,17 +5849,17 @@
       <c r="H117" s="1" t="n">
         <v>158</v>
       </c>
-      <c r="I117" s="16" t="s">
-        <v>340</v>
+      <c r="I117" s="12" t="s">
+        <v>341</v>
       </c>
       <c r="J117" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="118" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="118" s="1" customFormat="true" ht="162" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -5952,17 +5870,17 @@
       <c r="H118" s="1" t="n">
         <v>159</v>
       </c>
-      <c r="I118" s="16" t="s">
-        <v>343</v>
+      <c r="I118" s="12" t="s">
+        <v>344</v>
       </c>
       <c r="J118" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="119" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="119" s="1" customFormat="true" ht="162" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -5973,20 +5891,20 @@
       <c r="H119" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="I119" s="16" t="s">
-        <v>346</v>
+      <c r="I119" s="12" t="s">
+        <v>347</v>
       </c>
       <c r="J119" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="120" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="4"/>
       <c r="B120" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
@@ -5999,7 +5917,7 @@
     </row>
     <row r="121" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -6022,17 +5940,17 @@
       <c r="H122" s="1" t="n">
         <v>161</v>
       </c>
-      <c r="I122" s="17" t="s">
-        <v>349</v>
+      <c r="I122" s="13" t="s">
+        <v>350</v>
       </c>
       <c r="J122" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K122" s="4" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="123" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="123" s="1" customFormat="true" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -6043,17 +5961,17 @@
       <c r="H123" s="1" t="n">
         <v>162</v>
       </c>
-      <c r="I123" s="16" t="s">
-        <v>352</v>
+      <c r="I123" s="12" t="s">
+        <v>353</v>
       </c>
       <c r="J123" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K123" s="4" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="124" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="124" s="1" customFormat="true" ht="219.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -6064,17 +5982,17 @@
       <c r="H124" s="1" t="n">
         <v>163</v>
       </c>
-      <c r="I124" s="16" t="s">
-        <v>355</v>
+      <c r="I124" s="12" t="s">
+        <v>356</v>
       </c>
       <c r="J124" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K124" s="4" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="125" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="125" s="1" customFormat="true" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -6085,20 +6003,20 @@
       <c r="H125" s="1" t="n">
         <v>164</v>
       </c>
-      <c r="I125" s="16" t="s">
-        <v>358</v>
+      <c r="I125" s="12" t="s">
+        <v>359</v>
       </c>
       <c r="J125" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="126" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="4"/>
       <c r="B126" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
@@ -6134,14 +6052,14 @@
       <c r="H128" s="1" t="n">
         <v>165</v>
       </c>
-      <c r="I128" s="17" t="s">
-        <v>361</v>
+      <c r="I128" s="13" t="s">
+        <v>362</v>
       </c>
       <c r="J128" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K128" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="129" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6155,17 +6073,17 @@
       <c r="H129" s="1" t="n">
         <v>166</v>
       </c>
-      <c r="I129" s="17" t="s">
-        <v>160</v>
+      <c r="I129" s="13" t="s">
+        <v>161</v>
       </c>
       <c r="J129" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="K129" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="K129" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="130" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="130" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -6176,17 +6094,17 @@
       <c r="H130" s="1" t="n">
         <v>167</v>
       </c>
-      <c r="I130" s="17" t="s">
-        <v>364</v>
+      <c r="I130" s="13" t="s">
+        <v>365</v>
       </c>
       <c r="J130" s="10" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="131" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="131" s="1" customFormat="true" ht="150.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -6197,20 +6115,20 @@
       <c r="H131" s="1" t="n">
         <v>168</v>
       </c>
-      <c r="I131" s="16" t="s">
-        <v>367</v>
+      <c r="I131" s="12" t="s">
+        <v>368</v>
       </c>
       <c r="J131" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K131" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="132" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="4"/>
       <c r="B132" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
@@ -6235,7 +6153,7 @@
       <c r="J133" s="4"/>
       <c r="K133" s="4"/>
     </row>
-    <row r="134" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -6246,17 +6164,17 @@
       <c r="H134" s="1" t="n">
         <v>116</v>
       </c>
-      <c r="I134" s="16" t="s">
-        <v>370</v>
+      <c r="I134" s="12" t="s">
+        <v>371</v>
       </c>
       <c r="J134" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="135" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="135" s="1" customFormat="true" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -6267,17 +6185,17 @@
       <c r="H135" s="1" t="n">
         <v>117</v>
       </c>
-      <c r="I135" s="16" t="s">
-        <v>373</v>
+      <c r="I135" s="12" t="s">
+        <v>374</v>
       </c>
       <c r="J135" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K135" s="4" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="136" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="136" s="1" customFormat="true" ht="196.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -6288,17 +6206,17 @@
       <c r="H136" s="1" t="n">
         <v>118</v>
       </c>
-      <c r="I136" s="16" t="s">
-        <v>376</v>
+      <c r="I136" s="12" t="s">
+        <v>377</v>
       </c>
       <c r="J136" s="10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K136" s="4" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="137" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="137" s="1" customFormat="true" ht="127.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -6309,17 +6227,17 @@
       <c r="H137" s="1" t="n">
         <v>119</v>
       </c>
-      <c r="I137" s="16" t="s">
-        <v>379</v>
+      <c r="I137" s="12" t="s">
+        <v>380</v>
       </c>
       <c r="J137" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K137" s="4" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="138" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="138" s="1" customFormat="true" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -6330,20 +6248,20 @@
       <c r="H138" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="I138" s="16" t="s">
-        <v>382</v>
+      <c r="I138" s="12" t="s">
+        <v>383</v>
       </c>
       <c r="J138" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K138" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="139" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="4"/>
       <c r="B139" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C139" s="4"/>
       <c r="D139" s="4"/>
@@ -6380,7 +6298,7 @@
       <c r="J141" s="4"/>
       <c r="K141" s="4"/>
     </row>
-    <row r="142" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -6391,17 +6309,17 @@
       <c r="H142" s="1" t="n">
         <v>121</v>
       </c>
-      <c r="I142" s="16" t="s">
-        <v>385</v>
+      <c r="I142" s="12" t="s">
+        <v>386</v>
       </c>
       <c r="J142" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K142" s="4" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="143" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="143" s="1" customFormat="true" ht="150.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -6412,17 +6330,17 @@
       <c r="H143" s="1" t="n">
         <v>122</v>
       </c>
-      <c r="I143" s="16" t="s">
-        <v>388</v>
+      <c r="I143" s="12" t="s">
+        <v>389</v>
       </c>
       <c r="J143" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K143" s="4" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="144" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="144" s="1" customFormat="true" ht="184.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -6433,17 +6351,17 @@
       <c r="H144" s="1" t="n">
         <v>123</v>
       </c>
-      <c r="I144" s="16" t="s">
-        <v>391</v>
+      <c r="I144" s="12" t="s">
+        <v>392</v>
       </c>
       <c r="J144" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K144" s="4" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="145" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="145" s="1" customFormat="true" ht="138.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -6454,17 +6372,17 @@
       <c r="H145" s="1" t="n">
         <v>124</v>
       </c>
-      <c r="I145" s="16" t="s">
-        <v>394</v>
+      <c r="I145" s="12" t="s">
+        <v>395</v>
       </c>
       <c r="J145" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K145" s="4" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="146" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="146" s="1" customFormat="true" ht="173.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -6475,17 +6393,17 @@
       <c r="H146" s="1" t="n">
         <v>125</v>
       </c>
-      <c r="I146" s="16" t="s">
-        <v>397</v>
+      <c r="I146" s="12" t="s">
+        <v>398</v>
       </c>
       <c r="J146" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K146" s="4" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="147" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="147" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -6497,13 +6415,13 @@
         <v>126</v>
       </c>
       <c r="I147" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J147" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K147" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="148" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6521,7 +6439,7 @@
     <row r="149" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="4"/>
       <c r="B149" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C149" s="4"/>
       <c r="D149" s="4"/>
@@ -6558,7 +6476,7 @@
       <c r="J151" s="4"/>
       <c r="K151" s="4"/>
     </row>
-    <row r="152" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -6569,21 +6487,21 @@
       <c r="H152" s="1" t="n">
         <v>127</v>
       </c>
-      <c r="I152" s="16" t="s">
-        <v>403</v>
+      <c r="I152" s="12" t="s">
+        <v>404</v>
       </c>
       <c r="J152" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K152" s="4" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="153" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="153" s="1" customFormat="true" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
@@ -6592,21 +6510,21 @@
       <c r="H153" s="1" t="n">
         <v>230</v>
       </c>
-      <c r="I153" s="16" t="s">
-        <v>407</v>
+      <c r="I153" s="12" t="s">
+        <v>408</v>
       </c>
       <c r="J153" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K153" s="4" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="154" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="154" s="1" customFormat="true" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D154" s="4"/>
       <c r="E154" s="4"/>
@@ -6615,21 +6533,21 @@
       <c r="H154" s="1" t="n">
         <v>231</v>
       </c>
-      <c r="I154" s="16" t="s">
-        <v>411</v>
+      <c r="I154" s="12" t="s">
+        <v>412</v>
       </c>
       <c r="J154" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K154" s="4" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="155" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="155" s="1" customFormat="true" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
@@ -6638,17 +6556,17 @@
       <c r="H155" s="1" t="n">
         <v>232</v>
       </c>
-      <c r="I155" s="16" t="s">
-        <v>414</v>
+      <c r="I155" s="12" t="s">
+        <v>415</v>
       </c>
       <c r="J155" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K155" s="4" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="156" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="156" s="1" customFormat="true" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -6659,14 +6577,14 @@
       <c r="H156" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="I156" s="18" t="s">
-        <v>417</v>
+      <c r="I156" s="14" t="s">
+        <v>418</v>
       </c>
       <c r="J156" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K156" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6684,7 +6602,7 @@
     <row r="158" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="4"/>
       <c r="B158" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
@@ -6709,7 +6627,7 @@
     </row>
     <row r="160" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -6721,7 +6639,7 @@
       <c r="J160" s="4"/>
       <c r="K160" s="4"/>
     </row>
-    <row r="161" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -6732,17 +6650,17 @@
       <c r="H161" s="1" t="n">
         <v>129</v>
       </c>
-      <c r="I161" s="16" t="s">
-        <v>420</v>
+      <c r="I161" s="12" t="s">
+        <v>421</v>
       </c>
       <c r="J161" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K161" s="4" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="162" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="162" s="1" customFormat="true" ht="127.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -6753,17 +6671,17 @@
       <c r="H162" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="I162" s="16" t="s">
-        <v>423</v>
+      <c r="I162" s="12" t="s">
+        <v>424</v>
       </c>
       <c r="J162" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K162" s="4" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="163" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="163" s="1" customFormat="true" ht="127.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -6774,17 +6692,17 @@
       <c r="H163" s="1" t="n">
         <v>131</v>
       </c>
-      <c r="I163" s="16" t="s">
-        <v>426</v>
+      <c r="I163" s="12" t="s">
+        <v>427</v>
       </c>
       <c r="J163" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K163" s="4" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="164" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="164" s="1" customFormat="true" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -6795,17 +6713,17 @@
       <c r="H164" s="1" t="n">
         <v>132</v>
       </c>
-      <c r="I164" s="16" t="s">
-        <v>429</v>
+      <c r="I164" s="12" t="s">
+        <v>430</v>
       </c>
       <c r="J164" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K164" s="4" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="165" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="165" s="1" customFormat="true" ht="207.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -6816,17 +6734,17 @@
       <c r="H165" s="1" t="n">
         <v>133</v>
       </c>
-      <c r="I165" s="16" t="s">
-        <v>432</v>
+      <c r="I165" s="12" t="s">
+        <v>433</v>
       </c>
       <c r="J165" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K165" s="4" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="166" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="166" s="1" customFormat="true" ht="162" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -6837,17 +6755,17 @@
       <c r="H166" s="1" t="n">
         <v>134</v>
       </c>
-      <c r="I166" s="16" t="s">
-        <v>435</v>
+      <c r="I166" s="12" t="s">
+        <v>436</v>
       </c>
       <c r="J166" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K166" s="4" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="167" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="167" s="1" customFormat="true" ht="127.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -6858,17 +6776,17 @@
       <c r="H167" s="1" t="n">
         <v>135</v>
       </c>
-      <c r="I167" s="18" t="s">
-        <v>438</v>
+      <c r="I167" s="14" t="s">
+        <v>439</v>
       </c>
       <c r="J167" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K167" s="4" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="168" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="168" s="1" customFormat="true" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -6879,20 +6797,20 @@
       <c r="H168" s="1" t="n">
         <v>136</v>
       </c>
-      <c r="I168" s="18" t="s">
-        <v>441</v>
+      <c r="I168" s="14" t="s">
+        <v>442</v>
       </c>
       <c r="J168" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K168" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="169" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="4"/>
       <c r="B169" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
@@ -6929,7 +6847,7 @@
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
     </row>
-    <row r="172" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -6940,17 +6858,17 @@
       <c r="H172" s="1" t="n">
         <v>137</v>
       </c>
-      <c r="I172" s="16" t="s">
-        <v>444</v>
+      <c r="I172" s="12" t="s">
+        <v>445</v>
       </c>
       <c r="J172" s="10" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K172" s="4" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="173" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="173" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -6961,17 +6879,17 @@
       <c r="H173" s="1" t="n">
         <v>138</v>
       </c>
-      <c r="I173" s="16" t="s">
-        <v>447</v>
+      <c r="I173" s="12" t="s">
+        <v>448</v>
       </c>
       <c r="J173" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K173" s="4" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="174" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="174" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -6982,17 +6900,17 @@
       <c r="H174" s="1" t="n">
         <v>139</v>
       </c>
-      <c r="I174" s="16" t="s">
-        <v>450</v>
+      <c r="I174" s="12" t="s">
+        <v>451</v>
       </c>
       <c r="J174" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K174" s="4" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="175" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="175" s="1" customFormat="true" ht="162" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -7003,17 +6921,17 @@
       <c r="H175" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="I175" s="16" t="s">
-        <v>453</v>
+      <c r="I175" s="12" t="s">
+        <v>454</v>
       </c>
       <c r="J175" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K175" s="4" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="176" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="176" s="1" customFormat="true" ht="150.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -7024,17 +6942,17 @@
       <c r="H176" s="1" t="n">
         <v>141</v>
       </c>
-      <c r="I176" s="16" t="s">
-        <v>456</v>
+      <c r="I176" s="12" t="s">
+        <v>457</v>
       </c>
       <c r="J176" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K176" s="4" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="177" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="177" s="1" customFormat="true" ht="196.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -7045,20 +6963,20 @@
       <c r="H177" s="1" t="n">
         <v>142</v>
       </c>
-      <c r="I177" s="16" t="s">
-        <v>459</v>
+      <c r="I177" s="12" t="s">
+        <v>460</v>
       </c>
       <c r="J177" s="10" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K177" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="178" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="4"/>
       <c r="B178" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C178" s="4"/>
       <c r="D178" s="4"/>
@@ -7071,7 +6989,7 @@
     </row>
     <row r="179" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -7083,7 +7001,7 @@
       <c r="J179" s="4"/>
       <c r="K179" s="4"/>
     </row>
-    <row r="180" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -7094,17 +7012,17 @@
       <c r="H180" s="1" t="n">
         <v>143</v>
       </c>
-      <c r="I180" s="16" t="s">
-        <v>462</v>
+      <c r="I180" s="12" t="s">
+        <v>463</v>
       </c>
       <c r="J180" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K180" s="4" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="181" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="181" s="1" customFormat="true" ht="219.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -7115,17 +7033,17 @@
       <c r="H181" s="1" t="n">
         <v>144</v>
       </c>
-      <c r="I181" s="16" t="s">
-        <v>465</v>
+      <c r="I181" s="12" t="s">
+        <v>466</v>
       </c>
       <c r="J181" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K181" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="182" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="182" s="1" customFormat="true" ht="242.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -7136,17 +7054,17 @@
       <c r="H182" s="1" t="n">
         <v>145</v>
       </c>
-      <c r="I182" s="16" t="s">
-        <v>468</v>
+      <c r="I182" s="12" t="s">
+        <v>469</v>
       </c>
       <c r="J182" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K182" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="183" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="183" s="1" customFormat="true" ht="242.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -7157,17 +7075,17 @@
       <c r="H183" s="1" t="n">
         <v>146</v>
       </c>
-      <c r="I183" s="16" t="s">
-        <v>471</v>
+      <c r="I183" s="12" t="s">
+        <v>472</v>
       </c>
       <c r="J183" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K183" s="4" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="184" s="1" customFormat="true" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="184" s="1" customFormat="true" ht="219.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -7178,14 +7096,14 @@
       <c r="H184" s="1" t="n">
         <v>147</v>
       </c>
-      <c r="I184" s="16" t="s">
-        <v>474</v>
+      <c r="I184" s="12" t="s">
+        <v>475</v>
       </c>
       <c r="J184" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K184" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="185" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7215,7 +7133,7 @@
     <row r="187" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="4"/>
       <c r="B187" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C187" s="4"/>
       <c r="D187" s="4"/>
@@ -7240,7 +7158,7 @@
       <c r="J188" s="4"/>
       <c r="K188" s="4"/>
     </row>
-    <row r="189" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -7252,16 +7170,16 @@
         <v>148</v>
       </c>
       <c r="I189" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J189" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K189" s="4" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="190" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="190" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -7273,16 +7191,16 @@
         <v>149</v>
       </c>
       <c r="I190" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J190" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K190" s="4" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="191" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="191" s="1" customFormat="true" ht="150.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -7294,16 +7212,16 @@
         <v>150</v>
       </c>
       <c r="I191" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J191" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K191" s="4" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="192" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="192" s="1" customFormat="true" ht="230.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -7315,16 +7233,16 @@
         <v>151</v>
       </c>
       <c r="I192" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J192" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K192" s="4" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="193" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="193" s="1" customFormat="true" ht="184.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -7336,16 +7254,16 @@
         <v>152</v>
       </c>
       <c r="I193" s="4" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J193" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K193" s="4" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="194" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="194" s="1" customFormat="true" ht="219.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -7357,16 +7275,16 @@
         <v>153</v>
       </c>
       <c r="I194" s="4" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J194" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K194" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="195" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="162" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -7378,19 +7296,19 @@
         <v>154</v>
       </c>
       <c r="I195" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J195" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K195" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="196" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="4"/>
       <c r="B196" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C196" s="4"/>
       <c r="D196" s="4"/>
@@ -7403,43 +7321,39 @@
     </row>
     <row r="197" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B197" s="4"/>
-      <c r="K197" s="14"/>
     </row>
     <row r="198" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="K198" s="14"/>
-    </row>
-    <row r="199" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K199" s="14"/>
-    </row>
+    </row>
+    <row r="199" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="200" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H200" s="1" t="n">
         <v>105</v>
       </c>
       <c r="I200" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J200" s="10" t="s">
-        <v>499</v>
-      </c>
-      <c r="K200" s="14" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="201" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K200" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="201" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H201" s="1" t="n">
         <v>106</v>
       </c>
       <c r="I201" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J201" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="K201" s="14" t="s">
         <v>503</v>
+      </c>
+      <c r="K201" s="4" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="202" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7447,126 +7361,122 @@
         <v>107</v>
       </c>
       <c r="I202" s="4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="J202" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="K202" s="14" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="203" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K202" s="4" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="203" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H203" s="1" t="n">
         <v>108</v>
       </c>
       <c r="I203" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="J203" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="K203" s="14" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="204" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K203" s="4" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="204" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H204" s="1" t="n">
         <v>109</v>
       </c>
       <c r="I204" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="J204" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="K204" s="14" t="s">
         <v>512</v>
+      </c>
+      <c r="K204" s="4" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="205" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B205" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K205" s="14"/>
+        <v>178</v>
+      </c>
     </row>
     <row r="206" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K206" s="14"/>
-    </row>
-    <row r="207" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K207" s="14"/>
-    </row>
+    </row>
+    <row r="207" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="208" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H208" s="1" t="n">
         <v>110</v>
       </c>
       <c r="I208" s="4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J208" s="10" t="s">
-        <v>514</v>
-      </c>
-      <c r="K208" s="14" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="209" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K208" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="209" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H209" s="1" t="n">
         <v>111</v>
       </c>
       <c r="I209" s="4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="J209" s="10" t="s">
-        <v>517</v>
-      </c>
-      <c r="K209" s="14" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="210" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K209" s="4" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="210" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H210" s="1" t="n">
         <v>112</v>
       </c>
       <c r="I210" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J210" s="10" t="s">
-        <v>520</v>
-      </c>
-      <c r="K210" s="14" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="211" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K210" s="4" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="211" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H211" s="1" t="n">
         <v>113</v>
       </c>
       <c r="I211" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="J211" s="10" t="s">
-        <v>523</v>
-      </c>
-      <c r="K211" s="14" t="s">
         <v>524</v>
       </c>
-    </row>
-    <row r="212" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K211" s="4" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="212" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H212" s="1" t="n">
         <v>114</v>
       </c>
       <c r="I212" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="J212" s="10" t="s">
-        <v>526</v>
-      </c>
-      <c r="K212" s="14" t="s">
         <v>527</v>
+      </c>
+      <c r="K212" s="4" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7574,102 +7484,97 @@
         <v>115</v>
       </c>
       <c r="I213" s="4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J213" s="10" t="s">
-        <v>529</v>
-      </c>
-      <c r="K213" s="14" t="s">
         <v>530</v>
+      </c>
+      <c r="K213" s="1" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="214" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B214" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K214" s="14"/>
+        <v>178</v>
+      </c>
     </row>
     <row r="215" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B215" s="4"/>
-      <c r="K215" s="14"/>
     </row>
     <row r="216" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="K216" s="14"/>
-    </row>
-    <row r="217" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K217" s="14"/>
-    </row>
+    </row>
+    <row r="217" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="218" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H218" s="1" t="n">
         <v>26</v>
       </c>
       <c r="I218" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="J218" s="10" t="s">
-        <v>532</v>
-      </c>
-      <c r="K218" s="14" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="219" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K218" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="219" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H219" s="1" t="n">
         <v>27</v>
       </c>
       <c r="I219" s="4" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="J219" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="K219" s="14" t="s">
         <v>536</v>
       </c>
-    </row>
-    <row r="220" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K219" s="4" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="220" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H220" s="1" t="n">
         <v>28</v>
       </c>
       <c r="I220" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="J220" s="4" t="s">
-        <v>538</v>
-      </c>
-      <c r="K220" s="14" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="221" s="1" customFormat="true" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K220" s="4" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="221" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H221" s="1" t="n">
         <v>29</v>
       </c>
       <c r="I221" s="4" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="J221" s="4" t="s">
-        <v>541</v>
-      </c>
-      <c r="K221" s="14" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="222" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K221" s="4" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="222" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H222" s="1" t="n">
         <v>30</v>
       </c>
       <c r="I222" s="4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J222" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="K222" s="14" t="s">
         <v>545</v>
+      </c>
+      <c r="K222" s="4" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="223" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7677,13 +7582,13 @@
         <v>31</v>
       </c>
       <c r="I223" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J223" s="4" t="s">
-        <v>547</v>
-      </c>
-      <c r="K223" s="14" t="s">
         <v>548</v>
+      </c>
+      <c r="K223" s="1" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="224" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7691,27 +7596,27 @@
         <v>32</v>
       </c>
       <c r="I224" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J224" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="K224" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="K224" s="14" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="225" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="225" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H225" s="1" t="n">
         <v>33</v>
       </c>
       <c r="I225" s="4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J225" s="4" t="s">
-        <v>550</v>
-      </c>
-      <c r="K225" s="14" t="s">
         <v>551</v>
+      </c>
+      <c r="K225" s="4" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7719,20 +7624,20 @@
         <v>34</v>
       </c>
       <c r="I226" s="4" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="J226" s="4" t="s">
-        <v>553</v>
-      </c>
-      <c r="K226" s="14" t="s">
         <v>554</v>
+      </c>
+      <c r="K226" s="1" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B227" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K227" s="14"/>
+        <v>178</v>
+      </c>
+      <c r="K227" s="1"/>
     </row>
     <row r="228" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="229" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7747,53 +7652,53 @@
         <v>35</v>
       </c>
       <c r="I233" s="4" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="J233" s="10" t="s">
-        <v>556</v>
-      </c>
-      <c r="K233" s="12" t="s">
         <v>557</v>
+      </c>
+      <c r="K233" s="0" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B234" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H234" s="1" t="n">
         <v>36</v>
       </c>
       <c r="I234" s="4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="J234" s="10" t="s">
-        <v>561</v>
-      </c>
-      <c r="K234" s="12" t="s">
         <v>562</v>
+      </c>
+      <c r="K234" s="0" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B235" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H235" s="1" t="n">
         <v>37</v>
       </c>
       <c r="I235" s="4" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="J235" s="10" t="s">
-        <v>565</v>
-      </c>
-      <c r="K235" s="12" t="s">
         <v>566</v>
+      </c>
+      <c r="K235" s="0" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7802,23 +7707,23 @@
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="I237" s="4"/>
       <c r="J237" s="10"/>
     </row>
-    <row r="238" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H238" s="1" t="n">
         <v>38</v>
       </c>
       <c r="I238" s="4" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J238" s="4" t="s">
-        <v>568</v>
-      </c>
-      <c r="K238" s="12" t="s">
         <v>569</v>
+      </c>
+      <c r="K238" s="15" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="239" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7826,13 +7731,13 @@
         <v>39</v>
       </c>
       <c r="I239" s="4" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="J239" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="K239" s="14" t="s">
         <v>572</v>
+      </c>
+      <c r="K239" s="4" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7840,13 +7745,13 @@
         <v>40</v>
       </c>
       <c r="I240" s="4" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="J240" s="4" t="s">
-        <v>574</v>
-      </c>
-      <c r="K240" s="12" t="s">
         <v>575</v>
+      </c>
+      <c r="K240" s="15" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7854,52 +7759,52 @@
         <v>41</v>
       </c>
       <c r="I241" s="4" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="J241" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="K241" s="14" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="242" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K241" s="1" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H242" s="1" t="n">
         <v>42</v>
       </c>
       <c r="I242" s="4" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="J242" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="K242" s="12" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="243" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K242" s="15" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H243" s="1" t="n">
         <v>43</v>
       </c>
       <c r="I243" s="4" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="J243" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="K243" s="12" t="s">
         <v>584</v>
+      </c>
+      <c r="K243" s="15" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B244" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J244" s="4"/>
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="J245" s="4"/>
     </row>
@@ -7908,84 +7813,80 @@
         <v>44</v>
       </c>
       <c r="I246" s="4" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="J246" s="10" t="s">
-        <v>586</v>
-      </c>
-      <c r="K246" s="12" t="s">
         <v>587</v>
+      </c>
+      <c r="K246" s="0" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="247" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B247" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K247" s="14"/>
-    </row>
-    <row r="248" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K248" s="14"/>
-    </row>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="248" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="249" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="K249" s="14"/>
-    </row>
-    <row r="250" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="250" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H250" s="1" t="n">
         <v>93</v>
       </c>
       <c r="I250" s="4" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="J250" s="10" t="s">
-        <v>589</v>
-      </c>
-      <c r="K250" s="14" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="251" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K250" s="4" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="251" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H251" s="1" t="n">
         <v>94</v>
       </c>
       <c r="I251" s="4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="J251" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="K251" s="14" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="252" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K251" s="4" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="252" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H252" s="1" t="n">
         <v>95</v>
       </c>
       <c r="I252" s="4" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="J252" s="4" t="s">
-        <v>595</v>
-      </c>
-      <c r="K252" s="14" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="253" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K252" s="4" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="253" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H253" s="1" t="n">
         <v>96</v>
       </c>
       <c r="I253" s="4" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="J253" s="4" t="s">
-        <v>598</v>
-      </c>
-      <c r="K253" s="14" t="s">
         <v>599</v>
+      </c>
+      <c r="K253" s="4" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="254" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7993,13 +7894,13 @@
         <v>97</v>
       </c>
       <c r="I254" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J254" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="K254" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="K254" s="14" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="255" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8007,13 +7908,13 @@
         <v>98</v>
       </c>
       <c r="I255" s="4" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="J255" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="K255" s="14" t="s">
         <v>602</v>
+      </c>
+      <c r="K255" s="1" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="256" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8021,86 +7922,83 @@
         <v>99</v>
       </c>
       <c r="I256" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J256" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="K256" s="14" t="s">
         <v>605</v>
+      </c>
+      <c r="K256" s="4" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="257" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I257" s="4"/>
       <c r="J257" s="4"/>
-      <c r="K257" s="14"/>
     </row>
     <row r="258" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B258" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K258" s="14"/>
+        <v>178</v>
+      </c>
     </row>
     <row r="259" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="K259" s="14"/>
+        <v>105</v>
+      </c>
     </row>
     <row r="260" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H260" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I260" s="4" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="J260" s="10" t="s">
-        <v>607</v>
-      </c>
-      <c r="K260" s="14" t="s">
         <v>608</v>
       </c>
-    </row>
-    <row r="261" s="1" customFormat="true" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K260" s="4" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="261" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H261" s="1" t="n">
         <v>101</v>
       </c>
       <c r="I261" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="J261" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="K261" s="14" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="262" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K261" s="4" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="262" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H262" s="1" t="n">
         <v>102</v>
       </c>
       <c r="I262" s="4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="J262" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="K262" s="14" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="263" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K262" s="4" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="263" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H263" s="1" t="n">
         <v>103</v>
       </c>
       <c r="I263" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="J263" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="K263" s="14" t="s">
         <v>617</v>
+      </c>
+      <c r="K263" s="4" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="264" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8108,48 +8006,44 @@
         <v>104</v>
       </c>
       <c r="I264" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="J264" s="4" t="s">
-        <v>619</v>
-      </c>
-      <c r="K264" s="14" t="s">
         <v>620</v>
+      </c>
+      <c r="K264" s="1" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="265" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I265" s="4"/>
       <c r="J265" s="4"/>
-      <c r="K265" s="14"/>
     </row>
     <row r="266" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B266" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K266" s="14"/>
+        <v>178</v>
+      </c>
     </row>
     <row r="267" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B267" s="4"/>
-      <c r="K267" s="14"/>
     </row>
     <row r="268" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K268" s="14"/>
     </row>
     <row r="269" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H269" s="1" t="n">
         <v>79</v>
       </c>
       <c r="I269" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J269" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="K269" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="K269" s="14" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="270" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8157,55 +8051,55 @@
         <v>80</v>
       </c>
       <c r="I270" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="J270" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="K270" s="14" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="271" s="1" customFormat="true" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K270" s="1" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="271" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H271" s="1" t="n">
         <v>81</v>
       </c>
       <c r="I271" s="4" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="J271" s="4" t="s">
-        <v>625</v>
-      </c>
-      <c r="K271" s="14" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="272" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K271" s="4" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="272" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H272" s="1" t="n">
         <v>82</v>
       </c>
       <c r="I272" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="J272" s="4" t="s">
-        <v>628</v>
-      </c>
-      <c r="K272" s="14" t="s">
         <v>629</v>
       </c>
-    </row>
-    <row r="273" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K272" s="4" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="273" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H273" s="1" t="n">
         <v>83</v>
       </c>
       <c r="I273" s="4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="J273" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="K273" s="14" t="s">
         <v>632</v>
+      </c>
+      <c r="K273" s="4" t="s">
+        <v>633</v>
       </c>
     </row>
     <row r="274" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8213,48 +8107,48 @@
         <v>84</v>
       </c>
       <c r="I274" s="4" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="J274" s="4" t="s">
-        <v>634</v>
-      </c>
-      <c r="K274" s="14" t="s">
         <v>635</v>
+      </c>
+      <c r="K274" s="1" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I275" s="4"/>
       <c r="J275" s="4"/>
-      <c r="K275" s="14"/>
+      <c r="K275" s="1"/>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B276" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K276" s="14"/>
+        <v>178</v>
+      </c>
+      <c r="K276" s="1"/>
     </row>
     <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B277" s="4"/>
-      <c r="K277" s="14"/>
+      <c r="K277" s="1"/>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="K278" s="14"/>
+      <c r="K278" s="1"/>
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H279" s="1" t="n">
         <v>85</v>
       </c>
       <c r="I279" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J279" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="K279" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="K279" s="14" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8262,13 +8156,13 @@
         <v>86</v>
       </c>
       <c r="I280" s="4" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="J280" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="K280" s="14" t="s">
         <v>638</v>
+      </c>
+      <c r="K280" s="1" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8276,55 +8170,55 @@
         <v>87</v>
       </c>
       <c r="I281" s="4" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="J281" s="4" t="s">
-        <v>640</v>
-      </c>
-      <c r="K281" s="14" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="282" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K281" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="282" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H282" s="1" t="n">
         <v>88</v>
       </c>
       <c r="I282" s="4" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="J282" s="4" t="s">
-        <v>643</v>
-      </c>
-      <c r="K282" s="14" t="s">
         <v>644</v>
       </c>
-    </row>
-    <row r="283" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K282" s="1" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="283" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H283" s="1" t="n">
         <v>89</v>
       </c>
       <c r="I283" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="J283" s="4" t="s">
-        <v>646</v>
-      </c>
-      <c r="K283" s="14" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="284" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K283" s="1" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="284" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H284" s="1" t="n">
         <v>90</v>
       </c>
       <c r="I284" s="4" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="J284" s="4" t="s">
-        <v>649</v>
-      </c>
-      <c r="K284" s="14" t="s">
         <v>650</v>
+      </c>
+      <c r="K284" s="1" t="s">
+        <v>651</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8332,13 +8226,13 @@
         <v>91</v>
       </c>
       <c r="I285" s="4" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="J285" s="4" t="s">
-        <v>652</v>
-      </c>
-      <c r="K285" s="14" t="s">
         <v>653</v>
+      </c>
+      <c r="K285" s="1" t="s">
+        <v>654</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8346,39 +8240,39 @@
         <v>92</v>
       </c>
       <c r="I286" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J286" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="K286" s="14" t="s">
         <v>655</v>
+      </c>
+      <c r="K286" s="1" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B287" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K287" s="14"/>
+        <v>178</v>
+      </c>
+      <c r="K287" s="1"/>
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="K289" s="14"/>
+        <v>97</v>
+      </c>
+      <c r="K289" s="1"/>
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H290" s="1" t="n">
         <v>74</v>
       </c>
       <c r="I290" s="4" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="J290" s="10" t="s">
-        <v>657</v>
-      </c>
-      <c r="K290" s="14" t="s">
         <v>658</v>
+      </c>
+      <c r="K290" s="1" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8386,13 +8280,13 @@
         <v>75</v>
       </c>
       <c r="I291" s="4" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="J291" s="4" t="s">
-        <v>660</v>
-      </c>
-      <c r="K291" s="14" t="s">
         <v>661</v>
+      </c>
+      <c r="K291" s="1" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8400,80 +8294,76 @@
         <v>76</v>
       </c>
       <c r="I292" s="4" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="J292" s="4" t="s">
-        <v>663</v>
-      </c>
-      <c r="K292" s="14" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="293" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K292" s="1" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="293" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H293" s="1" t="n">
         <v>77</v>
       </c>
       <c r="I293" s="4" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="J293" s="4" t="s">
-        <v>666</v>
-      </c>
-      <c r="K293" s="14" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="294" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K293" s="1" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="294" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H294" s="1" t="n">
         <v>78</v>
       </c>
       <c r="I294" s="4" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="J294" s="4" t="s">
-        <v>669</v>
-      </c>
-      <c r="K294" s="14" t="s">
         <v>670</v>
+      </c>
+      <c r="K294" s="1" t="s">
+        <v>671</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I295" s="4"/>
       <c r="J295" s="4"/>
-      <c r="K295" s="14"/>
+      <c r="K295" s="1"/>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I296" s="4"/>
       <c r="J296" s="4"/>
-      <c r="K296" s="14"/>
+      <c r="K296" s="1"/>
     </row>
     <row r="297" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B297" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K297" s="14"/>
-    </row>
-    <row r="298" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K298" s="14"/>
-    </row>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="298" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="299" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="K299" s="14"/>
     </row>
     <row r="300" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H300" s="1" t="n">
         <v>66</v>
       </c>
       <c r="I300" s="4" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="J300" s="10" t="s">
-        <v>672</v>
-      </c>
-      <c r="K300" s="14" t="s">
         <v>673</v>
+      </c>
+      <c r="K300" s="4" t="s">
+        <v>674</v>
       </c>
     </row>
     <row r="301" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8481,13 +8371,13 @@
         <v>67</v>
       </c>
       <c r="I301" s="4" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="J301" s="4" t="s">
-        <v>675</v>
-      </c>
-      <c r="K301" s="14" t="s">
         <v>676</v>
+      </c>
+      <c r="K301" s="4" t="s">
+        <v>677</v>
       </c>
     </row>
     <row r="302" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8495,13 +8385,13 @@
         <v>68</v>
       </c>
       <c r="I302" s="4" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="J302" s="4" t="s">
-        <v>678</v>
-      </c>
-      <c r="K302" s="14" t="s">
         <v>679</v>
+      </c>
+      <c r="K302" s="1" t="s">
+        <v>680</v>
       </c>
     </row>
     <row r="303" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8509,55 +8399,55 @@
         <v>69</v>
       </c>
       <c r="I303" s="4" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="J303" s="4" t="s">
-        <v>681</v>
-      </c>
-      <c r="K303" s="14" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="304" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K303" s="4" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="304" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H304" s="1" t="n">
         <v>70</v>
       </c>
       <c r="I304" s="4" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="J304" s="4" t="s">
-        <v>684</v>
-      </c>
-      <c r="K304" s="14" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="305" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K304" s="4" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="305" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H305" s="1" t="n">
         <v>71</v>
       </c>
       <c r="I305" s="4" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="J305" s="4" t="s">
-        <v>687</v>
-      </c>
-      <c r="K305" s="14" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="306" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K305" s="4" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="306" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H306" s="1" t="n">
         <v>72</v>
       </c>
       <c r="I306" s="4" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="J306" s="4" t="s">
-        <v>690</v>
-      </c>
-      <c r="K306" s="14" t="s">
         <v>691</v>
+      </c>
+      <c r="K306" s="4" t="s">
+        <v>692</v>
       </c>
     </row>
     <row r="307" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8565,39 +8455,37 @@
         <v>73</v>
       </c>
       <c r="I307" s="4" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="J307" s="4" t="s">
-        <v>693</v>
-      </c>
-      <c r="K307" s="14" t="s">
         <v>694</v>
+      </c>
+      <c r="K307" s="1" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="308" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B308" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K308" s="14"/>
+        <v>178</v>
+      </c>
     </row>
     <row r="309" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="K309" s="14"/>
     </row>
     <row r="310" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H310" s="1" t="n">
         <v>60</v>
       </c>
       <c r="I310" s="4" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="J310" s="10" t="s">
-        <v>696</v>
-      </c>
-      <c r="K310" s="14" t="s">
         <v>697</v>
+      </c>
+      <c r="K310" s="1" t="s">
+        <v>698</v>
       </c>
     </row>
     <row r="311" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8605,55 +8493,55 @@
         <v>61</v>
       </c>
       <c r="I311" s="4" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="J311" s="4" t="s">
-        <v>699</v>
-      </c>
-      <c r="K311" s="14" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="312" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K311" s="4" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="312" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H312" s="1" t="n">
         <v>62</v>
       </c>
       <c r="I312" s="4" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="J312" s="4" t="s">
-        <v>702</v>
-      </c>
-      <c r="K312" s="14" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="313" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K312" s="4" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="313" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H313" s="1" t="n">
         <v>63</v>
       </c>
       <c r="I313" s="4" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="J313" s="4" t="s">
-        <v>705</v>
-      </c>
-      <c r="K313" s="14" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="314" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K313" s="4" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="314" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H314" s="1" t="n">
         <v>64</v>
       </c>
       <c r="I314" s="4" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="J314" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="K314" s="14" t="s">
         <v>709</v>
+      </c>
+      <c r="K314" s="4" t="s">
+        <v>710</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8661,45 +8549,40 @@
         <v>65</v>
       </c>
       <c r="I315" s="4" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="J315" s="4" t="s">
-        <v>711</v>
-      </c>
-      <c r="K315" s="14" t="s">
         <v>712</v>
+      </c>
+      <c r="K315" s="1" t="s">
+        <v>713</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B316" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K316" s="14"/>
-    </row>
-    <row r="317" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K317" s="14"/>
-    </row>
-    <row r="318" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K318" s="14"/>
-    </row>
+        <v>178</v>
+      </c>
+      <c r="K316" s="1"/>
+    </row>
+    <row r="317" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="318" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="319" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="K319" s="14"/>
     </row>
     <row r="320" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H320" s="1" t="n">
         <v>53</v>
       </c>
       <c r="I320" s="4" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="J320" s="10" t="s">
-        <v>714</v>
-      </c>
-      <c r="K320" s="14" t="s">
         <v>715</v>
+      </c>
+      <c r="K320" s="4" t="s">
+        <v>716</v>
       </c>
     </row>
     <row r="321" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8707,27 +8590,27 @@
         <v>54</v>
       </c>
       <c r="I321" s="4" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="J321" s="10" t="s">
-        <v>717</v>
-      </c>
-      <c r="K321" s="14" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="322" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K321" s="4" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="322" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H322" s="1" t="n">
         <v>55</v>
       </c>
       <c r="I322" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="J322" s="10" t="s">
-        <v>720</v>
-      </c>
-      <c r="K322" s="14" t="s">
         <v>721</v>
+      </c>
+      <c r="K322" s="4" t="s">
+        <v>722</v>
       </c>
     </row>
     <row r="323" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8735,13 +8618,13 @@
         <v>56</v>
       </c>
       <c r="I323" s="4" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="J323" s="10" t="s">
-        <v>723</v>
-      </c>
-      <c r="K323" s="14" t="s">
         <v>724</v>
+      </c>
+      <c r="K323" s="4" t="s">
+        <v>725</v>
       </c>
     </row>
     <row r="324" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8749,27 +8632,27 @@
         <v>57</v>
       </c>
       <c r="I324" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J324" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="K324" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="K324" s="14" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="325" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="325" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H325" s="1" t="n">
         <v>58</v>
       </c>
       <c r="I325" s="4" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="J325" s="10" t="s">
-        <v>726</v>
-      </c>
-      <c r="K325" s="14" t="s">
         <v>727</v>
+      </c>
+      <c r="K325" s="4" t="s">
+        <v>728</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8777,45 +8660,40 @@
         <v>59</v>
       </c>
       <c r="I326" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J326" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="K326" s="14" t="s">
-        <v>655</v>
+        <v>273</v>
+      </c>
+      <c r="K326" s="1" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B327" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K327" s="14"/>
-    </row>
-    <row r="329" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K329" s="14"/>
-    </row>
-    <row r="330" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K330" s="14"/>
-    </row>
+        <v>178</v>
+      </c>
+      <c r="K327" s="1"/>
+    </row>
+    <row r="329" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="330" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="331" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K331" s="14"/>
     </row>
     <row r="332" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H332" s="1" t="n">
         <v>45</v>
       </c>
       <c r="I332" s="4" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="J332" s="10" t="s">
-        <v>729</v>
-      </c>
-      <c r="K332" s="14" t="s">
         <v>730</v>
+      </c>
+      <c r="K332" s="1" t="s">
+        <v>731</v>
       </c>
     </row>
     <row r="333" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8823,55 +8701,55 @@
         <v>46</v>
       </c>
       <c r="I333" s="4" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="J333" s="4" t="s">
-        <v>732</v>
-      </c>
-      <c r="K333" s="14" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="334" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K333" s="4" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="334" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H334" s="1" t="n">
         <v>50</v>
       </c>
       <c r="I334" s="4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>735</v>
-      </c>
-      <c r="K334" s="14" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="335" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K334" s="4" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="335" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H335" s="1" t="n">
         <v>47</v>
       </c>
       <c r="I335" s="4" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="J335" s="10" t="s">
-        <v>738</v>
-      </c>
-      <c r="K335" s="14" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="336" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K335" s="4" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="336" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H336" s="1" t="n">
         <v>48</v>
       </c>
       <c r="I336" s="4" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="J336" s="4" t="s">
-        <v>741</v>
-      </c>
-      <c r="K336" s="14" t="s">
         <v>742</v>
+      </c>
+      <c r="K336" s="4" t="s">
+        <v>743</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8879,45 +8757,40 @@
         <v>49</v>
       </c>
       <c r="I337" s="4" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="J337" s="4" t="s">
-        <v>744</v>
-      </c>
-      <c r="K337" s="14" t="s">
         <v>745</v>
+      </c>
+      <c r="K337" s="1" t="s">
+        <v>746</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B338" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K338" s="14"/>
-    </row>
-    <row r="339" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K339" s="14"/>
-    </row>
-    <row r="340" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K340" s="14"/>
-    </row>
+        <v>178</v>
+      </c>
+      <c r="K338" s="1"/>
+    </row>
+    <row r="339" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="340" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="341" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="K341" s="14"/>
     </row>
     <row r="342" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H342" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I342" s="4" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="J342" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="K342" s="14" t="s">
         <v>748</v>
+      </c>
+      <c r="K342" s="4" t="s">
+        <v>749</v>
       </c>
     </row>
     <row r="343" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8925,27 +8798,27 @@
         <v>2</v>
       </c>
       <c r="I343" s="4" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="J343" s="4" t="s">
-        <v>750</v>
-      </c>
-      <c r="K343" s="14" t="s">
         <v>751</v>
       </c>
-    </row>
-    <row r="344" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K343" s="1" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="344" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H344" s="1" t="n">
         <v>5</v>
       </c>
       <c r="I344" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="J344" s="4" t="s">
-        <v>753</v>
-      </c>
-      <c r="K344" s="14" t="s">
         <v>754</v>
+      </c>
+      <c r="K344" s="4" t="s">
+        <v>755</v>
       </c>
     </row>
     <row r="345" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8953,27 +8826,27 @@
         <v>6</v>
       </c>
       <c r="I345" s="4" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="J345" s="4" t="s">
-        <v>756</v>
-      </c>
-      <c r="K345" s="14" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="346" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K345" s="4" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="346" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H346" s="1" t="n">
         <v>212</v>
       </c>
       <c r="I346" s="4" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="J346" s="4" t="s">
-        <v>759</v>
-      </c>
-      <c r="K346" s="14" t="s">
         <v>760</v>
+      </c>
+      <c r="K346" s="4" t="s">
+        <v>761</v>
       </c>
     </row>
     <row r="347" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8981,13 +8854,13 @@
         <v>52</v>
       </c>
       <c r="I347" s="4" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="J347" s="4" t="s">
-        <v>762</v>
-      </c>
-      <c r="K347" s="14" t="s">
         <v>763</v>
+      </c>
+      <c r="K347" s="4" t="s">
+        <v>764</v>
       </c>
     </row>
     <row r="348" s="1" customFormat="true" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8995,13 +8868,13 @@
         <v>17</v>
       </c>
       <c r="I348" s="4" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="J348" s="4" t="s">
-        <v>765</v>
-      </c>
-      <c r="K348" s="14" t="s">
         <v>766</v>
+      </c>
+      <c r="K348" s="4" t="s">
+        <v>767</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9009,32 +8882,32 @@
         <v>7</v>
       </c>
       <c r="I349" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J349" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="K349" s="14" t="s">
-        <v>655</v>
+        <v>273</v>
+      </c>
+      <c r="K349" s="1" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B350" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K350" s="14"/>
+        <v>178</v>
+      </c>
+      <c r="K350" s="1"/>
     </row>
     <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D353" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9042,156 +8915,156 @@
         <v>8</v>
       </c>
       <c r="I354" s="4" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>770</v>
-      </c>
-      <c r="K354" s="12" t="s">
         <v>771</v>
       </c>
-    </row>
-    <row r="355" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K354" s="15" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="355" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H355" s="1" t="n">
         <v>9</v>
       </c>
       <c r="I355" s="4" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="J355" s="4" t="s">
-        <v>773</v>
-      </c>
-      <c r="K355" s="12" t="s">
         <v>774</v>
+      </c>
+      <c r="K355" s="15" t="s">
+        <v>775</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B356" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H356" s="1" t="n">
         <v>10</v>
       </c>
       <c r="I356" s="4" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="J356" s="4" t="s">
-        <v>776</v>
-      </c>
-      <c r="K356" s="12" t="s">
         <v>777</v>
+      </c>
+      <c r="K356" s="15" t="s">
+        <v>778</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H359" s="1" t="n">
         <v>11</v>
       </c>
       <c r="I359" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="J359" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="K359" s="12" t="s">
         <v>781</v>
+      </c>
+      <c r="K359" s="0" t="s">
+        <v>782</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B360" s="1" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H360" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I360" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="J360" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="K360" s="12" t="s">
         <v>785</v>
+      </c>
+      <c r="K360" s="0" t="s">
+        <v>786</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B361" s="1" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H361" s="1" t="n">
         <v>13</v>
       </c>
       <c r="I361" s="1" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="J361" s="1" t="s">
-        <v>787</v>
-      </c>
-      <c r="K361" s="12" t="s">
         <v>788</v>
+      </c>
+      <c r="K361" s="0" t="s">
+        <v>789</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B362" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H362" s="1" t="n">
         <v>14</v>
       </c>
       <c r="I362" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="J362" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="K362" s="12" t="s">
         <v>792</v>
+      </c>
+      <c r="K362" s="0" t="s">
+        <v>793</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B363" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="1" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H367" s="1" t="n">
         <v>15</v>
       </c>
       <c r="I367" s="1" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="J367" s="1" t="s">
-        <v>795</v>
-      </c>
-      <c r="K367" s="12" t="s">
         <v>796</v>
+      </c>
+      <c r="K367" s="0" t="s">
+        <v>797</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B368" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9199,18 +9072,18 @@
         <v>16</v>
       </c>
       <c r="I372" s="1" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="J372" s="1" t="s">
-        <v>798</v>
-      </c>
-      <c r="K372" s="12" t="s">
         <v>799</v>
+      </c>
+      <c r="K372" s="0" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B373" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/_tutorial.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/_tutorial.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -3536,37 +3536,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -3640,7 +3640,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O39"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="8.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="19.26"/>
@@ -4553,7 +4553,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K373"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="8.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.83"/>
@@ -4659,7 +4659,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H14" s="1" t="n">
         <v>233</v>
       </c>
@@ -4673,7 +4673,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H15" s="1" t="n">
         <v>234</v>
       </c>
@@ -4823,7 +4823,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H28" s="1" t="n">
         <v>225</v>
       </c>
@@ -4837,7 +4837,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H29" s="1" t="n">
         <v>226</v>
       </c>
@@ -4963,7 +4963,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H39" s="1" t="n">
         <v>204</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H40" s="1" t="n">
         <v>205</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H41" s="1" t="n">
         <v>206</v>
       </c>
@@ -5152,7 +5152,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="57" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H57" s="1" t="n">
         <v>196</v>
       </c>
@@ -5166,7 +5166,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="58" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H58" s="1" t="n">
         <v>197</v>
       </c>
@@ -5180,7 +5180,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="59" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H59" s="1" t="n">
         <v>198</v>
       </c>
@@ -5304,7 +5304,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="71" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H71" s="1" t="n">
         <v>189</v>
       </c>
@@ -5399,7 +5399,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="81" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H81" s="1" t="n">
         <v>175</v>
       </c>
@@ -5413,7 +5413,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="82" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H82" s="1" t="n">
         <v>176</v>
       </c>
@@ -5441,7 +5441,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="84" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H84" s="1" t="n">
         <v>178</v>
       </c>
@@ -5455,7 +5455,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="85" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H85" s="1" t="n">
         <v>179</v>
       </c>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="K86" s="1"/>
     </row>
-    <row r="88" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="s">
         <v>113</v>
       </c>
@@ -5566,7 +5566,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="100" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H100" s="1" t="n">
         <v>23</v>
       </c>
@@ -5580,7 +5580,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="101" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H101" s="1" t="n">
         <v>24</v>
       </c>
@@ -5630,7 +5630,7 @@
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
     </row>
-    <row r="106" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -5651,7 +5651,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -5672,7 +5672,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -5693,7 +5693,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="287.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="262.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -5714,7 +5714,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="162" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -5775,7 +5775,7 @@
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
     </row>
-    <row r="114" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -5796,7 +5796,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="115" s="1" customFormat="true" ht="138.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" s="1" customFormat="true" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -5817,7 +5817,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="116" s="1" customFormat="true" ht="196.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" s="1" customFormat="true" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -5838,7 +5838,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="117" s="1" customFormat="true" ht="196.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" s="1" customFormat="true" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -5859,7 +5859,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="118" s="1" customFormat="true" ht="162" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" s="1" customFormat="true" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -5880,7 +5880,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="119" s="1" customFormat="true" ht="162" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" s="1" customFormat="true" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -5950,7 +5950,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="123" s="1" customFormat="true" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" s="1" customFormat="true" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -5971,7 +5971,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="124" s="1" customFormat="true" ht="219.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" s="1" customFormat="true" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -5992,7 +5992,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="125" s="1" customFormat="true" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" s="1" customFormat="true" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -6083,7 +6083,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="130" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" s="1" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -6104,7 +6104,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="131" s="1" customFormat="true" ht="150.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" s="1" customFormat="true" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -6153,7 +6153,7 @@
       <c r="J133" s="4"/>
       <c r="K133" s="4"/>
     </row>
-    <row r="134" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" s="1" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -6174,7 +6174,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="135" s="1" customFormat="true" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" s="1" customFormat="true" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -6195,7 +6195,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="136" s="1" customFormat="true" ht="196.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" s="1" customFormat="true" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -6216,7 +6216,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="137" s="1" customFormat="true" ht="127.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" s="1" customFormat="true" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -6237,7 +6237,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="138" s="1" customFormat="true" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" s="1" customFormat="true" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -6298,7 +6298,7 @@
       <c r="J141" s="4"/>
       <c r="K141" s="4"/>
     </row>
-    <row r="142" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -6319,7 +6319,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="143" s="1" customFormat="true" ht="150.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" s="1" customFormat="true" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -6340,7 +6340,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="144" s="1" customFormat="true" ht="184.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" s="1" customFormat="true" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -6361,7 +6361,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="145" s="1" customFormat="true" ht="138.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" s="1" customFormat="true" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -6382,7 +6382,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="146" s="1" customFormat="true" ht="173.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" s="1" customFormat="true" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -6403,7 +6403,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="147" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -6462,7 +6462,7 @@
       <c r="J150" s="4"/>
       <c r="K150" s="4"/>
     </row>
-    <row r="151" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="4" t="s">
         <v>85</v>
       </c>
@@ -6476,7 +6476,7 @@
       <c r="J151" s="4"/>
       <c r="K151" s="4"/>
     </row>
-    <row r="152" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" s="1" customFormat="true" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -6497,7 +6497,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="153" s="1" customFormat="true" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" s="1" customFormat="true" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4" t="s">
@@ -6520,7 +6520,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="154" s="1" customFormat="true" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" s="1" customFormat="true" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4" t="s">
@@ -6543,7 +6543,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="155" s="1" customFormat="true" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" s="1" customFormat="true" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4" t="s">
@@ -6566,7 +6566,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="156" s="1" customFormat="true" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" s="1" customFormat="true" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -6639,7 +6639,7 @@
       <c r="J160" s="4"/>
       <c r="K160" s="4"/>
     </row>
-    <row r="161" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -6660,7 +6660,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="162" s="1" customFormat="true" ht="127.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" s="1" customFormat="true" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -6681,7 +6681,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="163" s="1" customFormat="true" ht="127.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" s="1" customFormat="true" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -6702,7 +6702,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="164" s="1" customFormat="true" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" s="1" customFormat="true" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -6723,7 +6723,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="165" s="1" customFormat="true" ht="207.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" s="1" customFormat="true" ht="189.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -6744,7 +6744,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="166" s="1" customFormat="true" ht="162" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" s="1" customFormat="true" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -6765,7 +6765,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="167" s="1" customFormat="true" ht="127.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" s="1" customFormat="true" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -6786,7 +6786,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="168" s="1" customFormat="true" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" s="1" customFormat="true" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -6847,7 +6847,7 @@
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
     </row>
-    <row r="172" s="1" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" s="1" customFormat="true" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -6868,7 +6868,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="173" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" s="1" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -6889,7 +6889,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="174" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -6910,7 +6910,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="175" s="1" customFormat="true" ht="162" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" s="1" customFormat="true" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -6931,7 +6931,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="176" s="1" customFormat="true" ht="150.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" s="1" customFormat="true" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -6952,7 +6952,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="177" s="1" customFormat="true" ht="196.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" s="1" customFormat="true" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -7001,7 +7001,7 @@
       <c r="J179" s="4"/>
       <c r="K179" s="4"/>
     </row>
-    <row r="180" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -7022,7 +7022,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="181" s="1" customFormat="true" ht="219.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" s="1" customFormat="true" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -7043,7 +7043,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="182" s="1" customFormat="true" ht="242.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" s="1" customFormat="true" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -7064,7 +7064,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="183" s="1" customFormat="true" ht="242.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" s="1" customFormat="true" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -7085,7 +7085,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="184" s="1" customFormat="true" ht="219.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" s="1" customFormat="true" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -7158,7 +7158,7 @@
       <c r="J188" s="4"/>
       <c r="K188" s="4"/>
     </row>
-    <row r="189" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -7179,7 +7179,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="190" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -7200,7 +7200,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="191" s="1" customFormat="true" ht="150.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" s="1" customFormat="true" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -7221,7 +7221,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="192" s="1" customFormat="true" ht="230.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" s="1" customFormat="true" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -7242,7 +7242,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="193" s="1" customFormat="true" ht="184.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" s="1" customFormat="true" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -7263,7 +7263,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="194" s="1" customFormat="true" ht="219.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" s="1" customFormat="true" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -7284,7 +7284,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="162" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -7342,7 +7342,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="201" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H201" s="1" t="n">
         <v>106</v>
       </c>
@@ -7356,7 +7356,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="202" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H202" s="1" t="n">
         <v>107</v>
       </c>
@@ -7370,7 +7370,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="203" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H203" s="1" t="n">
         <v>108</v>
       </c>
@@ -7384,7 +7384,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="204" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H204" s="1" t="n">
         <v>109</v>
       </c>
@@ -7451,7 +7451,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="211" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H211" s="1" t="n">
         <v>113</v>
       </c>
@@ -7501,7 +7501,7 @@
     <row r="215" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B215" s="4"/>
     </row>
-    <row r="216" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="4" t="s">
         <v>17</v>
       </c>
@@ -7521,7 +7521,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="219" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H219" s="1" t="n">
         <v>27</v>
       </c>
@@ -7535,7 +7535,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="220" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H220" s="1" t="n">
         <v>28</v>
       </c>
@@ -7549,7 +7549,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="221" s="1" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" s="1" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H221" s="1" t="n">
         <v>29</v>
       </c>
@@ -7563,7 +7563,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="222" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H222" s="1" t="n">
         <v>30</v>
       </c>
@@ -7605,7 +7605,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="225" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H225" s="1" t="n">
         <v>33</v>
       </c>
@@ -7712,7 +7712,7 @@
       <c r="I237" s="4"/>
       <c r="J237" s="10"/>
     </row>
-    <row r="238" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H238" s="1" t="n">
         <v>38</v>
       </c>
@@ -7726,7 +7726,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="239" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H239" s="1" t="n">
         <v>39</v>
       </c>
@@ -7740,7 +7740,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H240" s="1" t="n">
         <v>40</v>
       </c>
@@ -7754,7 +7754,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H241" s="1" t="n">
         <v>41</v>
       </c>
@@ -7768,7 +7768,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H242" s="1" t="n">
         <v>42</v>
       </c>
@@ -7782,7 +7782,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H243" s="1" t="n">
         <v>43</v>
       </c>
@@ -7847,7 +7847,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="251" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H251" s="1" t="n">
         <v>94</v>
       </c>
@@ -7861,7 +7861,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="252" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H252" s="1" t="n">
         <v>95</v>
       </c>
@@ -7875,7 +7875,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="253" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H253" s="1" t="n">
         <v>96</v>
       </c>
@@ -7917,7 +7917,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="256" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H256" s="1" t="n">
         <v>99</v>
       </c>
@@ -7959,7 +7959,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="261" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H261" s="1" t="n">
         <v>101</v>
       </c>
@@ -7973,7 +7973,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="262" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="262" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H262" s="1" t="n">
         <v>102</v>
       </c>
@@ -7987,7 +7987,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="263" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H263" s="1" t="n">
         <v>103</v>
       </c>
@@ -8060,7 +8060,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="271" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H271" s="1" t="n">
         <v>81</v>
       </c>
@@ -8074,7 +8074,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="272" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H272" s="1" t="n">
         <v>82</v>
       </c>
@@ -8088,7 +8088,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="273" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H273" s="1" t="n">
         <v>83</v>
       </c>
@@ -8151,7 +8151,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="280" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="280" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H280" s="1" t="n">
         <v>86</v>
       </c>
@@ -8165,7 +8165,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="281" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H281" s="1" t="n">
         <v>87</v>
       </c>
@@ -8179,7 +8179,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="282" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H282" s="1" t="n">
         <v>88</v>
       </c>
@@ -8193,7 +8193,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="283" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H283" s="1" t="n">
         <v>89</v>
       </c>
@@ -8207,7 +8207,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="284" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H284" s="1" t="n">
         <v>90</v>
       </c>
@@ -8221,7 +8221,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="285" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="285" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H285" s="1" t="n">
         <v>91</v>
       </c>
@@ -8275,7 +8275,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="291" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H291" s="1" t="n">
         <v>75</v>
       </c>
@@ -8289,7 +8289,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="292" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="292" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H292" s="1" t="n">
         <v>76</v>
       </c>
@@ -8303,7 +8303,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="293" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="293" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H293" s="1" t="n">
         <v>77</v>
       </c>
@@ -8317,7 +8317,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="294" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="294" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H294" s="1" t="n">
         <v>78</v>
       </c>
@@ -8352,7 +8352,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="300" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H300" s="1" t="n">
         <v>66</v>
       </c>
@@ -8366,7 +8366,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="301" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="301" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H301" s="1" t="n">
         <v>67</v>
       </c>
@@ -8394,7 +8394,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="303" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H303" s="1" t="n">
         <v>69</v>
       </c>
@@ -8408,7 +8408,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="304" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="304" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H304" s="1" t="n">
         <v>70</v>
       </c>
@@ -8422,7 +8422,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="305" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H305" s="1" t="n">
         <v>71</v>
       </c>
@@ -8436,7 +8436,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="306" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H306" s="1" t="n">
         <v>72</v>
       </c>
@@ -8450,7 +8450,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="307" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="307" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H307" s="1" t="n">
         <v>73</v>
       </c>
@@ -8488,7 +8488,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="311" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="311" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H311" s="1" t="n">
         <v>61</v>
       </c>
@@ -8502,7 +8502,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="312" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="312" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H312" s="1" t="n">
         <v>62</v>
       </c>
@@ -8516,7 +8516,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="313" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H313" s="1" t="n">
         <v>63</v>
       </c>
@@ -8530,7 +8530,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="314" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H314" s="1" t="n">
         <v>64</v>
       </c>
@@ -8544,7 +8544,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="315" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H315" s="1" t="n">
         <v>65</v>
       </c>
@@ -8696,7 +8696,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="333" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="333" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H333" s="1" t="n">
         <v>46</v>
       </c>
@@ -8710,7 +8710,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="334" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="334" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H334" s="1" t="n">
         <v>50</v>
       </c>
@@ -8724,7 +8724,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="335" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="335" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H335" s="1" t="n">
         <v>47</v>
       </c>
@@ -8738,7 +8738,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="336" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="336" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H336" s="1" t="n">
         <v>48</v>
       </c>
@@ -8752,7 +8752,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="337" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="337" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H337" s="1" t="n">
         <v>49</v>
       </c>
@@ -8779,7 +8779,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="342" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="342" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H342" s="1" t="n">
         <v>1</v>
       </c>
@@ -8793,7 +8793,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="343" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="343" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H343" s="1" t="n">
         <v>2</v>
       </c>
@@ -8807,7 +8807,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="344" s="1" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="344" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H344" s="1" t="n">
         <v>5</v>
       </c>
@@ -8821,7 +8821,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="345" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="345" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H345" s="1" t="n">
         <v>6</v>
       </c>
@@ -8835,7 +8835,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="346" s="1" customFormat="true" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="346" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H346" s="1" t="n">
         <v>212</v>
       </c>
@@ -8849,7 +8849,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="347" s="1" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="347" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H347" s="1" t="n">
         <v>52</v>
       </c>
@@ -8863,7 +8863,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="348" s="1" customFormat="true" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" s="1" customFormat="true" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H348" s="1" t="n">
         <v>17</v>
       </c>
@@ -8910,7 +8910,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="354" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H354" s="1" t="n">
         <v>8</v>
       </c>
@@ -8924,7 +8924,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="355" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H355" s="1" t="n">
         <v>9</v>
       </c>
@@ -8938,7 +8938,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="356" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="356" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B356" s="1" t="s">
         <v>178</v>
       </c>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/_tutorial.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/_tutorial.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="803">
   <si>
     <t xml:space="preserve">version</t>
   </si>
@@ -1604,6 +1604,12 @@
   <si>
     <t xml:space="preserve">엇, 너 한 번도 안 죽었구나?
 장하다 장해. 자, 쓰담~쓰담~!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">getAchievement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NERUN2</t>
   </si>
   <si>
     <t xml:space="preserve">nerun_nadenade2</t>
@@ -4552,7 +4558,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K373"/>
+  <dimension ref="A1:K374"/>
   <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="8.83"/>
@@ -6520,74 +6526,71 @@
         <v>410</v>
       </c>
     </row>
-    <row r="154" s="1" customFormat="true" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="D154" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="D154" s="4"/>
-      <c r="E154" s="4"/>
+      <c r="E154" s="4" t="s">
+        <v>412</v>
+      </c>
       <c r="F154" s="4"/>
       <c r="G154" s="4"/>
-      <c r="H154" s="1" t="n">
-        <v>231</v>
-      </c>
-      <c r="I154" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="J154" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="K154" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="155" s="1" customFormat="true" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I154" s="12"/>
+      <c r="J154" s="10"/>
+      <c r="K154" s="4"/>
+    </row>
+    <row r="155" s="1" customFormat="true" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
       <c r="F155" s="4"/>
       <c r="G155" s="4"/>
       <c r="H155" s="1" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I155" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="J155" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="J155" s="10" t="s">
+      <c r="K155" s="4" t="s">
         <v>416</v>
-      </c>
-      <c r="K155" s="4" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="156" s="1" customFormat="true" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
-      <c r="C156" s="4"/>
+      <c r="C156" s="4" t="s">
+        <v>413</v>
+      </c>
       <c r="D156" s="4"/>
       <c r="E156" s="4"/>
       <c r="F156" s="4"/>
       <c r="G156" s="4"/>
       <c r="H156" s="1" t="n">
-        <v>128</v>
-      </c>
-      <c r="I156" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="I156" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="J156" s="10" t="s">
         <v>418</v>
       </c>
-      <c r="J156" s="4" t="s">
+      <c r="K156" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="K156" s="4" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="157" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="157" s="1" customFormat="true" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -6595,15 +6598,22 @@
       <c r="E157" s="4"/>
       <c r="F157" s="4"/>
       <c r="G157" s="4"/>
-      <c r="I157" s="4"/>
-      <c r="J157" s="4"/>
-      <c r="K157" s="4"/>
+      <c r="H157" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="I157" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="J157" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="K157" s="4" t="s">
+        <v>422</v>
+      </c>
     </row>
     <row r="158" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="4"/>
-      <c r="B158" s="4" t="s">
-        <v>178</v>
-      </c>
+      <c r="B158" s="4"/>
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
@@ -6615,7 +6625,9 @@
     </row>
     <row r="159" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="4"/>
-      <c r="B159" s="4"/>
+      <c r="B159" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
@@ -6626,9 +6638,7 @@
       <c r="K159" s="4"/>
     </row>
     <row r="160" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="4" t="s">
-        <v>129</v>
-      </c>
+      <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
@@ -6639,28 +6649,21 @@
       <c r="J160" s="4"/>
       <c r="K160" s="4"/>
     </row>
-    <row r="161" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="4"/>
+    <row r="161" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="4" t="s">
+        <v>129</v>
+      </c>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
       <c r="F161" s="4"/>
       <c r="G161" s="4"/>
-      <c r="H161" s="1" t="n">
-        <v>129</v>
-      </c>
-      <c r="I161" s="12" t="s">
-        <v>421</v>
-      </c>
-      <c r="J161" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="K161" s="4" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="162" s="1" customFormat="true" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I161" s="4"/>
+      <c r="J161" s="4"/>
+      <c r="K161" s="4"/>
+    </row>
+    <row r="162" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -6669,16 +6672,16 @@
       <c r="F162" s="4"/>
       <c r="G162" s="4"/>
       <c r="H162" s="1" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I162" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="J162" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="J162" s="4" t="s">
+      <c r="K162" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="K162" s="4" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="163" s="1" customFormat="true" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6690,19 +6693,19 @@
       <c r="F163" s="4"/>
       <c r="G163" s="4"/>
       <c r="H163" s="1" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I163" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="J163" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="J163" s="4" t="s">
+      <c r="K163" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="K163" s="4" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="164" s="1" customFormat="true" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="164" s="1" customFormat="true" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -6711,19 +6714,19 @@
       <c r="F164" s="4"/>
       <c r="G164" s="4"/>
       <c r="H164" s="1" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I164" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="J164" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="J164" s="4" t="s">
+      <c r="K164" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="K164" s="4" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="165" s="1" customFormat="true" ht="189.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="165" s="1" customFormat="true" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -6732,19 +6735,19 @@
       <c r="F165" s="4"/>
       <c r="G165" s="4"/>
       <c r="H165" s="1" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I165" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="J165" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="J165" s="4" t="s">
+      <c r="K165" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="K165" s="4" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="166" s="1" customFormat="true" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="166" s="1" customFormat="true" ht="189.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -6753,19 +6756,19 @@
       <c r="F166" s="4"/>
       <c r="G166" s="4"/>
       <c r="H166" s="1" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I166" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="J166" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="J166" s="4" t="s">
+      <c r="K166" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="K166" s="4" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="167" s="1" customFormat="true" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="167" s="1" customFormat="true" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -6774,19 +6777,19 @@
       <c r="F167" s="4"/>
       <c r="G167" s="4"/>
       <c r="H167" s="1" t="n">
-        <v>135</v>
-      </c>
-      <c r="I167" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="I167" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="J167" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="J167" s="4" t="s">
+      <c r="K167" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="K167" s="4" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="168" s="1" customFormat="true" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="168" s="1" customFormat="true" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -6795,35 +6798,44 @@
       <c r="F168" s="4"/>
       <c r="G168" s="4"/>
       <c r="H168" s="1" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I168" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="J168" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="J168" s="4" t="s">
+      <c r="K168" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="K168" s="4" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="169" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="169" s="1" customFormat="true" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="4"/>
-      <c r="B169" s="4" t="s">
-        <v>178</v>
-      </c>
+      <c r="B169" s="4"/>
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
       <c r="F169" s="4"/>
       <c r="G169" s="4"/>
-      <c r="I169" s="4"/>
-      <c r="J169" s="4"/>
-      <c r="K169" s="4"/>
+      <c r="H169" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="I169" s="14" t="s">
+        <v>444</v>
+      </c>
+      <c r="J169" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="K169" s="4" t="s">
+        <v>446</v>
+      </c>
     </row>
     <row r="170" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="4"/>
-      <c r="B170" s="4"/>
+      <c r="B170" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="C170" s="4"/>
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
@@ -6834,9 +6846,7 @@
       <c r="K170" s="4"/>
     </row>
     <row r="171" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="4" t="s">
-        <v>21</v>
-      </c>
+      <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
       <c r="D171" s="4"/>
@@ -6847,28 +6857,21 @@
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
     </row>
-    <row r="172" s="1" customFormat="true" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="4"/>
+    <row r="172" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
       <c r="F172" s="4"/>
       <c r="G172" s="4"/>
-      <c r="H172" s="1" t="n">
-        <v>137</v>
-      </c>
-      <c r="I172" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="J172" s="10" t="s">
-        <v>446</v>
-      </c>
-      <c r="K172" s="4" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="173" s="1" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I172" s="4"/>
+      <c r="J172" s="4"/>
+      <c r="K172" s="4"/>
+    </row>
+    <row r="173" s="1" customFormat="true" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -6877,19 +6880,19 @@
       <c r="F173" s="4"/>
       <c r="G173" s="4"/>
       <c r="H173" s="1" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I173" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="J173" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="J173" s="10" t="s">
+      <c r="K173" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="K173" s="4" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="174" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="174" s="1" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -6898,19 +6901,19 @@
       <c r="F174" s="4"/>
       <c r="G174" s="4"/>
       <c r="H174" s="1" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I174" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="J174" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="J174" s="10" t="s">
+      <c r="K174" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="K174" s="4" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="175" s="1" customFormat="true" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="175" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -6919,19 +6922,19 @@
       <c r="F175" s="4"/>
       <c r="G175" s="4"/>
       <c r="H175" s="1" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I175" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="J175" s="10" t="s">
         <v>454</v>
       </c>
-      <c r="J175" s="10" t="s">
+      <c r="K175" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="K175" s="4" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="176" s="1" customFormat="true" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="176" s="1" customFormat="true" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -6940,19 +6943,19 @@
       <c r="F176" s="4"/>
       <c r="G176" s="4"/>
       <c r="H176" s="1" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I176" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="J176" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="J176" s="10" t="s">
+      <c r="K176" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="K176" s="4" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="177" s="1" customFormat="true" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="177" s="1" customFormat="true" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -6961,37 +6964,44 @@
       <c r="F177" s="4"/>
       <c r="G177" s="4"/>
       <c r="H177" s="1" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I177" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="J177" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="J177" s="10" t="s">
+      <c r="K177" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="K177" s="4" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="178" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="178" s="1" customFormat="true" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="4"/>
-      <c r="B178" s="4" t="s">
-        <v>178</v>
-      </c>
+      <c r="B178" s="4"/>
       <c r="C178" s="4"/>
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
       <c r="F178" s="4"/>
       <c r="G178" s="4"/>
-      <c r="I178" s="4"/>
-      <c r="J178" s="4"/>
-      <c r="K178" s="4"/>
+      <c r="H178" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="I178" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="J178" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="K178" s="4" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="179" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B179" s="4"/>
+      <c r="A179" s="4"/>
+      <c r="B179" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="C179" s="4"/>
       <c r="D179" s="4"/>
       <c r="E179" s="4"/>
@@ -7001,28 +7011,21 @@
       <c r="J179" s="4"/>
       <c r="K179" s="4"/>
     </row>
-    <row r="180" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="4"/>
+    <row r="180" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="4" t="s">
+        <v>117</v>
+      </c>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
       <c r="D180" s="4"/>
       <c r="E180" s="4"/>
       <c r="F180" s="4"/>
       <c r="G180" s="4"/>
-      <c r="H180" s="1" t="n">
-        <v>143</v>
-      </c>
-      <c r="I180" s="12" t="s">
-        <v>463</v>
-      </c>
-      <c r="J180" s="10" t="s">
-        <v>464</v>
-      </c>
-      <c r="K180" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="181" s="1" customFormat="true" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I180" s="4"/>
+      <c r="J180" s="4"/>
+      <c r="K180" s="4"/>
+    </row>
+    <row r="181" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -7031,19 +7034,19 @@
       <c r="F181" s="4"/>
       <c r="G181" s="4"/>
       <c r="H181" s="1" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I181" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="J181" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="J181" s="4" t="s">
+      <c r="K181" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="K181" s="4" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="182" s="1" customFormat="true" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="182" s="1" customFormat="true" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -7052,16 +7055,16 @@
       <c r="F182" s="4"/>
       <c r="G182" s="4"/>
       <c r="H182" s="1" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I182" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="J182" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="J182" s="4" t="s">
+      <c r="K182" s="4" t="s">
         <v>470</v>
-      </c>
-      <c r="K182" s="4" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="183" s="1" customFormat="true" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7073,19 +7076,19 @@
       <c r="F183" s="4"/>
       <c r="G183" s="4"/>
       <c r="H183" s="1" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I183" s="12" t="s">
+        <v>471</v>
+      </c>
+      <c r="J183" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="J183" s="4" t="s">
+      <c r="K183" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="K183" s="4" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="184" s="1" customFormat="true" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="184" s="1" customFormat="true" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -7094,19 +7097,19 @@
       <c r="F184" s="4"/>
       <c r="G184" s="4"/>
       <c r="H184" s="1" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I184" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="J184" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="J184" s="4" t="s">
+      <c r="K184" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="K184" s="4" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="185" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="185" s="1" customFormat="true" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -7114,9 +7117,18 @@
       <c r="E185" s="4"/>
       <c r="F185" s="4"/>
       <c r="G185" s="4"/>
-      <c r="I185" s="4"/>
-      <c r="J185" s="4"/>
-      <c r="K185" s="4"/>
+      <c r="H185" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="I185" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="J185" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="K185" s="4" t="s">
+        <v>479</v>
+      </c>
     </row>
     <row r="186" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="4"/>
@@ -7132,9 +7144,7 @@
     </row>
     <row r="187" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="4"/>
-      <c r="B187" s="4" t="s">
-        <v>178</v>
-      </c>
+      <c r="B187" s="4"/>
       <c r="C187" s="4"/>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
@@ -7145,10 +7155,10 @@
       <c r="K187" s="4"/>
     </row>
     <row r="188" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B188" s="4"/>
+      <c r="A188" s="4"/>
+      <c r="B188" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="C188" s="4"/>
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
@@ -7158,28 +7168,21 @@
       <c r="J188" s="4"/>
       <c r="K188" s="4"/>
     </row>
-    <row r="189" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="4"/>
+    <row r="189" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
       <c r="F189" s="4"/>
       <c r="G189" s="4"/>
-      <c r="H189" s="1" t="n">
-        <v>148</v>
-      </c>
-      <c r="I189" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="J189" s="10" t="s">
-        <v>479</v>
-      </c>
-      <c r="K189" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="190" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I189" s="4"/>
+      <c r="J189" s="4"/>
+      <c r="K189" s="4"/>
+    </row>
+    <row r="190" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -7188,19 +7191,19 @@
       <c r="F190" s="4"/>
       <c r="G190" s="4"/>
       <c r="H190" s="1" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I190" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="J190" s="10" t="s">
         <v>481</v>
       </c>
-      <c r="J190" s="4" t="s">
+      <c r="K190" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="K190" s="4" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="191" s="1" customFormat="true" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="191" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -7209,19 +7212,19 @@
       <c r="F191" s="4"/>
       <c r="G191" s="4"/>
       <c r="H191" s="1" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I191" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="J191" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="J191" s="4" t="s">
+      <c r="K191" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="K191" s="4" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="192" s="1" customFormat="true" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="192" s="1" customFormat="true" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -7230,19 +7233,19 @@
       <c r="F192" s="4"/>
       <c r="G192" s="4"/>
       <c r="H192" s="1" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I192" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="J192" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="J192" s="4" t="s">
+      <c r="K192" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="K192" s="4" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="193" s="1" customFormat="true" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="193" s="1" customFormat="true" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -7251,19 +7254,19 @@
       <c r="F193" s="4"/>
       <c r="G193" s="4"/>
       <c r="H193" s="1" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I193" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="J193" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="J193" s="4" t="s">
+      <c r="K193" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="K193" s="4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="194" s="1" customFormat="true" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="194" s="1" customFormat="true" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -7272,19 +7275,19 @@
       <c r="F194" s="4"/>
       <c r="G194" s="4"/>
       <c r="H194" s="1" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I194" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="J194" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="J194" s="4" t="s">
+      <c r="K194" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="K194" s="4" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="195" customFormat="false" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="195" s="1" customFormat="true" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -7293,954 +7296,961 @@
       <c r="F195" s="4"/>
       <c r="G195" s="4"/>
       <c r="H195" s="1" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I195" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="J195" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="J195" s="4" t="s">
+      <c r="K195" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="K195" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="196" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="196" customFormat="false" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="4"/>
-      <c r="B196" s="4" t="s">
-        <v>178</v>
-      </c>
+      <c r="B196" s="4"/>
       <c r="C196" s="4"/>
       <c r="D196" s="4"/>
       <c r="E196" s="4"/>
       <c r="F196" s="4"/>
       <c r="G196" s="4"/>
-      <c r="I196" s="4"/>
-      <c r="J196" s="4"/>
-      <c r="K196" s="4"/>
+      <c r="H196" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="I196" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="J196" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="K196" s="4" t="s">
+        <v>500</v>
+      </c>
     </row>
     <row r="197" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B197" s="4"/>
+      <c r="A197" s="4"/>
+      <c r="B197" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C197" s="4"/>
+      <c r="D197" s="4"/>
+      <c r="E197" s="4"/>
+      <c r="F197" s="4"/>
+      <c r="G197" s="4"/>
+      <c r="I197" s="4"/>
+      <c r="J197" s="4"/>
+      <c r="K197" s="4"/>
     </row>
     <row r="198" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="4" t="s">
+      <c r="B198" s="4"/>
+    </row>
+    <row r="199" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="199" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="200" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H200" s="1" t="n">
+    <row r="200" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="201" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H201" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="I200" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="J200" s="10" t="s">
-        <v>500</v>
-      </c>
-      <c r="K200" s="1" t="s">
+      <c r="I201" s="4" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="201" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H201" s="1" t="n">
+      <c r="J201" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="K201" s="1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="202" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H202" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="I201" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="J201" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="K201" s="4" t="s">
+      <c r="I202" s="4" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="202" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H202" s="1" t="n">
-        <v>107</v>
-      </c>
-      <c r="I202" s="4" t="s">
+      <c r="J202" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="J202" s="4" t="s">
+      <c r="K202" s="4" t="s">
         <v>506</v>
-      </c>
-      <c r="K202" s="4" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="203" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H203" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="I203" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="J203" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="K203" s="4" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="204" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H204" s="1" t="n">
         <v>108</v>
       </c>
-      <c r="I203" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="J203" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="K203" s="4" t="s">
+      <c r="I204" s="4" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="204" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H204" s="1" t="n">
+      <c r="J204" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="K204" s="4" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="205" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H205" s="1" t="n">
         <v>109</v>
       </c>
-      <c r="I204" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="J204" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="K204" s="4" t="s">
+      <c r="I205" s="4" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="205" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B205" s="4" t="s">
+      <c r="J205" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="K205" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="206" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B206" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="206" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="4" t="s">
+    <row r="207" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="207" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="208" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H208" s="1" t="n">
+    <row r="208" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="209" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H209" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="I208" s="4" t="s">
-        <v>514</v>
-      </c>
-      <c r="J208" s="10" t="s">
-        <v>515</v>
-      </c>
-      <c r="K208" s="1" t="s">
+      <c r="I209" s="4" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="209" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H209" s="1" t="n">
-        <v>111</v>
-      </c>
-      <c r="I209" s="4" t="s">
+      <c r="J209" s="10" t="s">
         <v>517</v>
       </c>
-      <c r="J209" s="10" t="s">
+      <c r="K209" s="1" t="s">
         <v>518</v>
-      </c>
-      <c r="K209" s="4" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="210" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H210" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="I210" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="J210" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="K210" s="4" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="211" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H211" s="1" t="n">
         <v>112</v>
       </c>
-      <c r="I210" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="J210" s="10" t="s">
-        <v>521</v>
-      </c>
-      <c r="K210" s="4" t="s">
+      <c r="I211" s="4" t="s">
         <v>522</v>
       </c>
-    </row>
-    <row r="211" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H211" s="1" t="n">
+      <c r="J211" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="K211" s="4" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="212" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H212" s="1" t="n">
         <v>113</v>
       </c>
-      <c r="I211" s="4" t="s">
-        <v>523</v>
-      </c>
-      <c r="J211" s="10" t="s">
-        <v>524</v>
-      </c>
-      <c r="K211" s="4" t="s">
+      <c r="I212" s="4" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="212" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H212" s="1" t="n">
+      <c r="J212" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="K212" s="4" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="213" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H213" s="1" t="n">
         <v>114</v>
       </c>
-      <c r="I212" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="J212" s="10" t="s">
-        <v>527</v>
-      </c>
-      <c r="K212" s="4" t="s">
+      <c r="I213" s="4" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="213" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H213" s="1" t="n">
+      <c r="J213" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="K213" s="4" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H214" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="I213" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="J213" s="10" t="s">
-        <v>530</v>
-      </c>
-      <c r="K213" s="1" t="s">
+      <c r="I214" s="4" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="214" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B214" s="4" t="s">
+      <c r="J214" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="K214" s="1" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="215" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B215" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="215" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B215" s="4"/>
-    </row>
-    <row r="216" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="4" t="s">
+    <row r="216" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B216" s="4"/>
+    </row>
+    <row r="217" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="217" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="218" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H218" s="1" t="n">
+    <row r="218" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="219" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H219" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="I218" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="J218" s="10" t="s">
-        <v>533</v>
-      </c>
-      <c r="K218" s="1" t="s">
+      <c r="I219" s="4" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="219" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H219" s="1" t="n">
+      <c r="J219" s="10" t="s">
+        <v>535</v>
+      </c>
+      <c r="K219" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="220" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H220" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="I219" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="J219" s="4" t="s">
-        <v>536</v>
-      </c>
-      <c r="K219" s="4" t="s">
+      <c r="I220" s="4" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="220" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H220" s="1" t="n">
+      <c r="J220" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="K220" s="4" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="221" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H221" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="I220" s="4" t="s">
-        <v>538</v>
-      </c>
-      <c r="J220" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="K220" s="4" t="s">
+      <c r="I221" s="4" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="221" s="1" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H221" s="1" t="n">
+      <c r="J221" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="K221" s="4" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="222" s="1" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H222" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="I221" s="4" t="s">
-        <v>541</v>
-      </c>
-      <c r="J221" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="K221" s="4" t="s">
+      <c r="I222" s="4" t="s">
         <v>543</v>
       </c>
-    </row>
-    <row r="222" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H222" s="1" t="n">
+      <c r="J222" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="K222" s="4" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="223" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H223" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="I222" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="J222" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="K222" s="4" t="s">
+      <c r="I223" s="4" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="223" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H223" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="I223" s="4" t="s">
+      <c r="J223" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="J223" s="4" t="s">
+      <c r="K223" s="4" t="s">
         <v>548</v>
-      </c>
-      <c r="K223" s="1" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="224" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H224" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I224" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="J224" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="K224" s="1" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="225" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H225" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="I224" s="4" t="s">
+      <c r="I225" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="J224" s="4" t="s">
+      <c r="J225" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="K224" s="1" t="s">
+      <c r="K225" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="225" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H225" s="1" t="n">
+    <row r="226" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H226" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="I225" s="4" t="s">
-        <v>550</v>
-      </c>
-      <c r="J225" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="K225" s="4" t="s">
+      <c r="I226" s="4" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H226" s="1" t="n">
+      <c r="J226" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="K226" s="4" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H227" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="I226" s="4" t="s">
-        <v>553</v>
-      </c>
-      <c r="J226" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="K226" s="1" t="s">
+      <c r="I227" s="4" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B227" s="4" t="s">
+      <c r="J227" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="K227" s="1" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B228" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="K227" s="1"/>
-    </row>
-    <row r="228" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="K228" s="1"/>
+    </row>
     <row r="229" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="230" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="1" t="s">
+    <row r="231" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H233" s="1" t="n">
+    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H234" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="I233" s="4" t="s">
-        <v>556</v>
-      </c>
-      <c r="J233" s="10" t="s">
-        <v>557</v>
-      </c>
-      <c r="K233" s="0" t="s">
+      <c r="I234" s="4" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B234" s="1" t="s">
+      <c r="J234" s="10" t="s">
         <v>559</v>
       </c>
-      <c r="D234" s="1" t="s">
+      <c r="K234" s="0" t="s">
         <v>560</v>
-      </c>
-      <c r="H234" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="I234" s="4" t="s">
-        <v>561</v>
-      </c>
-      <c r="J234" s="10" t="s">
-        <v>562</v>
-      </c>
-      <c r="K234" s="0" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B235" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="H235" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="I235" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="J235" s="10" t="s">
         <v>564</v>
       </c>
-      <c r="D235" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="H235" s="1" t="n">
+      <c r="K235" s="0" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B236" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="H236" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="I235" s="4" t="s">
-        <v>565</v>
-      </c>
-      <c r="J235" s="10" t="s">
-        <v>566</v>
-      </c>
-      <c r="K235" s="0" t="s">
+      <c r="I236" s="4" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I236" s="4"/>
-      <c r="J236" s="10"/>
+      <c r="J236" s="10" t="s">
+        <v>568</v>
+      </c>
+      <c r="K236" s="0" t="s">
+        <v>569</v>
+      </c>
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="1" t="s">
-        <v>559</v>
-      </c>
       <c r="I237" s="4"/>
       <c r="J237" s="10"/>
     </row>
-    <row r="238" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H238" s="1" t="n">
+    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="I238" s="4"/>
+      <c r="J238" s="10"/>
+    </row>
+    <row r="239" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H239" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="I238" s="4" t="s">
-        <v>568</v>
-      </c>
-      <c r="J238" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="K238" s="15" t="s">
+      <c r="I239" s="4" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="239" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H239" s="1" t="n">
+      <c r="J239" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="K239" s="15" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="240" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H240" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="I239" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="J239" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="K239" s="4" t="s">
+      <c r="I240" s="4" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="240" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H240" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="I240" s="4" t="s">
+      <c r="J240" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="J240" s="4" t="s">
+      <c r="K240" s="4" t="s">
         <v>575</v>
-      </c>
-      <c r="K240" s="15" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H241" s="1" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I241" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="J241" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="J241" s="4" t="s">
+      <c r="K241" s="15" t="s">
         <v>578</v>
-      </c>
-      <c r="K241" s="1" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H242" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="I242" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="J242" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="K242" s="1" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H243" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="I242" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="J242" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="K242" s="15" t="s">
+      <c r="I243" s="4" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="243" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H243" s="1" t="n">
+      <c r="J243" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="K243" s="15" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H244" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="I243" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="J243" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="K243" s="15" t="s">
+      <c r="I244" s="4" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B244" s="1" t="s">
+      <c r="J244" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="K244" s="15" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B245" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="J244" s="4"/>
-    </row>
-    <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="1" t="s">
-        <v>564</v>
-      </c>
       <c r="J245" s="4"/>
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H246" s="1" t="n">
+      <c r="A246" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="J246" s="4"/>
+    </row>
+    <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H247" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="I246" s="4" t="s">
-        <v>586</v>
-      </c>
-      <c r="J246" s="10" t="s">
-        <v>587</v>
-      </c>
-      <c r="K246" s="0" t="s">
+      <c r="I247" s="4" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="247" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B247" s="1" t="s">
+      <c r="J247" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="K247" s="0" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="248" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B248" s="1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="248" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="249" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="4" t="s">
+    <row r="249" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="250" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="4" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="250" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H250" s="1" t="n">
+    <row r="251" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H251" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="I250" s="4" t="s">
-        <v>589</v>
-      </c>
-      <c r="J250" s="10" t="s">
-        <v>590</v>
-      </c>
-      <c r="K250" s="4" t="s">
+      <c r="I251" s="4" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="251" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H251" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="I251" s="4" t="s">
+      <c r="J251" s="10" t="s">
         <v>592</v>
       </c>
-      <c r="J251" s="4" t="s">
+      <c r="K251" s="4" t="s">
         <v>593</v>
-      </c>
-      <c r="K251" s="4" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="252" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H252" s="1" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I252" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="J252" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="J252" s="4" t="s">
+      <c r="K252" s="4" t="s">
         <v>596</v>
-      </c>
-      <c r="K252" s="4" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="253" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H253" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="I253" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="J253" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="K253" s="4" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="254" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H254" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="I253" s="4" t="s">
-        <v>598</v>
-      </c>
-      <c r="J253" s="4" t="s">
-        <v>599</v>
-      </c>
-      <c r="K253" s="4" t="s">
+      <c r="I254" s="4" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="254" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H254" s="1" t="n">
-        <v>97</v>
-      </c>
-      <c r="I254" s="4" t="s">
-        <v>161</v>
-      </c>
       <c r="J254" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="K254" s="1" t="s">
-        <v>161</v>
+        <v>601</v>
+      </c>
+      <c r="K254" s="4" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="255" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H255" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="I255" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="J255" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="K255" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="256" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H256" s="1" t="n">
         <v>98</v>
       </c>
-      <c r="I255" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="J255" s="4" t="s">
-        <v>602</v>
-      </c>
-      <c r="K255" s="1" t="s">
+      <c r="I256" s="4" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="256" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H256" s="1" t="n">
+      <c r="J256" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="K256" s="1" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="257" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H257" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="I256" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="J256" s="4" t="s">
-        <v>605</v>
-      </c>
-      <c r="K256" s="4" t="s">
+      <c r="I257" s="4" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="257" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I257" s="4"/>
-      <c r="J257" s="4"/>
+      <c r="J257" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="K257" s="4" t="s">
+        <v>608</v>
+      </c>
     </row>
     <row r="258" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B258" s="4" t="s">
+      <c r="I258" s="4"/>
+      <c r="J258" s="4"/>
+    </row>
+    <row r="259" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B259" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="259" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="4" t="s">
+    <row r="260" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="4" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="260" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H260" s="1" t="n">
+    <row r="261" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H261" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="I260" s="4" t="s">
-        <v>607</v>
-      </c>
-      <c r="J260" s="10" t="s">
-        <v>608</v>
-      </c>
-      <c r="K260" s="4" t="s">
+      <c r="I261" s="4" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="261" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H261" s="1" t="n">
+      <c r="J261" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="K261" s="4" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="262" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H262" s="1" t="n">
         <v>101</v>
       </c>
-      <c r="I261" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="J261" s="4" t="s">
-        <v>611</v>
-      </c>
-      <c r="K261" s="4" t="s">
+      <c r="I262" s="4" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="262" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H262" s="1" t="n">
+      <c r="J262" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="K262" s="4" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="263" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H263" s="1" t="n">
         <v>102</v>
       </c>
-      <c r="I262" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="J262" s="4" t="s">
-        <v>614</v>
-      </c>
-      <c r="K262" s="4" t="s">
+      <c r="I263" s="4" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="263" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H263" s="1" t="n">
+      <c r="J263" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="K263" s="4" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="264" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H264" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="I263" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="J263" s="4" t="s">
-        <v>617</v>
-      </c>
-      <c r="K263" s="4" t="s">
+      <c r="I264" s="4" t="s">
         <v>618</v>
       </c>
-    </row>
-    <row r="264" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H264" s="1" t="n">
+      <c r="J264" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="K264" s="4" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="265" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H265" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="I264" s="4" t="s">
-        <v>619</v>
-      </c>
-      <c r="J264" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="K264" s="1" t="s">
+      <c r="I265" s="4" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="265" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I265" s="4"/>
-      <c r="J265" s="4"/>
+      <c r="J265" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="K265" s="1" t="s">
+        <v>623</v>
+      </c>
     </row>
     <row r="266" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B266" s="4" t="s">
+      <c r="I266" s="4"/>
+      <c r="J266" s="4"/>
+    </row>
+    <row r="267" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B267" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="267" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B267" s="4"/>
-    </row>
     <row r="268" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="4" t="s">
+      <c r="B268" s="4"/>
+    </row>
+    <row r="269" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="4" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="269" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H269" s="1" t="n">
-        <v>79</v>
-      </c>
-      <c r="I269" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="J269" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="K269" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="270" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H270" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="I270" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="J270" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="K270" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="271" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H271" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="I270" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="J270" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="K270" s="1" t="s">
+      <c r="I271" s="4" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="271" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H271" s="1" t="n">
+      <c r="J271" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="K271" s="1" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="272" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H272" s="1" t="n">
         <v>81</v>
       </c>
-      <c r="I271" s="4" t="s">
-        <v>625</v>
-      </c>
-      <c r="J271" s="4" t="s">
-        <v>626</v>
-      </c>
-      <c r="K271" s="4" t="s">
+      <c r="I272" s="4" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="272" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H272" s="1" t="n">
+      <c r="J272" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="K272" s="4" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="273" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H273" s="1" t="n">
         <v>82</v>
       </c>
-      <c r="I272" s="4" t="s">
-        <v>628</v>
-      </c>
-      <c r="J272" s="4" t="s">
-        <v>629</v>
-      </c>
-      <c r="K272" s="4" t="s">
+      <c r="I273" s="4" t="s">
         <v>630</v>
       </c>
-    </row>
-    <row r="273" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H273" s="1" t="n">
+      <c r="J273" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="K273" s="4" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="274" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H274" s="1" t="n">
         <v>83</v>
       </c>
-      <c r="I273" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="J273" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="K273" s="4" t="s">
+      <c r="I274" s="4" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="274" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H274" s="1" t="n">
+      <c r="J274" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="K274" s="4" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="275" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H275" s="1" t="n">
         <v>84</v>
       </c>
-      <c r="I274" s="4" t="s">
-        <v>634</v>
-      </c>
-      <c r="J274" s="4" t="s">
-        <v>635</v>
-      </c>
-      <c r="K274" s="1" t="s">
+      <c r="I275" s="4" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I275" s="4"/>
-      <c r="J275" s="4"/>
-      <c r="K275" s="1"/>
+      <c r="J275" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="K275" s="1" t="s">
+        <v>638</v>
+      </c>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B276" s="4" t="s">
+      <c r="I276" s="4"/>
+      <c r="J276" s="4"/>
+      <c r="K276" s="1"/>
+    </row>
+    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B277" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="K276" s="1"/>
-    </row>
-    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B277" s="4"/>
       <c r="K277" s="1"/>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="4" t="s">
+      <c r="B278" s="4"/>
+      <c r="K278" s="1"/>
+    </row>
+    <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A279" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="K278" s="1"/>
-    </row>
-    <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H279" s="1" t="n">
+      <c r="K279" s="1"/>
+    </row>
+    <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H280" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="I279" s="4" t="s">
+      <c r="I280" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="J279" s="10" t="s">
+      <c r="J280" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="K279" s="1" t="s">
+      <c r="K280" s="1" t="s">
         <v>161</v>
-      </c>
-    </row>
-    <row r="280" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H280" s="1" t="n">
-        <v>86</v>
-      </c>
-      <c r="I280" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="J280" s="4" t="s">
-        <v>638</v>
-      </c>
-      <c r="K280" s="1" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H281" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="I281" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="J281" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="K281" s="1" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="282" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H282" s="1" t="n">
         <v>87</v>
       </c>
-      <c r="I281" s="4" t="s">
-        <v>640</v>
-      </c>
-      <c r="J281" s="4" t="s">
-        <v>641</v>
-      </c>
-      <c r="K281" s="1" t="s">
+      <c r="I282" s="4" t="s">
         <v>642</v>
       </c>
-    </row>
-    <row r="282" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H282" s="1" t="n">
+      <c r="J282" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="K282" s="1" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="283" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H283" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="I282" s="4" t="s">
-        <v>643</v>
-      </c>
-      <c r="J282" s="4" t="s">
-        <v>644</v>
-      </c>
-      <c r="K282" s="1" t="s">
+      <c r="I283" s="4" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="283" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H283" s="1" t="n">
+      <c r="J283" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="K283" s="1" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="284" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H284" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="I283" s="4" t="s">
-        <v>646</v>
-      </c>
-      <c r="J283" s="4" t="s">
-        <v>647</v>
-      </c>
-      <c r="K283" s="1" t="s">
+      <c r="I284" s="4" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="284" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H284" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="I284" s="4" t="s">
+      <c r="J284" s="4" t="s">
         <v>649</v>
       </c>
-      <c r="J284" s="4" t="s">
+      <c r="K284" s="1" t="s">
         <v>650</v>
-      </c>
-      <c r="K284" s="1" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H285" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="I285" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="J285" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="K285" s="1" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="286" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H286" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="I285" s="4" t="s">
-        <v>652</v>
-      </c>
-      <c r="J285" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="K285" s="1" t="s">
+      <c r="I286" s="4" t="s">
         <v>654</v>
-      </c>
-    </row>
-    <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H286" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="I286" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="J286" s="4" t="s">
         <v>655</v>
@@ -8250,839 +8260,853 @@
       </c>
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B287" s="4" t="s">
+      <c r="H287" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="I287" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="J287" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="K287" s="1" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B288" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="K287" s="1"/>
-    </row>
-    <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="4" t="s">
+      <c r="K288" s="1"/>
+    </row>
+    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="K289" s="1"/>
-    </row>
-    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H290" s="1" t="n">
+      <c r="K290" s="1"/>
+    </row>
+    <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H291" s="1" t="n">
         <v>74</v>
       </c>
-      <c r="I290" s="4" t="s">
-        <v>657</v>
-      </c>
-      <c r="J290" s="10" t="s">
-        <v>658</v>
-      </c>
-      <c r="K290" s="1" t="s">
+      <c r="I291" s="4" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="291" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H291" s="1" t="n">
+      <c r="J291" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="K291" s="1" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="292" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H292" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="I291" s="4" t="s">
-        <v>660</v>
-      </c>
-      <c r="J291" s="4" t="s">
-        <v>661</v>
-      </c>
-      <c r="K291" s="1" t="s">
+      <c r="I292" s="4" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="292" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H292" s="1" t="n">
+      <c r="J292" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="K292" s="1" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="293" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H293" s="1" t="n">
         <v>76</v>
       </c>
-      <c r="I292" s="4" t="s">
-        <v>663</v>
-      </c>
-      <c r="J292" s="4" t="s">
-        <v>664</v>
-      </c>
-      <c r="K292" s="1" t="s">
+      <c r="I293" s="4" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="293" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H293" s="1" t="n">
+      <c r="J293" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="K293" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="294" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H294" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="I293" s="4" t="s">
-        <v>666</v>
-      </c>
-      <c r="J293" s="4" t="s">
-        <v>667</v>
-      </c>
-      <c r="K293" s="1" t="s">
+      <c r="I294" s="4" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="294" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H294" s="1" t="n">
+      <c r="J294" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="K294" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="295" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H295" s="1" t="n">
         <v>78</v>
       </c>
-      <c r="I294" s="4" t="s">
-        <v>669</v>
-      </c>
-      <c r="J294" s="4" t="s">
-        <v>670</v>
-      </c>
-      <c r="K294" s="1" t="s">
+      <c r="I295" s="4" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I295" s="4"/>
-      <c r="J295" s="4"/>
-      <c r="K295" s="1"/>
+      <c r="J295" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="K295" s="1" t="s">
+        <v>673</v>
+      </c>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I296" s="4"/>
       <c r="J296" s="4"/>
       <c r="K296" s="1"/>
     </row>
-    <row r="297" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B297" s="4" t="s">
+    <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I297" s="4"/>
+      <c r="J297" s="4"/>
+      <c r="K297" s="1"/>
+    </row>
+    <row r="298" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B298" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="298" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="299" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="4" t="s">
+    <row r="299" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="300" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A300" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="300" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H300" s="1" t="n">
+    <row r="301" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H301" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="I300" s="4" t="s">
-        <v>672</v>
-      </c>
-      <c r="J300" s="10" t="s">
-        <v>673</v>
-      </c>
-      <c r="K300" s="4" t="s">
+      <c r="I301" s="4" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="301" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H301" s="1" t="n">
+      <c r="J301" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="K301" s="4" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="302" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H302" s="1" t="n">
         <v>67</v>
       </c>
-      <c r="I301" s="4" t="s">
-        <v>675</v>
-      </c>
-      <c r="J301" s="4" t="s">
-        <v>676</v>
-      </c>
-      <c r="K301" s="4" t="s">
+      <c r="I302" s="4" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="302" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H302" s="1" t="n">
+      <c r="J302" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="K302" s="4" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="303" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H303" s="1" t="n">
         <v>68</v>
       </c>
-      <c r="I302" s="4" t="s">
-        <v>678</v>
-      </c>
-      <c r="J302" s="4" t="s">
-        <v>679</v>
-      </c>
-      <c r="K302" s="1" t="s">
+      <c r="I303" s="4" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="303" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H303" s="1" t="n">
+      <c r="J303" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="K303" s="1" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="304" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H304" s="1" t="n">
         <v>69</v>
       </c>
-      <c r="I303" s="4" t="s">
-        <v>681</v>
-      </c>
-      <c r="J303" s="4" t="s">
-        <v>682</v>
-      </c>
-      <c r="K303" s="4" t="s">
+      <c r="I304" s="4" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="304" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H304" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="I304" s="4" t="s">
+      <c r="J304" s="4" t="s">
         <v>684</v>
       </c>
-      <c r="J304" s="4" t="s">
+      <c r="K304" s="4" t="s">
         <v>685</v>
-      </c>
-      <c r="K304" s="4" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="305" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H305" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="I305" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="J305" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="K305" s="4" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="306" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H306" s="1" t="n">
         <v>71</v>
       </c>
-      <c r="I305" s="4" t="s">
-        <v>687</v>
-      </c>
-      <c r="J305" s="4" t="s">
-        <v>688</v>
-      </c>
-      <c r="K305" s="4" t="s">
+      <c r="I306" s="4" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="306" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H306" s="1" t="n">
-        <v>72</v>
-      </c>
-      <c r="I306" s="4" t="s">
+      <c r="J306" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="J306" s="4" t="s">
+      <c r="K306" s="4" t="s">
         <v>691</v>
-      </c>
-      <c r="K306" s="4" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="307" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H307" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="I307" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="J307" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="K307" s="4" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="308" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H308" s="1" t="n">
         <v>73</v>
       </c>
-      <c r="I307" s="4" t="s">
-        <v>693</v>
-      </c>
-      <c r="J307" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="K307" s="1" t="s">
+      <c r="I308" s="4" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="308" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B308" s="4" t="s">
+      <c r="J308" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="K308" s="1" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="309" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B309" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="309" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="4" t="s">
+    <row r="310" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A310" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="310" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H310" s="1" t="n">
+    <row r="311" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H311" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="I310" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="J310" s="10" t="s">
-        <v>697</v>
-      </c>
-      <c r="K310" s="1" t="s">
+      <c r="I311" s="4" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="311" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H311" s="1" t="n">
+      <c r="J311" s="10" t="s">
+        <v>699</v>
+      </c>
+      <c r="K311" s="1" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="312" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H312" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="I311" s="4" t="s">
-        <v>699</v>
-      </c>
-      <c r="J311" s="4" t="s">
-        <v>700</v>
-      </c>
-      <c r="K311" s="4" t="s">
+      <c r="I312" s="4" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="312" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H312" s="1" t="n">
-        <v>62</v>
-      </c>
-      <c r="I312" s="4" t="s">
+      <c r="J312" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="J312" s="4" t="s">
+      <c r="K312" s="4" t="s">
         <v>703</v>
-      </c>
-      <c r="K312" s="4" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="313" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H313" s="1" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I313" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="J313" s="4" t="s">
         <v>705</v>
       </c>
-      <c r="J313" s="4" t="s">
+      <c r="K313" s="4" t="s">
         <v>706</v>
-      </c>
-      <c r="K313" s="4" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="314" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H314" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="I314" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="J314" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="K314" s="4" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="315" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H315" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="I314" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="J314" s="4" t="s">
-        <v>709</v>
-      </c>
-      <c r="K314" s="4" t="s">
+      <c r="I315" s="4" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="315" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H315" s="1" t="n">
+      <c r="J315" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="K315" s="4" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="316" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H316" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="I315" s="4" t="s">
-        <v>711</v>
-      </c>
-      <c r="J315" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="K315" s="1" t="s">
+      <c r="I316" s="4" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B316" s="4" t="s">
+      <c r="J316" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="K316" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B317" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="K316" s="1"/>
-    </row>
-    <row r="317" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="K317" s="1"/>
+    </row>
     <row r="318" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="319" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="4" t="s">
+    <row r="319" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="320" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A320" s="4" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="320" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H320" s="1" t="n">
-        <v>53</v>
-      </c>
-      <c r="I320" s="4" t="s">
-        <v>714</v>
-      </c>
-      <c r="J320" s="10" t="s">
-        <v>715</v>
-      </c>
-      <c r="K320" s="4" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="321" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H321" s="1" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I321" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="J321" s="10" t="s">
         <v>717</v>
       </c>
-      <c r="J321" s="10" t="s">
+      <c r="K321" s="4" t="s">
         <v>718</v>
-      </c>
-      <c r="K321" s="4" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="322" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H322" s="1" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I322" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="J322" s="10" t="s">
         <v>720</v>
       </c>
-      <c r="J322" s="10" t="s">
+      <c r="K322" s="4" t="s">
         <v>721</v>
-      </c>
-      <c r="K322" s="4" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="323" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H323" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="I323" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="J323" s="10" t="s">
+        <v>723</v>
+      </c>
+      <c r="K323" s="4" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="324" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H324" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="I323" s="4" t="s">
-        <v>723</v>
-      </c>
-      <c r="J323" s="10" t="s">
-        <v>724</v>
-      </c>
-      <c r="K323" s="4" t="s">
+      <c r="I324" s="4" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="324" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H324" s="1" t="n">
+      <c r="J324" s="10" t="s">
+        <v>726</v>
+      </c>
+      <c r="K324" s="4" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="325" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H325" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="I324" s="4" t="s">
+      <c r="I325" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="J324" s="4" t="s">
+      <c r="J325" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="K324" s="1" t="s">
+      <c r="K325" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="325" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H325" s="1" t="n">
+    <row r="326" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H326" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="I325" s="4" t="s">
-        <v>726</v>
-      </c>
-      <c r="J325" s="10" t="s">
-        <v>727</v>
-      </c>
-      <c r="K325" s="4" t="s">
+      <c r="I326" s="4" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H326" s="1" t="n">
+      <c r="J326" s="10" t="s">
+        <v>729</v>
+      </c>
+      <c r="K326" s="4" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H327" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="I326" s="4" t="s">
+      <c r="I327" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="J326" s="10" t="s">
+      <c r="J327" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="K326" s="1" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B327" s="4" t="s">
+      <c r="K327" s="1" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B328" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="K327" s="1"/>
-    </row>
-    <row r="329" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="K328" s="1"/>
+    </row>
     <row r="330" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="331" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A331" s="4" t="s">
+    <row r="331" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="332" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A332" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="332" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H332" s="1" t="n">
+    <row r="333" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H333" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="I332" s="4" t="s">
-        <v>729</v>
-      </c>
-      <c r="J332" s="10" t="s">
-        <v>730</v>
-      </c>
-      <c r="K332" s="1" t="s">
+      <c r="I333" s="4" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="333" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H333" s="1" t="n">
+      <c r="J333" s="10" t="s">
+        <v>732</v>
+      </c>
+      <c r="K333" s="1" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="334" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H334" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="I333" s="4" t="s">
-        <v>732</v>
-      </c>
-      <c r="J333" s="4" t="s">
-        <v>733</v>
-      </c>
-      <c r="K333" s="4" t="s">
+      <c r="I334" s="4" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="334" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H334" s="1" t="n">
+      <c r="J334" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="K334" s="4" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="335" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H335" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="I334" s="4" t="s">
-        <v>735</v>
-      </c>
-      <c r="J334" s="4" t="s">
-        <v>736</v>
-      </c>
-      <c r="K334" s="4" t="s">
+      <c r="I335" s="4" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="335" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H335" s="1" t="n">
+      <c r="J335" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="K335" s="4" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="336" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H336" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="I335" s="4" t="s">
-        <v>738</v>
-      </c>
-      <c r="J335" s="10" t="s">
-        <v>739</v>
-      </c>
-      <c r="K335" s="4" t="s">
+      <c r="I336" s="4" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="336" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H336" s="1" t="n">
+      <c r="J336" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="K336" s="4" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="337" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H337" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="I336" s="4" t="s">
-        <v>741</v>
-      </c>
-      <c r="J336" s="4" t="s">
-        <v>742</v>
-      </c>
-      <c r="K336" s="4" t="s">
+      <c r="I337" s="4" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="337" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H337" s="1" t="n">
+      <c r="J337" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="K337" s="4" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="338" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H338" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="I337" s="4" t="s">
-        <v>744</v>
-      </c>
-      <c r="J337" s="4" t="s">
-        <v>745</v>
-      </c>
-      <c r="K337" s="1" t="s">
+      <c r="I338" s="4" t="s">
         <v>746</v>
       </c>
-    </row>
-    <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B338" s="4" t="s">
+      <c r="J338" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="K338" s="1" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B339" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="K338" s="1"/>
-    </row>
-    <row r="339" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="K339" s="1"/>
+    </row>
     <row r="340" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="341" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="4" t="s">
+    <row r="341" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="342" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A342" s="4" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="342" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H342" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I342" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="J342" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="K342" s="4" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="343" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H343" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I343" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="J343" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="K343" s="4" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="344" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H344" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I343" s="4" t="s">
-        <v>750</v>
-      </c>
-      <c r="J343" s="4" t="s">
-        <v>751</v>
-      </c>
-      <c r="K343" s="1" t="s">
+      <c r="I344" s="4" t="s">
         <v>752</v>
       </c>
-    </row>
-    <row r="344" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H344" s="1" t="n">
+      <c r="J344" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="K344" s="1" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="345" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H345" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I344" s="4" t="s">
-        <v>753</v>
-      </c>
-      <c r="J344" s="4" t="s">
-        <v>754</v>
-      </c>
-      <c r="K344" s="4" t="s">
+      <c r="I345" s="4" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="345" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H345" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I345" s="4" t="s">
+      <c r="J345" s="4" t="s">
         <v>756</v>
       </c>
-      <c r="J345" s="4" t="s">
+      <c r="K345" s="4" t="s">
         <v>757</v>
-      </c>
-      <c r="K345" s="4" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="346" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H346" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I346" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="J346" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="K346" s="4" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="347" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H347" s="1" t="n">
         <v>212</v>
       </c>
-      <c r="I346" s="4" t="s">
-        <v>759</v>
-      </c>
-      <c r="J346" s="4" t="s">
-        <v>760</v>
-      </c>
-      <c r="K346" s="4" t="s">
+      <c r="I347" s="4" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="347" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H347" s="1" t="n">
+      <c r="J347" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="K347" s="4" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="348" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H348" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="I347" s="4" t="s">
-        <v>762</v>
-      </c>
-      <c r="J347" s="4" t="s">
-        <v>763</v>
-      </c>
-      <c r="K347" s="4" t="s">
+      <c r="I348" s="4" t="s">
         <v>764</v>
       </c>
-    </row>
-    <row r="348" s="1" customFormat="true" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H348" s="1" t="n">
+      <c r="J348" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="K348" s="4" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="349" s="1" customFormat="true" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H349" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="I348" s="4" t="s">
-        <v>765</v>
-      </c>
-      <c r="J348" s="4" t="s">
-        <v>766</v>
-      </c>
-      <c r="K348" s="4" t="s">
+      <c r="I349" s="4" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H349" s="1" t="n">
+      <c r="J349" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="K349" s="4" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H350" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I349" s="4" t="s">
+      <c r="I350" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="J349" s="10" t="s">
+      <c r="J350" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="K349" s="1" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B350" s="4" t="s">
+      <c r="K350" s="1" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B351" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="K350" s="1"/>
-    </row>
-    <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="1" t="s">
+      <c r="K351" s="1"/>
+    </row>
+    <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A353" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D353" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="E353" s="1" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="354" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H354" s="1" t="n">
+    <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D354" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="E354" s="1" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="355" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H355" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I354" s="4" t="s">
-        <v>770</v>
-      </c>
-      <c r="J354" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="K354" s="15" t="s">
+      <c r="I355" s="4" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="355" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H355" s="1" t="n">
+      <c r="J355" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="K355" s="15" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="356" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H356" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="I355" s="4" t="s">
-        <v>773</v>
-      </c>
-      <c r="J355" s="4" t="s">
-        <v>774</v>
-      </c>
-      <c r="K355" s="15" t="s">
+      <c r="I356" s="4" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="356" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B356" s="1" t="s">
+      <c r="J356" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="K356" s="15" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="357" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B357" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="H356" s="1" t="n">
+      <c r="H357" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I356" s="4" t="s">
-        <v>776</v>
-      </c>
-      <c r="J356" s="4" t="s">
-        <v>777</v>
-      </c>
-      <c r="K356" s="15" t="s">
+      <c r="I357" s="4" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A359" s="1" t="s">
+      <c r="J357" s="4" t="s">
         <v>779</v>
       </c>
-      <c r="H359" s="1" t="n">
+      <c r="K357" s="15" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A360" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="H360" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="I359" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="J359" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="K359" s="0" t="s">
+      <c r="I360" s="1" t="s">
         <v>782</v>
       </c>
-    </row>
-    <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B360" s="1" t="s">
+      <c r="J360" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="D360" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="H360" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="I360" s="1" t="s">
+      <c r="K360" s="0" t="s">
         <v>784</v>
-      </c>
-      <c r="J360" s="1" t="s">
-        <v>785</v>
-      </c>
-      <c r="K360" s="0" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B361" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="H361" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I361" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="J361" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="J361" s="1" t="s">
+      <c r="K361" s="0" t="s">
         <v>788</v>
-      </c>
-      <c r="K361" s="0" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B362" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="D362" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="H362" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I362" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="J362" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="D362" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="H362" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="I362" s="1" t="s">
+      <c r="K362" s="0" t="s">
         <v>791</v>
-      </c>
-      <c r="J362" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="K362" s="0" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B363" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="H363" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="I363" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="J363" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="K363" s="0" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B364" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D363" s="1" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A367" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="H367" s="1" t="n">
+      <c r="D364" s="1" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A368" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="H368" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="I367" s="1" t="s">
-        <v>795</v>
-      </c>
-      <c r="J367" s="1" t="s">
-        <v>796</v>
-      </c>
-      <c r="K367" s="0" t="s">
+      <c r="I368" s="1" t="s">
         <v>797</v>
       </c>
-    </row>
-    <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B368" s="1" t="s">
+      <c r="J368" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="K368" s="0" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B369" s="1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="1" t="s">
-        <v>790</v>
-      </c>
-    </row>
     <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H372" s="1" t="n">
+      <c r="A372" s="1" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H373" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="I372" s="1" t="s">
-        <v>798</v>
-      </c>
-      <c r="J372" s="1" t="s">
-        <v>799</v>
-      </c>
-      <c r="K372" s="0" t="s">
+      <c r="I373" s="1" t="s">
         <v>800</v>
       </c>
-    </row>
-    <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B373" s="1" t="s">
+      <c r="J373" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="K373" s="0" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B374" s="1" t="s">
         <v>178</v>
       </c>
     </row>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/_tutorial.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/_tutorial.xlsx
@@ -3266,7 +3266,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3318,6 +3318,13 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3382,7 +3389,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3431,15 +3438,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4661,7 +4672,7 @@
       <c r="J13" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="12" t="s">
         <v>161</v>
       </c>
     </row>
@@ -5647,7 +5658,7 @@
       <c r="H106" s="1" t="n">
         <v>169</v>
       </c>
-      <c r="I106" s="12" t="s">
+      <c r="I106" s="13" t="s">
         <v>317</v>
       </c>
       <c r="J106" s="10" t="s">
@@ -5668,7 +5679,7 @@
       <c r="H107" s="1" t="n">
         <v>170</v>
       </c>
-      <c r="I107" s="12" t="s">
+      <c r="I107" s="13" t="s">
         <v>320</v>
       </c>
       <c r="J107" s="10" t="s">
@@ -5689,7 +5700,7 @@
       <c r="H108" s="1" t="n">
         <v>171</v>
       </c>
-      <c r="I108" s="12" t="s">
+      <c r="I108" s="13" t="s">
         <v>323</v>
       </c>
       <c r="J108" s="10" t="s">
@@ -5710,7 +5721,7 @@
       <c r="H109" s="1" t="n">
         <v>172</v>
       </c>
-      <c r="I109" s="12" t="s">
+      <c r="I109" s="13" t="s">
         <v>326</v>
       </c>
       <c r="J109" s="10" t="s">
@@ -5731,7 +5742,7 @@
       <c r="H110" s="1" t="n">
         <v>173</v>
       </c>
-      <c r="I110" s="12" t="s">
+      <c r="I110" s="13" t="s">
         <v>329</v>
       </c>
       <c r="J110" s="10" t="s">
@@ -5792,7 +5803,7 @@
       <c r="H114" s="1" t="n">
         <v>155</v>
       </c>
-      <c r="I114" s="13" t="s">
+      <c r="I114" s="14" t="s">
         <v>332</v>
       </c>
       <c r="J114" s="10" t="s">
@@ -5813,7 +5824,7 @@
       <c r="H115" s="1" t="n">
         <v>156</v>
       </c>
-      <c r="I115" s="12" t="s">
+      <c r="I115" s="13" t="s">
         <v>335</v>
       </c>
       <c r="J115" s="10" t="s">
@@ -5834,7 +5845,7 @@
       <c r="H116" s="1" t="n">
         <v>157</v>
       </c>
-      <c r="I116" s="12" t="s">
+      <c r="I116" s="13" t="s">
         <v>338</v>
       </c>
       <c r="J116" s="10" t="s">
@@ -5855,7 +5866,7 @@
       <c r="H117" s="1" t="n">
         <v>158</v>
       </c>
-      <c r="I117" s="12" t="s">
+      <c r="I117" s="13" t="s">
         <v>341</v>
       </c>
       <c r="J117" s="10" t="s">
@@ -5876,7 +5887,7 @@
       <c r="H118" s="1" t="n">
         <v>159</v>
       </c>
-      <c r="I118" s="12" t="s">
+      <c r="I118" s="13" t="s">
         <v>344</v>
       </c>
       <c r="J118" s="10" t="s">
@@ -5897,7 +5908,7 @@
       <c r="H119" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="I119" s="12" t="s">
+      <c r="I119" s="13" t="s">
         <v>347</v>
       </c>
       <c r="J119" s="10" t="s">
@@ -5946,7 +5957,7 @@
       <c r="H122" s="1" t="n">
         <v>161</v>
       </c>
-      <c r="I122" s="13" t="s">
+      <c r="I122" s="14" t="s">
         <v>350</v>
       </c>
       <c r="J122" s="10" t="s">
@@ -5967,7 +5978,7 @@
       <c r="H123" s="1" t="n">
         <v>162</v>
       </c>
-      <c r="I123" s="12" t="s">
+      <c r="I123" s="13" t="s">
         <v>353</v>
       </c>
       <c r="J123" s="10" t="s">
@@ -5988,7 +5999,7 @@
       <c r="H124" s="1" t="n">
         <v>163</v>
       </c>
-      <c r="I124" s="12" t="s">
+      <c r="I124" s="13" t="s">
         <v>356</v>
       </c>
       <c r="J124" s="10" t="s">
@@ -6009,7 +6020,7 @@
       <c r="H125" s="1" t="n">
         <v>164</v>
       </c>
-      <c r="I125" s="12" t="s">
+      <c r="I125" s="13" t="s">
         <v>359</v>
       </c>
       <c r="J125" s="10" t="s">
@@ -6058,7 +6069,7 @@
       <c r="H128" s="1" t="n">
         <v>165</v>
       </c>
-      <c r="I128" s="13" t="s">
+      <c r="I128" s="14" t="s">
         <v>362</v>
       </c>
       <c r="J128" s="10" t="s">
@@ -6079,7 +6090,7 @@
       <c r="H129" s="1" t="n">
         <v>166</v>
       </c>
-      <c r="I129" s="13" t="s">
+      <c r="I129" s="14" t="s">
         <v>161</v>
       </c>
       <c r="J129" s="10" t="s">
@@ -6100,7 +6111,7 @@
       <c r="H130" s="1" t="n">
         <v>167</v>
       </c>
-      <c r="I130" s="13" t="s">
+      <c r="I130" s="14" t="s">
         <v>365</v>
       </c>
       <c r="J130" s="10" t="s">
@@ -6121,7 +6132,7 @@
       <c r="H131" s="1" t="n">
         <v>168</v>
       </c>
-      <c r="I131" s="12" t="s">
+      <c r="I131" s="13" t="s">
         <v>368</v>
       </c>
       <c r="J131" s="10" t="s">
@@ -6170,7 +6181,7 @@
       <c r="H134" s="1" t="n">
         <v>116</v>
       </c>
-      <c r="I134" s="12" t="s">
+      <c r="I134" s="13" t="s">
         <v>371</v>
       </c>
       <c r="J134" s="10" t="s">
@@ -6191,7 +6202,7 @@
       <c r="H135" s="1" t="n">
         <v>117</v>
       </c>
-      <c r="I135" s="12" t="s">
+      <c r="I135" s="13" t="s">
         <v>374</v>
       </c>
       <c r="J135" s="10" t="s">
@@ -6212,7 +6223,7 @@
       <c r="H136" s="1" t="n">
         <v>118</v>
       </c>
-      <c r="I136" s="12" t="s">
+      <c r="I136" s="13" t="s">
         <v>377</v>
       </c>
       <c r="J136" s="10" t="s">
@@ -6233,7 +6244,7 @@
       <c r="H137" s="1" t="n">
         <v>119</v>
       </c>
-      <c r="I137" s="12" t="s">
+      <c r="I137" s="13" t="s">
         <v>380</v>
       </c>
       <c r="J137" s="10" t="s">
@@ -6254,7 +6265,7 @@
       <c r="H138" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="I138" s="12" t="s">
+      <c r="I138" s="13" t="s">
         <v>383</v>
       </c>
       <c r="J138" s="10" t="s">
@@ -6315,7 +6326,7 @@
       <c r="H142" s="1" t="n">
         <v>121</v>
       </c>
-      <c r="I142" s="12" t="s">
+      <c r="I142" s="13" t="s">
         <v>386</v>
       </c>
       <c r="J142" s="10" t="s">
@@ -6336,7 +6347,7 @@
       <c r="H143" s="1" t="n">
         <v>122</v>
       </c>
-      <c r="I143" s="12" t="s">
+      <c r="I143" s="13" t="s">
         <v>389</v>
       </c>
       <c r="J143" s="4" t="s">
@@ -6357,7 +6368,7 @@
       <c r="H144" s="1" t="n">
         <v>123</v>
       </c>
-      <c r="I144" s="12" t="s">
+      <c r="I144" s="13" t="s">
         <v>392</v>
       </c>
       <c r="J144" s="4" t="s">
@@ -6378,7 +6389,7 @@
       <c r="H145" s="1" t="n">
         <v>124</v>
       </c>
-      <c r="I145" s="12" t="s">
+      <c r="I145" s="13" t="s">
         <v>395</v>
       </c>
       <c r="J145" s="4" t="s">
@@ -6399,7 +6410,7 @@
       <c r="H146" s="1" t="n">
         <v>125</v>
       </c>
-      <c r="I146" s="12" t="s">
+      <c r="I146" s="13" t="s">
         <v>398</v>
       </c>
       <c r="J146" s="4" t="s">
@@ -6493,7 +6504,7 @@
       <c r="H152" s="1" t="n">
         <v>127</v>
       </c>
-      <c r="I152" s="12" t="s">
+      <c r="I152" s="13" t="s">
         <v>404</v>
       </c>
       <c r="J152" s="10" t="s">
@@ -6516,7 +6527,7 @@
       <c r="H153" s="1" t="n">
         <v>230</v>
       </c>
-      <c r="I153" s="12" t="s">
+      <c r="I153" s="13" t="s">
         <v>408</v>
       </c>
       <c r="J153" s="10" t="s">
@@ -6540,7 +6551,7 @@
       </c>
       <c r="F154" s="4"/>
       <c r="G154" s="4"/>
-      <c r="I154" s="12"/>
+      <c r="I154" s="13"/>
       <c r="J154" s="10"/>
       <c r="K154" s="4"/>
     </row>
@@ -6557,7 +6568,7 @@
       <c r="H155" s="1" t="n">
         <v>231</v>
       </c>
-      <c r="I155" s="12" t="s">
+      <c r="I155" s="13" t="s">
         <v>414</v>
       </c>
       <c r="J155" s="10" t="s">
@@ -6580,7 +6591,7 @@
       <c r="H156" s="1" t="n">
         <v>232</v>
       </c>
-      <c r="I156" s="12" t="s">
+      <c r="I156" s="13" t="s">
         <v>417</v>
       </c>
       <c r="J156" s="10" t="s">
@@ -6601,7 +6612,7 @@
       <c r="H157" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="I157" s="14" t="s">
+      <c r="I157" s="15" t="s">
         <v>420</v>
       </c>
       <c r="J157" s="4" t="s">
@@ -6674,7 +6685,7 @@
       <c r="H162" s="1" t="n">
         <v>129</v>
       </c>
-      <c r="I162" s="12" t="s">
+      <c r="I162" s="13" t="s">
         <v>423</v>
       </c>
       <c r="J162" s="10" t="s">
@@ -6695,7 +6706,7 @@
       <c r="H163" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="I163" s="12" t="s">
+      <c r="I163" s="13" t="s">
         <v>426</v>
       </c>
       <c r="J163" s="4" t="s">
@@ -6716,7 +6727,7 @@
       <c r="H164" s="1" t="n">
         <v>131</v>
       </c>
-      <c r="I164" s="12" t="s">
+      <c r="I164" s="13" t="s">
         <v>429</v>
       </c>
       <c r="J164" s="4" t="s">
@@ -6737,7 +6748,7 @@
       <c r="H165" s="1" t="n">
         <v>132</v>
       </c>
-      <c r="I165" s="12" t="s">
+      <c r="I165" s="13" t="s">
         <v>432</v>
       </c>
       <c r="J165" s="4" t="s">
@@ -6758,7 +6769,7 @@
       <c r="H166" s="1" t="n">
         <v>133</v>
       </c>
-      <c r="I166" s="12" t="s">
+      <c r="I166" s="13" t="s">
         <v>435</v>
       </c>
       <c r="J166" s="4" t="s">
@@ -6779,7 +6790,7 @@
       <c r="H167" s="1" t="n">
         <v>134</v>
       </c>
-      <c r="I167" s="12" t="s">
+      <c r="I167" s="13" t="s">
         <v>438</v>
       </c>
       <c r="J167" s="4" t="s">
@@ -6800,7 +6811,7 @@
       <c r="H168" s="1" t="n">
         <v>135</v>
       </c>
-      <c r="I168" s="14" t="s">
+      <c r="I168" s="15" t="s">
         <v>441</v>
       </c>
       <c r="J168" s="4" t="s">
@@ -6821,7 +6832,7 @@
       <c r="H169" s="1" t="n">
         <v>136</v>
       </c>
-      <c r="I169" s="14" t="s">
+      <c r="I169" s="15" t="s">
         <v>444</v>
       </c>
       <c r="J169" s="4" t="s">
@@ -6882,7 +6893,7 @@
       <c r="H173" s="1" t="n">
         <v>137</v>
       </c>
-      <c r="I173" s="12" t="s">
+      <c r="I173" s="13" t="s">
         <v>447</v>
       </c>
       <c r="J173" s="10" t="s">
@@ -6903,7 +6914,7 @@
       <c r="H174" s="1" t="n">
         <v>138</v>
       </c>
-      <c r="I174" s="12" t="s">
+      <c r="I174" s="13" t="s">
         <v>450</v>
       </c>
       <c r="J174" s="10" t="s">
@@ -6924,7 +6935,7 @@
       <c r="H175" s="1" t="n">
         <v>139</v>
       </c>
-      <c r="I175" s="12" t="s">
+      <c r="I175" s="13" t="s">
         <v>453</v>
       </c>
       <c r="J175" s="10" t="s">
@@ -6945,7 +6956,7 @@
       <c r="H176" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="I176" s="12" t="s">
+      <c r="I176" s="13" t="s">
         <v>456</v>
       </c>
       <c r="J176" s="10" t="s">
@@ -6966,7 +6977,7 @@
       <c r="H177" s="1" t="n">
         <v>141</v>
       </c>
-      <c r="I177" s="12" t="s">
+      <c r="I177" s="13" t="s">
         <v>459</v>
       </c>
       <c r="J177" s="10" t="s">
@@ -6987,7 +6998,7 @@
       <c r="H178" s="1" t="n">
         <v>142</v>
       </c>
-      <c r="I178" s="12" t="s">
+      <c r="I178" s="13" t="s">
         <v>462</v>
       </c>
       <c r="J178" s="10" t="s">
@@ -7036,7 +7047,7 @@
       <c r="H181" s="1" t="n">
         <v>143</v>
       </c>
-      <c r="I181" s="12" t="s">
+      <c r="I181" s="13" t="s">
         <v>465</v>
       </c>
       <c r="J181" s="10" t="s">
@@ -7057,7 +7068,7 @@
       <c r="H182" s="1" t="n">
         <v>144</v>
       </c>
-      <c r="I182" s="12" t="s">
+      <c r="I182" s="13" t="s">
         <v>468</v>
       </c>
       <c r="J182" s="4" t="s">
@@ -7078,7 +7089,7 @@
       <c r="H183" s="1" t="n">
         <v>145</v>
       </c>
-      <c r="I183" s="12" t="s">
+      <c r="I183" s="13" t="s">
         <v>471</v>
       </c>
       <c r="J183" s="4" t="s">
@@ -7099,7 +7110,7 @@
       <c r="H184" s="1" t="n">
         <v>146</v>
       </c>
-      <c r="I184" s="12" t="s">
+      <c r="I184" s="13" t="s">
         <v>474</v>
       </c>
       <c r="J184" s="4" t="s">
@@ -7120,7 +7131,7 @@
       <c r="H185" s="1" t="n">
         <v>147</v>
       </c>
-      <c r="I185" s="12" t="s">
+      <c r="I185" s="13" t="s">
         <v>477</v>
       </c>
       <c r="J185" s="4" t="s">
@@ -7746,7 +7757,7 @@
       <c r="J239" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="K239" s="15" t="s">
+      <c r="K239" s="16" t="s">
         <v>572</v>
       </c>
     </row>
@@ -7774,7 +7785,7 @@
       <c r="J241" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="K241" s="15" t="s">
+      <c r="K241" s="16" t="s">
         <v>578</v>
       </c>
     </row>
@@ -7802,7 +7813,7 @@
       <c r="J243" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="K243" s="15" t="s">
+      <c r="K243" s="16" t="s">
         <v>584</v>
       </c>
     </row>
@@ -7816,7 +7827,7 @@
       <c r="J244" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="K244" s="15" t="s">
+      <c r="K244" s="16" t="s">
         <v>587</v>
       </c>
     </row>
@@ -8944,7 +8955,7 @@
       <c r="J355" s="4" t="s">
         <v>773</v>
       </c>
-      <c r="K355" s="15" t="s">
+      <c r="K355" s="16" t="s">
         <v>774</v>
       </c>
     </row>
@@ -8958,7 +8969,7 @@
       <c r="J356" s="4" t="s">
         <v>776</v>
       </c>
-      <c r="K356" s="15" t="s">
+      <c r="K356" s="16" t="s">
         <v>777</v>
       </c>
     </row>
@@ -8975,7 +8986,7 @@
       <c r="J357" s="4" t="s">
         <v>779</v>
       </c>
-      <c r="K357" s="15" t="s">
+      <c r="K357" s="16" t="s">
         <v>780</v>
       </c>
     </row>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/_tutorial.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/_tutorial.xlsx
@@ -3266,7 +3266,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3318,13 +3318,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3389,7 +3382,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3438,19 +3431,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4579,6 +4568,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="74.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="88.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="35.74"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4672,7 +4662,7 @@
       <c r="J13" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="K13" s="12" t="s">
+      <c r="K13" s="4" t="s">
         <v>161</v>
       </c>
     </row>
@@ -5658,7 +5648,7 @@
       <c r="H106" s="1" t="n">
         <v>169</v>
       </c>
-      <c r="I106" s="13" t="s">
+      <c r="I106" s="12" t="s">
         <v>317</v>
       </c>
       <c r="J106" s="10" t="s">
@@ -5679,7 +5669,7 @@
       <c r="H107" s="1" t="n">
         <v>170</v>
       </c>
-      <c r="I107" s="13" t="s">
+      <c r="I107" s="12" t="s">
         <v>320</v>
       </c>
       <c r="J107" s="10" t="s">
@@ -5700,7 +5690,7 @@
       <c r="H108" s="1" t="n">
         <v>171</v>
       </c>
-      <c r="I108" s="13" t="s">
+      <c r="I108" s="12" t="s">
         <v>323</v>
       </c>
       <c r="J108" s="10" t="s">
@@ -5721,7 +5711,7 @@
       <c r="H109" s="1" t="n">
         <v>172</v>
       </c>
-      <c r="I109" s="13" t="s">
+      <c r="I109" s="12" t="s">
         <v>326</v>
       </c>
       <c r="J109" s="10" t="s">
@@ -5742,7 +5732,7 @@
       <c r="H110" s="1" t="n">
         <v>173</v>
       </c>
-      <c r="I110" s="13" t="s">
+      <c r="I110" s="12" t="s">
         <v>329</v>
       </c>
       <c r="J110" s="10" t="s">
@@ -5803,7 +5793,7 @@
       <c r="H114" s="1" t="n">
         <v>155</v>
       </c>
-      <c r="I114" s="14" t="s">
+      <c r="I114" s="13" t="s">
         <v>332</v>
       </c>
       <c r="J114" s="10" t="s">
@@ -5824,7 +5814,7 @@
       <c r="H115" s="1" t="n">
         <v>156</v>
       </c>
-      <c r="I115" s="13" t="s">
+      <c r="I115" s="12" t="s">
         <v>335</v>
       </c>
       <c r="J115" s="10" t="s">
@@ -5845,7 +5835,7 @@
       <c r="H116" s="1" t="n">
         <v>157</v>
       </c>
-      <c r="I116" s="13" t="s">
+      <c r="I116" s="12" t="s">
         <v>338</v>
       </c>
       <c r="J116" s="10" t="s">
@@ -5866,7 +5856,7 @@
       <c r="H117" s="1" t="n">
         <v>158</v>
       </c>
-      <c r="I117" s="13" t="s">
+      <c r="I117" s="12" t="s">
         <v>341</v>
       </c>
       <c r="J117" s="10" t="s">
@@ -5887,7 +5877,7 @@
       <c r="H118" s="1" t="n">
         <v>159</v>
       </c>
-      <c r="I118" s="13" t="s">
+      <c r="I118" s="12" t="s">
         <v>344</v>
       </c>
       <c r="J118" s="10" t="s">
@@ -5908,7 +5898,7 @@
       <c r="H119" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="I119" s="13" t="s">
+      <c r="I119" s="12" t="s">
         <v>347</v>
       </c>
       <c r="J119" s="10" t="s">
@@ -5957,7 +5947,7 @@
       <c r="H122" s="1" t="n">
         <v>161</v>
       </c>
-      <c r="I122" s="14" t="s">
+      <c r="I122" s="13" t="s">
         <v>350</v>
       </c>
       <c r="J122" s="10" t="s">
@@ -5978,7 +5968,7 @@
       <c r="H123" s="1" t="n">
         <v>162</v>
       </c>
-      <c r="I123" s="13" t="s">
+      <c r="I123" s="12" t="s">
         <v>353</v>
       </c>
       <c r="J123" s="10" t="s">
@@ -5999,7 +5989,7 @@
       <c r="H124" s="1" t="n">
         <v>163</v>
       </c>
-      <c r="I124" s="13" t="s">
+      <c r="I124" s="12" t="s">
         <v>356</v>
       </c>
       <c r="J124" s="10" t="s">
@@ -6020,7 +6010,7 @@
       <c r="H125" s="1" t="n">
         <v>164</v>
       </c>
-      <c r="I125" s="13" t="s">
+      <c r="I125" s="12" t="s">
         <v>359</v>
       </c>
       <c r="J125" s="10" t="s">
@@ -6069,7 +6059,7 @@
       <c r="H128" s="1" t="n">
         <v>165</v>
       </c>
-      <c r="I128" s="14" t="s">
+      <c r="I128" s="13" t="s">
         <v>362</v>
       </c>
       <c r="J128" s="10" t="s">
@@ -6090,7 +6080,7 @@
       <c r="H129" s="1" t="n">
         <v>166</v>
       </c>
-      <c r="I129" s="14" t="s">
+      <c r="I129" s="13" t="s">
         <v>161</v>
       </c>
       <c r="J129" s="10" t="s">
@@ -6111,7 +6101,7 @@
       <c r="H130" s="1" t="n">
         <v>167</v>
       </c>
-      <c r="I130" s="14" t="s">
+      <c r="I130" s="13" t="s">
         <v>365</v>
       </c>
       <c r="J130" s="10" t="s">
@@ -6132,7 +6122,7 @@
       <c r="H131" s="1" t="n">
         <v>168</v>
       </c>
-      <c r="I131" s="13" t="s">
+      <c r="I131" s="12" t="s">
         <v>368</v>
       </c>
       <c r="J131" s="10" t="s">
@@ -6181,7 +6171,7 @@
       <c r="H134" s="1" t="n">
         <v>116</v>
       </c>
-      <c r="I134" s="13" t="s">
+      <c r="I134" s="12" t="s">
         <v>371</v>
       </c>
       <c r="J134" s="10" t="s">
@@ -6202,7 +6192,7 @@
       <c r="H135" s="1" t="n">
         <v>117</v>
       </c>
-      <c r="I135" s="13" t="s">
+      <c r="I135" s="12" t="s">
         <v>374</v>
       </c>
       <c r="J135" s="10" t="s">
@@ -6223,7 +6213,7 @@
       <c r="H136" s="1" t="n">
         <v>118</v>
       </c>
-      <c r="I136" s="13" t="s">
+      <c r="I136" s="12" t="s">
         <v>377</v>
       </c>
       <c r="J136" s="10" t="s">
@@ -6244,7 +6234,7 @@
       <c r="H137" s="1" t="n">
         <v>119</v>
       </c>
-      <c r="I137" s="13" t="s">
+      <c r="I137" s="12" t="s">
         <v>380</v>
       </c>
       <c r="J137" s="10" t="s">
@@ -6265,7 +6255,7 @@
       <c r="H138" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="I138" s="13" t="s">
+      <c r="I138" s="12" t="s">
         <v>383</v>
       </c>
       <c r="J138" s="10" t="s">
@@ -6326,7 +6316,7 @@
       <c r="H142" s="1" t="n">
         <v>121</v>
       </c>
-      <c r="I142" s="13" t="s">
+      <c r="I142" s="12" t="s">
         <v>386</v>
       </c>
       <c r="J142" s="10" t="s">
@@ -6347,7 +6337,7 @@
       <c r="H143" s="1" t="n">
         <v>122</v>
       </c>
-      <c r="I143" s="13" t="s">
+      <c r="I143" s="12" t="s">
         <v>389</v>
       </c>
       <c r="J143" s="4" t="s">
@@ -6368,7 +6358,7 @@
       <c r="H144" s="1" t="n">
         <v>123</v>
       </c>
-      <c r="I144" s="13" t="s">
+      <c r="I144" s="12" t="s">
         <v>392</v>
       </c>
       <c r="J144" s="4" t="s">
@@ -6389,7 +6379,7 @@
       <c r="H145" s="1" t="n">
         <v>124</v>
       </c>
-      <c r="I145" s="13" t="s">
+      <c r="I145" s="12" t="s">
         <v>395</v>
       </c>
       <c r="J145" s="4" t="s">
@@ -6410,7 +6400,7 @@
       <c r="H146" s="1" t="n">
         <v>125</v>
       </c>
-      <c r="I146" s="13" t="s">
+      <c r="I146" s="12" t="s">
         <v>398</v>
       </c>
       <c r="J146" s="4" t="s">
@@ -6504,7 +6494,7 @@
       <c r="H152" s="1" t="n">
         <v>127</v>
       </c>
-      <c r="I152" s="13" t="s">
+      <c r="I152" s="12" t="s">
         <v>404</v>
       </c>
       <c r="J152" s="10" t="s">
@@ -6527,7 +6517,7 @@
       <c r="H153" s="1" t="n">
         <v>230</v>
       </c>
-      <c r="I153" s="13" t="s">
+      <c r="I153" s="12" t="s">
         <v>408</v>
       </c>
       <c r="J153" s="10" t="s">
@@ -6551,7 +6541,7 @@
       </c>
       <c r="F154" s="4"/>
       <c r="G154" s="4"/>
-      <c r="I154" s="13"/>
+      <c r="I154" s="12"/>
       <c r="J154" s="10"/>
       <c r="K154" s="4"/>
     </row>
@@ -6568,7 +6558,7 @@
       <c r="H155" s="1" t="n">
         <v>231</v>
       </c>
-      <c r="I155" s="13" t="s">
+      <c r="I155" s="12" t="s">
         <v>414</v>
       </c>
       <c r="J155" s="10" t="s">
@@ -6591,7 +6581,7 @@
       <c r="H156" s="1" t="n">
         <v>232</v>
       </c>
-      <c r="I156" s="13" t="s">
+      <c r="I156" s="12" t="s">
         <v>417</v>
       </c>
       <c r="J156" s="10" t="s">
@@ -6612,7 +6602,7 @@
       <c r="H157" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="I157" s="15" t="s">
+      <c r="I157" s="14" t="s">
         <v>420</v>
       </c>
       <c r="J157" s="4" t="s">
@@ -6685,7 +6675,7 @@
       <c r="H162" s="1" t="n">
         <v>129</v>
       </c>
-      <c r="I162" s="13" t="s">
+      <c r="I162" s="12" t="s">
         <v>423</v>
       </c>
       <c r="J162" s="10" t="s">
@@ -6706,7 +6696,7 @@
       <c r="H163" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="I163" s="13" t="s">
+      <c r="I163" s="12" t="s">
         <v>426</v>
       </c>
       <c r="J163" s="4" t="s">
@@ -6727,7 +6717,7 @@
       <c r="H164" s="1" t="n">
         <v>131</v>
       </c>
-      <c r="I164" s="13" t="s">
+      <c r="I164" s="12" t="s">
         <v>429</v>
       </c>
       <c r="J164" s="4" t="s">
@@ -6748,7 +6738,7 @@
       <c r="H165" s="1" t="n">
         <v>132</v>
       </c>
-      <c r="I165" s="13" t="s">
+      <c r="I165" s="12" t="s">
         <v>432</v>
       </c>
       <c r="J165" s="4" t="s">
@@ -6769,7 +6759,7 @@
       <c r="H166" s="1" t="n">
         <v>133</v>
       </c>
-      <c r="I166" s="13" t="s">
+      <c r="I166" s="12" t="s">
         <v>435</v>
       </c>
       <c r="J166" s="4" t="s">
@@ -6790,7 +6780,7 @@
       <c r="H167" s="1" t="n">
         <v>134</v>
       </c>
-      <c r="I167" s="13" t="s">
+      <c r="I167" s="12" t="s">
         <v>438</v>
       </c>
       <c r="J167" s="4" t="s">
@@ -6811,7 +6801,7 @@
       <c r="H168" s="1" t="n">
         <v>135</v>
       </c>
-      <c r="I168" s="15" t="s">
+      <c r="I168" s="14" t="s">
         <v>441</v>
       </c>
       <c r="J168" s="4" t="s">
@@ -6832,7 +6822,7 @@
       <c r="H169" s="1" t="n">
         <v>136</v>
       </c>
-      <c r="I169" s="15" t="s">
+      <c r="I169" s="14" t="s">
         <v>444</v>
       </c>
       <c r="J169" s="4" t="s">
@@ -6893,7 +6883,7 @@
       <c r="H173" s="1" t="n">
         <v>137</v>
       </c>
-      <c r="I173" s="13" t="s">
+      <c r="I173" s="12" t="s">
         <v>447</v>
       </c>
       <c r="J173" s="10" t="s">
@@ -6914,7 +6904,7 @@
       <c r="H174" s="1" t="n">
         <v>138</v>
       </c>
-      <c r="I174" s="13" t="s">
+      <c r="I174" s="12" t="s">
         <v>450</v>
       </c>
       <c r="J174" s="10" t="s">
@@ -6935,7 +6925,7 @@
       <c r="H175" s="1" t="n">
         <v>139</v>
       </c>
-      <c r="I175" s="13" t="s">
+      <c r="I175" s="12" t="s">
         <v>453</v>
       </c>
       <c r="J175" s="10" t="s">
@@ -6956,7 +6946,7 @@
       <c r="H176" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="I176" s="13" t="s">
+      <c r="I176" s="12" t="s">
         <v>456</v>
       </c>
       <c r="J176" s="10" t="s">
@@ -6977,7 +6967,7 @@
       <c r="H177" s="1" t="n">
         <v>141</v>
       </c>
-      <c r="I177" s="13" t="s">
+      <c r="I177" s="12" t="s">
         <v>459</v>
       </c>
       <c r="J177" s="10" t="s">
@@ -6998,7 +6988,7 @@
       <c r="H178" s="1" t="n">
         <v>142</v>
       </c>
-      <c r="I178" s="13" t="s">
+      <c r="I178" s="12" t="s">
         <v>462</v>
       </c>
       <c r="J178" s="10" t="s">
@@ -7047,7 +7037,7 @@
       <c r="H181" s="1" t="n">
         <v>143</v>
       </c>
-      <c r="I181" s="13" t="s">
+      <c r="I181" s="12" t="s">
         <v>465</v>
       </c>
       <c r="J181" s="10" t="s">
@@ -7068,7 +7058,7 @@
       <c r="H182" s="1" t="n">
         <v>144</v>
       </c>
-      <c r="I182" s="13" t="s">
+      <c r="I182" s="12" t="s">
         <v>468</v>
       </c>
       <c r="J182" s="4" t="s">
@@ -7089,7 +7079,7 @@
       <c r="H183" s="1" t="n">
         <v>145</v>
       </c>
-      <c r="I183" s="13" t="s">
+      <c r="I183" s="12" t="s">
         <v>471</v>
       </c>
       <c r="J183" s="4" t="s">
@@ -7110,7 +7100,7 @@
       <c r="H184" s="1" t="n">
         <v>146</v>
       </c>
-      <c r="I184" s="13" t="s">
+      <c r="I184" s="12" t="s">
         <v>474</v>
       </c>
       <c r="J184" s="4" t="s">
@@ -7131,7 +7121,7 @@
       <c r="H185" s="1" t="n">
         <v>147</v>
       </c>
-      <c r="I185" s="13" t="s">
+      <c r="I185" s="12" t="s">
         <v>477</v>
       </c>
       <c r="J185" s="4" t="s">
@@ -7757,7 +7747,7 @@
       <c r="J239" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="K239" s="16" t="s">
+      <c r="K239" s="15" t="s">
         <v>572</v>
       </c>
     </row>
@@ -7785,7 +7775,7 @@
       <c r="J241" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="K241" s="16" t="s">
+      <c r="K241" s="15" t="s">
         <v>578</v>
       </c>
     </row>
@@ -7813,7 +7803,7 @@
       <c r="J243" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="K243" s="16" t="s">
+      <c r="K243" s="15" t="s">
         <v>584</v>
       </c>
     </row>
@@ -7827,7 +7817,7 @@
       <c r="J244" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="K244" s="16" t="s">
+      <c r="K244" s="15" t="s">
         <v>587</v>
       </c>
     </row>
@@ -8955,7 +8945,7 @@
       <c r="J355" s="4" t="s">
         <v>773</v>
       </c>
-      <c r="K355" s="16" t="s">
+      <c r="K355" s="15" t="s">
         <v>774</v>
       </c>
     </row>
@@ -8969,7 +8959,7 @@
       <c r="J356" s="4" t="s">
         <v>776</v>
       </c>
-      <c r="K356" s="16" t="s">
+      <c r="K356" s="15" t="s">
         <v>777</v>
       </c>
     </row>
@@ -8986,7 +8976,7 @@
       <c r="J357" s="4" t="s">
         <v>779</v>
       </c>
-      <c r="K357" s="16" t="s">
+      <c r="K357" s="15" t="s">
         <v>780</v>
       </c>
     </row>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/_tutorial.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/_tutorial.xlsx
@@ -4568,7 +4568,6 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="74.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="88.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="35.74"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
